--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings website/rock/resources/setlists/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98941BBB-016E-904C-87C4-876AAFC79C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{43FFD721-C3C2-AA4F-87B3-B0F966A45747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3260" yWindow="2560" windowWidth="30620" windowHeight="18100" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6700" yWindow="3000" windowWidth="25600" windowHeight="18560" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -13389,7 +13389,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="92" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C5" s="93" t="s">
         <v>2</v>
@@ -13398,10 +13398,10 @@
         <v>3</v>
       </c>
       <c r="E5" s="92" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F5" s="82">
-        <v>2.5810185185185198E-3</v>
+        <v>2.6504629629629599E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -13819,7 +13819,7 @@
         <v>24</v>
       </c>
       <c r="B27" s="92" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C27" s="93" t="s">
         <v>2</v>
@@ -13828,10 +13828,10 @@
         <v>3</v>
       </c>
       <c r="E27" s="92" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F27" s="82">
-        <v>2.6504629629629599E-3</v>
+        <v>2.5810185185185198E-3</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -13937,8 +13937,8 @@
     <hyperlink ref="D9" r:id="rId34" xr:uid="{FF32505C-F8C0-BA49-BD6A-754E19DC05CA}"/>
     <hyperlink ref="C22" r:id="rId35" xr:uid="{BB24184C-0CC4-F741-B5FC-FB7417E8E5AB}"/>
     <hyperlink ref="D22" r:id="rId36" xr:uid="{3CAD6422-2DA3-B244-A86E-A84A34EB5A35}"/>
-    <hyperlink ref="C5" r:id="rId37" xr:uid="{E680ADD2-B380-AD40-95AE-3555DE5059EE}"/>
-    <hyperlink ref="D5" r:id="rId38" xr:uid="{7D32B9CA-4963-DA49-98CF-90ACBCA1F720}"/>
+    <hyperlink ref="C27" r:id="rId37" xr:uid="{E680ADD2-B380-AD40-95AE-3555DE5059EE}"/>
+    <hyperlink ref="D27" r:id="rId38" xr:uid="{7D32B9CA-4963-DA49-98CF-90ACBCA1F720}"/>
     <hyperlink ref="C24" r:id="rId39" xr:uid="{F8D996AF-7AB8-8D4E-8992-0A414935A790}"/>
     <hyperlink ref="D24" r:id="rId40" xr:uid="{5E49751D-7AD6-3042-ABA1-54BF2121B35B}"/>
     <hyperlink ref="C25" r:id="rId41" xr:uid="{57EEA659-BF50-0F4B-BB7B-0387CB139937}"/>
@@ -13947,12 +13947,12 @@
     <hyperlink ref="D26" r:id="rId44" xr:uid="{6CFCBEE4-0F89-8A4E-8A9A-34BFFC520B3A}"/>
     <hyperlink ref="C21" r:id="rId45" xr:uid="{9739C796-6A91-E243-B275-0CB315E77720}"/>
     <hyperlink ref="D21" r:id="rId46" xr:uid="{777EE288-310E-784F-9102-E0DC02E0DFF6}"/>
-    <hyperlink ref="C27" r:id="rId47" xr:uid="{DB070572-2D38-7947-BAB8-A1041EB21526}"/>
-    <hyperlink ref="D27" r:id="rId48" xr:uid="{126CB3D9-81A6-6046-BD60-F05E0F393D2A}"/>
-    <hyperlink ref="C29" r:id="rId49" xr:uid="{18F37730-F3BE-C746-B255-3B43B3187EE2}"/>
-    <hyperlink ref="D29" r:id="rId50" xr:uid="{5911AF34-D2FB-8143-AA88-B053A4313E61}"/>
-    <hyperlink ref="C28" r:id="rId51" xr:uid="{A6EB0356-7914-8D44-985C-B14088BE3110}"/>
-    <hyperlink ref="D28" r:id="rId52" xr:uid="{CCD42764-6A52-F144-A9C0-C0AB05033BF6}"/>
+    <hyperlink ref="C29" r:id="rId47" xr:uid="{18F37730-F3BE-C746-B255-3B43B3187EE2}"/>
+    <hyperlink ref="D29" r:id="rId48" xr:uid="{5911AF34-D2FB-8143-AA88-B053A4313E61}"/>
+    <hyperlink ref="C28" r:id="rId49" xr:uid="{A6EB0356-7914-8D44-985C-B14088BE3110}"/>
+    <hyperlink ref="D28" r:id="rId50" xr:uid="{CCD42764-6A52-F144-A9C0-C0AB05033BF6}"/>
+    <hyperlink ref="C5" r:id="rId51" xr:uid="{35CC4A7D-C1CA-6D41-AFB6-F0525BA45269}"/>
+    <hyperlink ref="D5" r:id="rId52" xr:uid="{CD8E5A75-E6B0-3244-BA65-EA1C992A117A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{432AEBB4-1126-2543-89D4-D8953EC9F34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B3C77D9-6CE3-EA46-81D1-EBEC0FD62205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4760" yWindow="4580" windowWidth="27380" windowHeight="16920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -2190,33 +2190,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2285,6 +2258,33 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2319,10 +2319,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2642,8 +2638,8 @@
       <c r="I1" s="42"/>
       <c r="J1" s="43"/>
       <c r="K1" s="42"/>
-      <c r="L1" s="135"/>
-      <c r="M1" s="135"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
       <c r="N1" s="42"/>
       <c r="O1" s="42"/>
       <c r="P1" s="42"/>
@@ -2691,16 +2687,16 @@
       <c r="J2" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="133" t="s">
+      <c r="K2" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="145" t="s">
+      <c r="L2" s="136" t="s">
         <v>273</v>
       </c>
-      <c r="M2" s="144" t="s">
+      <c r="M2" s="135" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="134" t="s">
+      <c r="N2" s="125" t="s">
         <v>13</v>
       </c>
       <c r="O2" s="46" t="s">
@@ -2775,10 +2771,10 @@
       <c r="J3" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="127"/>
-      <c r="L3" s="142"/>
-      <c r="M3" s="143"/>
-      <c r="N3" s="130"/>
+      <c r="K3" s="118"/>
+      <c r="L3" s="133"/>
+      <c r="M3" s="134"/>
+      <c r="N3" s="121"/>
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
@@ -2799,56 +2795,56 @@
       <c r="AB3" s="13"/>
     </row>
     <row r="4" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="120" t="s">
+      <c r="A4" s="111" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="120" t="s">
+      <c r="B4" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="111" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="122" t="s">
+      <c r="E4" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="123">
+      <c r="F4" s="114">
         <v>3.9583333333333337E-3</v>
       </c>
-      <c r="G4" s="120" t="s">
+      <c r="G4" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="120"/>
-      <c r="I4" s="120"/>
-      <c r="J4" s="120" t="s">
+      <c r="H4" s="111"/>
+      <c r="I4" s="111"/>
+      <c r="J4" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="128"/>
-      <c r="L4" s="137"/>
-      <c r="M4" s="139"/>
-      <c r="N4" s="131"/>
-      <c r="O4" s="120"/>
-      <c r="P4" s="120"/>
-      <c r="Q4" s="120"/>
-      <c r="R4" s="120"/>
-      <c r="S4" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T4" s="120"/>
-      <c r="U4" s="120"/>
-      <c r="V4" s="120"/>
-      <c r="W4" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X4" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y4" s="120"/>
-      <c r="Z4" s="120"/>
-      <c r="AA4" s="120"/>
-      <c r="AB4" s="120"/>
+      <c r="K4" s="119"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="111"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="111"/>
+      <c r="S4" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" s="111"/>
+      <c r="U4" s="111"/>
+      <c r="V4" s="111"/>
+      <c r="W4" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X4" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y4" s="111"/>
+      <c r="Z4" s="111"/>
+      <c r="AA4" s="111"/>
+      <c r="AB4" s="111"/>
     </row>
     <row r="5" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
@@ -2879,14 +2875,14 @@
       <c r="J5" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="129"/>
-      <c r="L5" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="N5" s="132" t="s">
+      <c r="K5" s="120"/>
+      <c r="L5" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="123" t="s">
         <v>32</v>
       </c>
       <c r="O5" s="14"/>
@@ -2917,60 +2913,60 @@
       <c r="AB5" s="14"/>
     </row>
     <row r="6" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="120" t="s">
+      <c r="A6" s="111" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="120" t="s">
+      <c r="B6" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="122" t="s">
+      <c r="E6" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="123">
+      <c r="F6" s="114">
         <v>2.7199074074074074E-3</v>
       </c>
-      <c r="G6" s="120" t="s">
+      <c r="G6" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="120"/>
-      <c r="I6" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="120" t="s">
+      <c r="H6" s="111"/>
+      <c r="I6" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="128"/>
-      <c r="L6" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6" s="139"/>
-      <c r="N6" s="131"/>
-      <c r="O6" s="120"/>
-      <c r="P6" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q6" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="R6" s="120"/>
-      <c r="S6" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T6" s="120"/>
-      <c r="U6" s="120"/>
-      <c r="V6" s="120"/>
-      <c r="W6" s="120"/>
-      <c r="X6" s="120"/>
-      <c r="Y6" s="120"/>
-      <c r="Z6" s="120"/>
-      <c r="AA6" s="120"/>
-      <c r="AB6" s="120"/>
+      <c r="K6" s="119"/>
+      <c r="L6" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M6" s="130"/>
+      <c r="N6" s="122"/>
+      <c r="O6" s="111"/>
+      <c r="P6" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="R6" s="111"/>
+      <c r="S6" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" s="111"/>
+      <c r="U6" s="111"/>
+      <c r="V6" s="111"/>
+      <c r="W6" s="111"/>
+      <c r="X6" s="111"/>
+      <c r="Y6" s="111"/>
+      <c r="Z6" s="111"/>
+      <c r="AA6" s="111"/>
+      <c r="AB6" s="111"/>
     </row>
     <row r="7" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
@@ -3001,14 +2997,14 @@
       <c r="J7" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="129"/>
-      <c r="L7" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="N7" s="132" t="s">
+      <c r="K7" s="120"/>
+      <c r="L7" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="123" t="s">
         <v>32</v>
       </c>
       <c r="O7" s="14" t="s">
@@ -3031,70 +3027,70 @@
       <c r="AB7" s="14"/>
     </row>
     <row r="8" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="120" t="s">
+      <c r="A8" s="111" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="120" t="s">
+      <c r="B8" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="111" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="122" t="s">
+      <c r="E8" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="123">
+      <c r="F8" s="114">
         <v>1.7476851851851852E-3</v>
       </c>
-      <c r="G8" s="120" t="s">
+      <c r="G8" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="122" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="120" t="s">
+      <c r="H8" s="113" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="128"/>
-      <c r="L8" s="137"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="131"/>
-      <c r="O8" s="120"/>
-      <c r="P8" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q8" s="120"/>
-      <c r="R8" s="120"/>
-      <c r="S8" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T8" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="U8" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="V8" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="W8" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X8" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y8" s="120"/>
-      <c r="Z8" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA8" s="120"/>
-      <c r="AB8" s="120" t="s">
+      <c r="K8" s="119"/>
+      <c r="L8" s="128"/>
+      <c r="M8" s="130"/>
+      <c r="N8" s="122"/>
+      <c r="O8" s="111"/>
+      <c r="P8" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="111"/>
+      <c r="S8" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="U8" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="V8" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="W8" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X8" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y8" s="111"/>
+      <c r="Z8" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA8" s="111"/>
+      <c r="AB8" s="111" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3127,14 +3123,14 @@
       <c r="J9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="129"/>
-      <c r="L9" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" s="132" t="s">
+      <c r="K9" s="120"/>
+      <c r="L9" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="123" t="s">
         <v>32</v>
       </c>
       <c r="O9" s="14" t="s">
@@ -3181,54 +3177,54 @@
       </c>
     </row>
     <row r="10" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="120" t="s">
+      <c r="B10" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="122" t="s">
+      <c r="E10" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="123">
+      <c r="F10" s="114">
         <v>3.3449074074074076E-3</v>
       </c>
-      <c r="G10" s="120" t="s">
+      <c r="G10" s="111" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="122" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="120"/>
-      <c r="J10" s="120" t="s">
+      <c r="H10" s="113" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="111"/>
+      <c r="J10" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="128"/>
-      <c r="L10" s="137"/>
-      <c r="M10" s="139"/>
-      <c r="N10" s="131"/>
-      <c r="O10" s="120"/>
-      <c r="P10" s="120"/>
-      <c r="Q10" s="120"/>
-      <c r="R10" s="120"/>
-      <c r="S10" s="120"/>
-      <c r="T10" s="120"/>
-      <c r="U10" s="120"/>
-      <c r="V10" s="120"/>
-      <c r="W10" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X10" s="120"/>
-      <c r="Y10" s="120"/>
-      <c r="Z10" s="120"/>
-      <c r="AA10" s="120"/>
-      <c r="AB10" s="120"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="128"/>
+      <c r="M10" s="130"/>
+      <c r="N10" s="122"/>
+      <c r="O10" s="111"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="111"/>
+      <c r="S10" s="111"/>
+      <c r="T10" s="111"/>
+      <c r="U10" s="111"/>
+      <c r="V10" s="111"/>
+      <c r="W10" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X10" s="111"/>
+      <c r="Y10" s="111"/>
+      <c r="Z10" s="111"/>
+      <c r="AA10" s="111"/>
+      <c r="AB10" s="111"/>
     </row>
     <row r="11" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
@@ -3257,10 +3253,10 @@
       <c r="J11" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="129"/>
-      <c r="L11" s="136"/>
-      <c r="M11" s="138"/>
-      <c r="N11" s="132"/>
+      <c r="K11" s="120"/>
+      <c r="L11" s="127"/>
+      <c r="M11" s="129"/>
+      <c r="N11" s="123"/>
       <c r="O11" s="14"/>
       <c r="P11" s="14"/>
       <c r="Q11" s="14"/>
@@ -3295,64 +3291,64 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="120" t="s">
+      <c r="A12" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="120" t="s">
+      <c r="B12" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="111" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="122" t="s">
+      <c r="E12" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="123">
+      <c r="F12" s="114">
         <v>2.7430555555555554E-3</v>
       </c>
-      <c r="G12" s="120" t="s">
+      <c r="G12" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="120"/>
-      <c r="I12" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="120" t="s">
+      <c r="H12" s="111"/>
+      <c r="I12" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="111" t="s">
         <v>56</v>
       </c>
-      <c r="K12" s="128"/>
-      <c r="L12" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="N12" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="O12" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="P12" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q12" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="R12" s="120"/>
-      <c r="S12" s="120"/>
-      <c r="T12" s="120"/>
-      <c r="U12" s="120"/>
-      <c r="V12" s="120"/>
-      <c r="W12" s="120"/>
-      <c r="X12" s="120"/>
-      <c r="Y12" s="120"/>
-      <c r="Z12" s="120"/>
-      <c r="AA12" s="120"/>
-      <c r="AB12" s="120"/>
+      <c r="K12" s="119"/>
+      <c r="L12" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="N12" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q12" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="R12" s="111"/>
+      <c r="S12" s="111"/>
+      <c r="T12" s="111"/>
+      <c r="U12" s="111"/>
+      <c r="V12" s="111"/>
+      <c r="W12" s="111"/>
+      <c r="X12" s="111"/>
+      <c r="Y12" s="111"/>
+      <c r="Z12" s="111"/>
+      <c r="AA12" s="111"/>
+      <c r="AB12" s="111"/>
     </row>
     <row r="13" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
@@ -3383,10 +3379,10 @@
       <c r="J13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="K13" s="129"/>
-      <c r="L13" s="136"/>
-      <c r="M13" s="138"/>
-      <c r="N13" s="132"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="127"/>
+      <c r="M13" s="129"/>
+      <c r="N13" s="123"/>
       <c r="O13" s="14"/>
       <c r="P13" s="14"/>
       <c r="Q13" s="14"/>
@@ -3407,50 +3403,50 @@
       <c r="AB13" s="14"/>
     </row>
     <row r="14" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="120" t="s">
+      <c r="A14" s="111" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="125" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="120" t="s">
+      <c r="B14" s="116" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="111" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="122" t="s">
+      <c r="E14" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="123">
+      <c r="F14" s="114">
         <v>1.7708333333333332E-3</v>
       </c>
-      <c r="G14" s="120" t="s">
+      <c r="G14" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="120"/>
-      <c r="I14" s="120"/>
-      <c r="J14" s="120" t="s">
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="128"/>
-      <c r="L14" s="137"/>
-      <c r="M14" s="139"/>
-      <c r="N14" s="131"/>
-      <c r="O14" s="120"/>
-      <c r="P14" s="120"/>
-      <c r="Q14" s="120"/>
-      <c r="R14" s="120"/>
-      <c r="S14" s="120"/>
-      <c r="T14" s="120"/>
-      <c r="U14" s="120"/>
-      <c r="V14" s="120"/>
-      <c r="W14" s="120"/>
-      <c r="X14" s="120"/>
-      <c r="Y14" s="120"/>
-      <c r="Z14" s="120"/>
-      <c r="AA14" s="120"/>
-      <c r="AB14" s="120" t="s">
+      <c r="K14" s="119"/>
+      <c r="L14" s="128"/>
+      <c r="M14" s="130"/>
+      <c r="N14" s="122"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="111"/>
+      <c r="S14" s="111"/>
+      <c r="T14" s="111"/>
+      <c r="U14" s="111"/>
+      <c r="V14" s="111"/>
+      <c r="W14" s="111"/>
+      <c r="X14" s="111"/>
+      <c r="Y14" s="111"/>
+      <c r="Z14" s="111"/>
+      <c r="AA14" s="111"/>
+      <c r="AB14" s="111" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3483,14 +3479,14 @@
       <c r="J15" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="129"/>
-      <c r="L15" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M15" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="N15" s="132" t="s">
+      <c r="K15" s="120"/>
+      <c r="L15" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="N15" s="123" t="s">
         <v>32</v>
       </c>
       <c r="O15" s="14"/>
@@ -3529,66 +3525,66 @@
       <c r="AB15" s="14"/>
     </row>
     <row r="16" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="120" t="s">
+      <c r="A16" s="111" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="120" t="s">
+      <c r="B16" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="111" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="122" t="s">
+      <c r="E16" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="123">
+      <c r="F16" s="114">
         <v>2.488425925925926E-3</v>
       </c>
-      <c r="G16" s="120" t="s">
+      <c r="G16" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="120"/>
-      <c r="I16" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" s="120" t="s">
+      <c r="H16" s="111"/>
+      <c r="I16" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="111" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="128"/>
-      <c r="L16" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M16" s="139"/>
-      <c r="N16" s="131"/>
-      <c r="O16" s="120"/>
-      <c r="P16" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q16" s="120"/>
-      <c r="R16" s="120"/>
-      <c r="S16" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T16" s="120"/>
-      <c r="U16" s="120"/>
-      <c r="V16" s="120"/>
-      <c r="W16" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X16" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y16" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z16" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA16" s="120"/>
-      <c r="AB16" s="120" t="s">
+      <c r="K16" s="119"/>
+      <c r="L16" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M16" s="130"/>
+      <c r="N16" s="122"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="111"/>
+      <c r="S16" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T16" s="111"/>
+      <c r="U16" s="111"/>
+      <c r="V16" s="111"/>
+      <c r="W16" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X16" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y16" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z16" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA16" s="111"/>
+      <c r="AB16" s="111" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3621,10 +3617,10 @@
       <c r="J17" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="129"/>
-      <c r="L17" s="136"/>
-      <c r="M17" s="138"/>
-      <c r="N17" s="132"/>
+      <c r="K17" s="120"/>
+      <c r="L17" s="127"/>
+      <c r="M17" s="129"/>
+      <c r="N17" s="123"/>
       <c r="O17" s="14"/>
       <c r="P17" s="14" t="s">
         <v>32</v>
@@ -3643,68 +3639,68 @@
       <c r="AB17" s="14"/>
     </row>
     <row r="18" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="120" t="s">
+      <c r="A18" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="120" t="s">
+      <c r="B18" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="111" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="122" t="s">
+      <c r="E18" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="123">
+      <c r="F18" s="114">
         <v>2.4305555555555556E-3</v>
       </c>
-      <c r="G18" s="120" t="s">
+      <c r="G18" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="120"/>
-      <c r="I18" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="120" t="s">
+      <c r="H18" s="111"/>
+      <c r="I18" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="111" t="s">
         <v>69</v>
       </c>
-      <c r="K18" s="128"/>
-      <c r="L18" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M18" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="N18" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="O18" s="120"/>
-      <c r="P18" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q18" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="R18" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="S18" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T18" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="U18" s="120"/>
-      <c r="V18" s="120"/>
-      <c r="W18" s="120"/>
-      <c r="X18" s="120"/>
-      <c r="Y18" s="120"/>
-      <c r="Z18" s="120"/>
-      <c r="AA18" s="120"/>
-      <c r="AB18" s="120"/>
+      <c r="K18" s="119"/>
+      <c r="L18" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="N18" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" s="111"/>
+      <c r="P18" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="R18" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="S18" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T18" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="U18" s="111"/>
+      <c r="V18" s="111"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="111"/>
+      <c r="Y18" s="111"/>
+      <c r="Z18" s="111"/>
+      <c r="AA18" s="111"/>
+      <c r="AB18" s="111"/>
     </row>
     <row r="19" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
@@ -3735,14 +3731,14 @@
       <c r="J19" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="K19" s="129"/>
-      <c r="L19" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M19" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="N19" s="132" t="s">
+      <c r="K19" s="120"/>
+      <c r="L19" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" s="123" t="s">
         <v>32</v>
       </c>
       <c r="O19" s="14" t="s">
@@ -3765,68 +3761,68 @@
       <c r="AB19" s="14"/>
     </row>
     <row r="20" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="120" t="s">
+      <c r="A20" s="111" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="120" t="s">
+      <c r="B20" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="111" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="122" t="s">
+      <c r="E20" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="123">
+      <c r="F20" s="114">
         <v>4.6874999999999998E-3</v>
       </c>
-      <c r="G20" s="120" t="s">
+      <c r="G20" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="H20" s="120"/>
-      <c r="I20" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" s="120" t="s">
+      <c r="H20" s="111"/>
+      <c r="I20" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="K20" s="128"/>
-      <c r="L20" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M20" s="139"/>
-      <c r="N20" s="131"/>
-      <c r="O20" s="120"/>
-      <c r="P20" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q20" s="120"/>
-      <c r="R20" s="120"/>
-      <c r="S20" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T20" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="U20" s="120"/>
-      <c r="V20" s="120"/>
-      <c r="W20" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X20" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y20" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z20" s="120"/>
-      <c r="AA20" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB20" s="120" t="s">
+      <c r="K20" s="119"/>
+      <c r="L20" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" s="130"/>
+      <c r="N20" s="122"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="111"/>
+      <c r="S20" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T20" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="U20" s="111"/>
+      <c r="V20" s="111"/>
+      <c r="W20" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X20" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y20" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z20" s="111"/>
+      <c r="AA20" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB20" s="111" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3857,10 +3853,10 @@
       <c r="J21" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="K21" s="129"/>
-      <c r="L21" s="136"/>
-      <c r="M21" s="138"/>
-      <c r="N21" s="132"/>
+      <c r="K21" s="120"/>
+      <c r="L21" s="127"/>
+      <c r="M21" s="129"/>
+      <c r="N21" s="123"/>
       <c r="O21" s="14"/>
       <c r="P21" s="14"/>
       <c r="Q21" s="14"/>
@@ -3879,82 +3875,82 @@
       <c r="AB21" s="14"/>
     </row>
     <row r="22" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="120" t="s">
+      <c r="A22" s="111" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="120" t="s">
+      <c r="B22" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="111" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="122" t="s">
+      <c r="E22" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="123">
+      <c r="F22" s="114">
         <v>2.5810185185185185E-3</v>
       </c>
-      <c r="G22" s="120" t="s">
+      <c r="G22" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="H22" s="120"/>
-      <c r="I22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="120" t="s">
+      <c r="H22" s="111"/>
+      <c r="I22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="111" t="s">
         <v>56</v>
       </c>
-      <c r="K22" s="128"/>
-      <c r="L22" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M22" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="N22" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="O22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="P22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q22" s="120"/>
-      <c r="R22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="S22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="U22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="V22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="W22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA22" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB22" s="120" t="s">
+      <c r="K22" s="119"/>
+      <c r="L22" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M22" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="U22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="V22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="W22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA22" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB22" s="111" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3987,10 +3983,10 @@
       <c r="J23" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K23" s="129"/>
-      <c r="L23" s="136"/>
-      <c r="M23" s="138"/>
-      <c r="N23" s="132"/>
+      <c r="K23" s="120"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="129"/>
+      <c r="N23" s="123"/>
       <c r="O23" s="14"/>
       <c r="P23" s="14" t="s">
         <v>32</v>
@@ -4023,66 +4019,66 @@
       <c r="AB23" s="14"/>
     </row>
     <row r="24" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="120" t="s">
+      <c r="A24" s="111" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="126"/>
-      <c r="D24" s="120" t="s">
+      <c r="B24" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="117"/>
+      <c r="D24" s="111" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="122" t="s">
+      <c r="E24" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="123">
+      <c r="F24" s="114">
         <v>3.8541666666666668E-3</v>
       </c>
-      <c r="G24" s="120" t="s">
+      <c r="G24" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="120"/>
-      <c r="I24" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J24" s="120" t="s">
+      <c r="H24" s="111"/>
+      <c r="I24" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="111" t="s">
         <v>84</v>
       </c>
-      <c r="K24" s="128"/>
-      <c r="L24" s="137"/>
-      <c r="M24" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="N24" s="131"/>
-      <c r="O24" s="120"/>
-      <c r="P24" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q24" s="120"/>
-      <c r="R24" s="120"/>
-      <c r="S24" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T24" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="U24" s="120"/>
-      <c r="V24" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="W24" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X24" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y24" s="120"/>
-      <c r="Z24" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA24" s="120"/>
-      <c r="AB24" s="120"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="122"/>
+      <c r="O24" s="111"/>
+      <c r="P24" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="111"/>
+      <c r="S24" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T24" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="U24" s="111"/>
+      <c r="V24" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="W24" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X24" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y24" s="111"/>
+      <c r="Z24" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA24" s="111"/>
+      <c r="AB24" s="111"/>
     </row>
     <row r="25" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
@@ -4115,11 +4111,11 @@
       <c r="J25" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="K25" s="129"/>
-      <c r="L25" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M25" s="138"/>
+      <c r="K25" s="120"/>
+      <c r="L25" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M25" s="129"/>
       <c r="N25" s="12"/>
       <c r="O25" s="14" t="s">
         <v>32</v>
@@ -4155,54 +4151,54 @@
       <c r="AB25" s="14"/>
     </row>
     <row r="26" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="120" t="s">
+      <c r="A26" s="111" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="120" t="s">
+      <c r="B26" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="122" t="s">
+      <c r="E26" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="123">
+      <c r="F26" s="114">
         <v>2.650462962962963E-3</v>
       </c>
-      <c r="G26" s="120" t="s">
+      <c r="G26" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="120"/>
-      <c r="I26" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26" s="120" t="s">
+      <c r="H26" s="111"/>
+      <c r="I26" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="128"/>
-      <c r="L26" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" s="139"/>
-      <c r="N26" s="124"/>
-      <c r="O26" s="124"/>
-      <c r="P26" s="124"/>
-      <c r="Q26" s="124"/>
-      <c r="R26" s="124"/>
-      <c r="S26" s="124"/>
-      <c r="T26" s="124"/>
-      <c r="U26" s="124"/>
-      <c r="V26" s="124"/>
-      <c r="W26" s="124"/>
-      <c r="X26" s="124"/>
-      <c r="Y26" s="124"/>
-      <c r="Z26" s="124"/>
-      <c r="AA26" s="124"/>
-      <c r="AB26" s="124"/>
+      <c r="K26" s="119"/>
+      <c r="L26" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M26" s="130"/>
+      <c r="N26" s="115"/>
+      <c r="O26" s="115"/>
+      <c r="P26" s="115"/>
+      <c r="Q26" s="115"/>
+      <c r="R26" s="115"/>
+      <c r="S26" s="115"/>
+      <c r="T26" s="115"/>
+      <c r="U26" s="115"/>
+      <c r="V26" s="115"/>
+      <c r="W26" s="115"/>
+      <c r="X26" s="115"/>
+      <c r="Y26" s="115"/>
+      <c r="Z26" s="115"/>
+      <c r="AA26" s="115"/>
+      <c r="AB26" s="115"/>
     </row>
     <row r="27" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="14" t="s">
@@ -4235,12 +4231,12 @@
       <c r="J27" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="K27" s="129"/>
-      <c r="L27" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M27" s="140"/>
-      <c r="N27" s="132"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M27" s="131"/>
+      <c r="N27" s="123"/>
       <c r="O27" s="14"/>
       <c r="P27" s="14" t="s">
         <v>32</v>
@@ -4259,62 +4255,62 @@
       <c r="AB27" s="14"/>
     </row>
     <row r="28" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="120" t="s">
+      <c r="A28" s="111" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="120" t="s">
+      <c r="B28" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="122" t="s">
+      <c r="E28" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="123">
+      <c r="F28" s="114">
         <v>2.8587962962962963E-3</v>
       </c>
-      <c r="G28" s="120" t="s">
+      <c r="G28" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="120"/>
-      <c r="I28" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" s="120" t="s">
+      <c r="H28" s="111"/>
+      <c r="I28" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="111" t="s">
         <v>56</v>
       </c>
-      <c r="K28" s="128"/>
-      <c r="L28" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M28" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="N28" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="O28" s="120"/>
-      <c r="P28" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q28" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="R28" s="120"/>
-      <c r="S28" s="120"/>
-      <c r="T28" s="120"/>
-      <c r="U28" s="120"/>
-      <c r="V28" s="120"/>
-      <c r="W28" s="120"/>
-      <c r="X28" s="120"/>
-      <c r="Y28" s="120"/>
-      <c r="Z28" s="120"/>
-      <c r="AA28" s="120"/>
-      <c r="AB28" s="120"/>
+      <c r="K28" s="119"/>
+      <c r="L28" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M28" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="O28" s="111"/>
+      <c r="P28" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q28" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" s="111"/>
+      <c r="S28" s="111"/>
+      <c r="T28" s="111"/>
+      <c r="U28" s="111"/>
+      <c r="V28" s="111"/>
+      <c r="W28" s="111"/>
+      <c r="X28" s="111"/>
+      <c r="Y28" s="111"/>
+      <c r="Z28" s="111"/>
+      <c r="AA28" s="111"/>
+      <c r="AB28" s="111"/>
     </row>
     <row r="29" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="14" t="s">
@@ -4345,12 +4341,12 @@
       <c r="J29" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K29" s="129"/>
-      <c r="L29" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M29" s="138"/>
-      <c r="N29" s="132"/>
+      <c r="K29" s="120"/>
+      <c r="L29" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M29" s="129"/>
+      <c r="N29" s="123"/>
       <c r="O29" s="14"/>
       <c r="P29" s="14" t="s">
         <v>32</v>
@@ -4389,82 +4385,82 @@
       <c r="AB29" s="14"/>
     </row>
     <row r="30" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="120" t="s">
+      <c r="A30" s="111" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="120" t="s">
+      <c r="B30" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="111" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="122" t="s">
+      <c r="E30" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="123">
+      <c r="F30" s="114">
         <v>3.5995370370370369E-3</v>
       </c>
-      <c r="G30" s="120" t="s">
+      <c r="G30" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="H30" s="120"/>
-      <c r="I30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J30" s="120" t="s">
+      <c r="H30" s="111"/>
+      <c r="I30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="K30" s="128"/>
-      <c r="L30" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M30" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="N30" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="O30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="P30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="R30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="S30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="U30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="V30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="W30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z30" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA30" s="120"/>
-      <c r="AB30" s="120"/>
+      <c r="K30" s="119"/>
+      <c r="L30" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M30" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="O30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="P30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="S30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="U30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="V30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="W30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z30" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA30" s="111"/>
+      <c r="AB30" s="111"/>
     </row>
     <row r="31" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
@@ -4495,10 +4491,10 @@
       <c r="J31" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="K31" s="129"/>
-      <c r="L31" s="136"/>
-      <c r="M31" s="138"/>
-      <c r="N31" s="132"/>
+      <c r="K31" s="120"/>
+      <c r="L31" s="127"/>
+      <c r="M31" s="129"/>
+      <c r="N31" s="123"/>
       <c r="O31" s="14"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
@@ -4519,66 +4515,66 @@
       </c>
     </row>
     <row r="32" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="120" t="s">
+      <c r="A32" s="111" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="120" t="s">
+      <c r="B32" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="111" t="s">
         <v>98</v>
       </c>
-      <c r="E32" s="122" t="s">
+      <c r="E32" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="123">
+      <c r="F32" s="114">
         <v>3.2291666666666666E-3</v>
       </c>
-      <c r="G32" s="120" t="s">
+      <c r="G32" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="H32" s="120"/>
-      <c r="I32" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J32" s="120" t="s">
+      <c r="H32" s="111"/>
+      <c r="I32" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J32" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="K32" s="128"/>
-      <c r="L32" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M32" s="139"/>
-      <c r="N32" s="131"/>
-      <c r="O32" s="120"/>
-      <c r="P32" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q32" s="120"/>
-      <c r="R32" s="120"/>
-      <c r="S32" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T32" s="120"/>
-      <c r="U32" s="120"/>
-      <c r="V32" s="120"/>
-      <c r="W32" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X32" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y32" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z32" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA32" s="120"/>
-      <c r="AB32" s="120"/>
+      <c r="K32" s="119"/>
+      <c r="L32" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M32" s="130"/>
+      <c r="N32" s="122"/>
+      <c r="O32" s="111"/>
+      <c r="P32" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q32" s="111"/>
+      <c r="R32" s="111"/>
+      <c r="S32" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T32" s="111"/>
+      <c r="U32" s="111"/>
+      <c r="V32" s="111"/>
+      <c r="W32" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X32" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y32" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z32" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA32" s="111"/>
+      <c r="AB32" s="111"/>
     </row>
     <row r="33" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
@@ -4609,14 +4605,14 @@
       <c r="J33" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="K33" s="129"/>
-      <c r="L33" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M33" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="N33" s="132" t="s">
+      <c r="K33" s="120"/>
+      <c r="L33" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M33" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33" s="123" t="s">
         <v>32</v>
       </c>
       <c r="O33" s="14" t="s">
@@ -4653,66 +4649,66 @@
       <c r="AB33" s="14"/>
     </row>
     <row r="34" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="120" t="s">
+      <c r="A34" s="111" t="s">
         <v>101</v>
       </c>
-      <c r="B34" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="120" t="s">
+      <c r="B34" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="111" t="s">
         <v>102</v>
       </c>
-      <c r="E34" s="122" t="s">
+      <c r="E34" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="123">
+      <c r="F34" s="114">
         <v>4.1319444444444442E-3</v>
       </c>
-      <c r="G34" s="120" t="s">
+      <c r="G34" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="H34" s="120"/>
-      <c r="I34" s="120"/>
-      <c r="J34" s="120" t="s">
+      <c r="H34" s="111"/>
+      <c r="I34" s="111"/>
+      <c r="J34" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="128"/>
-      <c r="L34" s="137"/>
-      <c r="M34" s="139"/>
-      <c r="N34" s="131"/>
-      <c r="O34" s="120"/>
-      <c r="P34" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q34" s="120"/>
-      <c r="R34" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="S34" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T34" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="U34" s="120"/>
-      <c r="V34" s="120"/>
-      <c r="W34" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X34" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y34" s="120"/>
-      <c r="Z34" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA34" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB34" s="120"/>
+      <c r="K34" s="119"/>
+      <c r="L34" s="128"/>
+      <c r="M34" s="130"/>
+      <c r="N34" s="122"/>
+      <c r="O34" s="111"/>
+      <c r="P34" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q34" s="111"/>
+      <c r="R34" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="S34" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T34" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="U34" s="111"/>
+      <c r="V34" s="111"/>
+      <c r="W34" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X34" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y34" s="111"/>
+      <c r="Z34" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA34" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB34" s="111"/>
     </row>
     <row r="35" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="s">
@@ -4743,12 +4739,12 @@
       <c r="J35" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="K35" s="129"/>
-      <c r="L35" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M35" s="138"/>
-      <c r="N35" s="132"/>
+      <c r="K35" s="120"/>
+      <c r="L35" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M35" s="129"/>
+      <c r="N35" s="123"/>
       <c r="O35" s="14"/>
       <c r="P35" s="14" t="s">
         <v>32</v>
@@ -4781,58 +4777,58 @@
       <c r="AB35" s="14"/>
     </row>
     <row r="36" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="120" t="s">
+      <c r="A36" s="111" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="120" t="s">
+      <c r="B36" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="E36" s="122" t="s">
+      <c r="E36" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="123">
+      <c r="F36" s="114">
         <v>2.4305555555555556E-3</v>
       </c>
-      <c r="G36" s="120" t="s">
+      <c r="G36" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="H36" s="120"/>
-      <c r="I36" s="120"/>
-      <c r="J36" s="120" t="s">
+      <c r="H36" s="111"/>
+      <c r="I36" s="111"/>
+      <c r="J36" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="K36" s="128"/>
-      <c r="L36" s="137"/>
-      <c r="M36" s="139"/>
-      <c r="N36" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="O36" s="120"/>
-      <c r="P36" s="120"/>
-      <c r="Q36" s="120"/>
-      <c r="R36" s="120"/>
-      <c r="S36" s="120"/>
-      <c r="T36" s="120"/>
-      <c r="U36" s="120"/>
-      <c r="V36" s="120"/>
-      <c r="W36" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X36" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y36" s="120"/>
-      <c r="Z36" s="120"/>
-      <c r="AA36" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB36" s="120"/>
+      <c r="K36" s="119"/>
+      <c r="L36" s="128"/>
+      <c r="M36" s="130"/>
+      <c r="N36" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="O36" s="111"/>
+      <c r="P36" s="111"/>
+      <c r="Q36" s="111"/>
+      <c r="R36" s="111"/>
+      <c r="S36" s="111"/>
+      <c r="T36" s="111"/>
+      <c r="U36" s="111"/>
+      <c r="V36" s="111"/>
+      <c r="W36" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X36" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y36" s="111"/>
+      <c r="Z36" s="111"/>
+      <c r="AA36" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB36" s="111"/>
     </row>
     <row r="37" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
@@ -4863,14 +4859,14 @@
       <c r="J37" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="K37" s="129"/>
-      <c r="L37" s="136" t="s">
-        <v>32</v>
-      </c>
-      <c r="M37" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="N37" s="132" t="s">
+      <c r="K37" s="120"/>
+      <c r="L37" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="M37" s="131" t="s">
+        <v>32</v>
+      </c>
+      <c r="N37" s="123" t="s">
         <v>32</v>
       </c>
       <c r="O37" s="14"/>
@@ -4901,62 +4897,62 @@
       <c r="AB37" s="14"/>
     </row>
     <row r="38" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="120" t="s">
+      <c r="A38" s="111" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="120" t="s">
+      <c r="B38" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="111" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="122" t="s">
+      <c r="E38" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F38" s="123">
+      <c r="F38" s="114">
         <v>2.6041666666666665E-3</v>
       </c>
-      <c r="G38" s="120" t="s">
+      <c r="G38" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="H38" s="120"/>
-      <c r="I38" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J38" s="120" t="s">
+      <c r="H38" s="111"/>
+      <c r="I38" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="K38" s="128"/>
-      <c r="L38" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M38" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="N38" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="O38" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="P38" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q38" s="120"/>
-      <c r="R38" s="120"/>
-      <c r="S38" s="120"/>
-      <c r="T38" s="120"/>
-      <c r="U38" s="120"/>
-      <c r="V38" s="120"/>
-      <c r="W38" s="120"/>
-      <c r="X38" s="120"/>
-      <c r="Y38" s="120"/>
-      <c r="Z38" s="120"/>
-      <c r="AA38" s="120"/>
-      <c r="AB38" s="120"/>
+      <c r="K38" s="119"/>
+      <c r="L38" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M38" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="N38" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="O38" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="P38" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q38" s="111"/>
+      <c r="R38" s="111"/>
+      <c r="S38" s="111"/>
+      <c r="T38" s="111"/>
+      <c r="U38" s="111"/>
+      <c r="V38" s="111"/>
+      <c r="W38" s="111"/>
+      <c r="X38" s="111"/>
+      <c r="Y38" s="111"/>
+      <c r="Z38" s="111"/>
+      <c r="AA38" s="111"/>
+      <c r="AB38" s="111"/>
     </row>
     <row r="39" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="14" t="s">
@@ -4985,10 +4981,10 @@
       <c r="J39" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="K39" s="129"/>
-      <c r="L39" s="136"/>
-      <c r="M39" s="138"/>
-      <c r="N39" s="132"/>
+      <c r="K39" s="120"/>
+      <c r="L39" s="127"/>
+      <c r="M39" s="129"/>
+      <c r="N39" s="123"/>
       <c r="O39" s="14"/>
       <c r="P39" s="14"/>
       <c r="Q39" s="14"/>
@@ -5009,52 +5005,52 @@
       <c r="AB39" s="14"/>
     </row>
     <row r="40" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="120" t="s">
+      <c r="A40" s="111" t="s">
         <v>113</v>
       </c>
-      <c r="B40" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="120" t="s">
+      <c r="B40" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="111" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="122" t="s">
+      <c r="E40" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F40" s="123">
+      <c r="F40" s="114">
         <v>2.0023148148148148E-3</v>
       </c>
-      <c r="G40" s="120" t="s">
+      <c r="G40" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="H40" s="120"/>
-      <c r="I40" s="120"/>
-      <c r="J40" s="120" t="s">
+      <c r="H40" s="111"/>
+      <c r="I40" s="111"/>
+      <c r="J40" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="K40" s="128"/>
-      <c r="L40" s="137"/>
-      <c r="M40" s="139"/>
-      <c r="N40" s="131"/>
-      <c r="O40" s="120"/>
-      <c r="P40" s="120"/>
-      <c r="Q40" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="R40" s="120"/>
-      <c r="S40" s="120"/>
-      <c r="T40" s="120"/>
-      <c r="U40" s="120"/>
-      <c r="V40" s="120"/>
-      <c r="W40" s="120"/>
-      <c r="X40" s="120"/>
-      <c r="Y40" s="120"/>
-      <c r="Z40" s="120"/>
-      <c r="AA40" s="120"/>
-      <c r="AB40" s="120"/>
+      <c r="K40" s="119"/>
+      <c r="L40" s="128"/>
+      <c r="M40" s="130"/>
+      <c r="N40" s="122"/>
+      <c r="O40" s="111"/>
+      <c r="P40" s="111"/>
+      <c r="Q40" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="R40" s="111"/>
+      <c r="S40" s="111"/>
+      <c r="T40" s="111"/>
+      <c r="U40" s="111"/>
+      <c r="V40" s="111"/>
+      <c r="W40" s="111"/>
+      <c r="X40" s="111"/>
+      <c r="Y40" s="111"/>
+      <c r="Z40" s="111"/>
+      <c r="AA40" s="111"/>
+      <c r="AB40" s="111"/>
     </row>
     <row r="41" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="14" t="s">
@@ -5085,10 +5081,10 @@
       <c r="J41" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="K41" s="129"/>
-      <c r="L41" s="136"/>
-      <c r="M41" s="138"/>
-      <c r="N41" s="132"/>
+      <c r="K41" s="120"/>
+      <c r="L41" s="127"/>
+      <c r="M41" s="129"/>
+      <c r="N41" s="123"/>
       <c r="O41" s="14"/>
       <c r="P41" s="14" t="s">
         <v>32</v>
@@ -5111,64 +5107,64 @@
       <c r="AB41" s="14"/>
     </row>
     <row r="42" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="120" t="s">
+      <c r="A42" s="111" t="s">
         <v>116</v>
       </c>
-      <c r="B42" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="120" t="s">
+      <c r="B42" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="111" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="122" t="s">
+      <c r="E42" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F42" s="123">
+      <c r="F42" s="114">
         <v>2.2569444444444442E-3</v>
       </c>
-      <c r="G42" s="120" t="s">
+      <c r="G42" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="H42" s="120"/>
-      <c r="I42" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J42" s="120" t="s">
+      <c r="H42" s="111"/>
+      <c r="I42" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="K42" s="128"/>
-      <c r="L42" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M42" s="139"/>
-      <c r="N42" s="131"/>
-      <c r="O42" s="120"/>
-      <c r="P42" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q42" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="R42" s="120"/>
-      <c r="S42" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T42" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="U42" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="V42" s="120"/>
-      <c r="W42" s="120"/>
-      <c r="X42" s="120"/>
-      <c r="Y42" s="120"/>
-      <c r="Z42" s="120"/>
-      <c r="AA42" s="120"/>
-      <c r="AB42" s="120"/>
+      <c r="K42" s="119"/>
+      <c r="L42" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M42" s="130"/>
+      <c r="N42" s="122"/>
+      <c r="O42" s="111"/>
+      <c r="P42" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q42" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="R42" s="111"/>
+      <c r="S42" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T42" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="U42" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="V42" s="111"/>
+      <c r="W42" s="111"/>
+      <c r="X42" s="111"/>
+      <c r="Y42" s="111"/>
+      <c r="Z42" s="111"/>
+      <c r="AA42" s="111"/>
+      <c r="AB42" s="111"/>
     </row>
     <row r="43" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="14" t="s">
@@ -5197,10 +5193,10 @@
       <c r="J43" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="K43" s="129"/>
-      <c r="L43" s="136"/>
-      <c r="M43" s="138"/>
-      <c r="N43" s="132"/>
+      <c r="K43" s="120"/>
+      <c r="L43" s="127"/>
+      <c r="M43" s="129"/>
+      <c r="N43" s="123"/>
       <c r="O43" s="14"/>
       <c r="P43" s="14" t="s">
         <v>32</v>
@@ -5221,62 +5217,62 @@
       <c r="AB43" s="14"/>
     </row>
     <row r="44" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="120" t="s">
+      <c r="A44" s="111" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="120" t="s">
+      <c r="B44" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="111" t="s">
         <v>53</v>
       </c>
-      <c r="E44" s="122" t="s">
+      <c r="E44" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F44" s="123">
+      <c r="F44" s="114">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="G44" s="120" t="s">
+      <c r="G44" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="H44" s="120"/>
-      <c r="I44" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J44" s="120" t="s">
+      <c r="H44" s="111"/>
+      <c r="I44" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J44" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="K44" s="128"/>
-      <c r="L44" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M44" s="139"/>
-      <c r="N44" s="131"/>
-      <c r="O44" s="120"/>
-      <c r="P44" s="120"/>
-      <c r="Q44" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="R44" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="S44" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T44" s="120"/>
-      <c r="U44" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="V44" s="120"/>
-      <c r="W44" s="120"/>
-      <c r="X44" s="120"/>
-      <c r="Y44" s="120"/>
-      <c r="Z44" s="120"/>
-      <c r="AA44" s="120"/>
-      <c r="AB44" s="120"/>
+      <c r="K44" s="119"/>
+      <c r="L44" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M44" s="130"/>
+      <c r="N44" s="122"/>
+      <c r="O44" s="111"/>
+      <c r="P44" s="111"/>
+      <c r="Q44" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="R44" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="S44" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T44" s="111"/>
+      <c r="U44" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="V44" s="111"/>
+      <c r="W44" s="111"/>
+      <c r="X44" s="111"/>
+      <c r="Y44" s="111"/>
+      <c r="Z44" s="111"/>
+      <c r="AA44" s="111"/>
+      <c r="AB44" s="111"/>
     </row>
     <row r="45" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
@@ -5305,12 +5301,12 @@
       <c r="J45" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K45" s="129" t="s">
-        <v>32</v>
-      </c>
-      <c r="L45" s="136"/>
-      <c r="M45" s="138"/>
-      <c r="N45" s="132"/>
+      <c r="K45" s="120" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" s="127"/>
+      <c r="M45" s="129"/>
+      <c r="N45" s="123"/>
       <c r="O45" s="14"/>
       <c r="P45" s="14"/>
       <c r="Q45" s="14"/>
@@ -5327,84 +5323,84 @@
       <c r="AB45" s="14"/>
     </row>
     <row r="46" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="120" t="s">
+      <c r="A46" s="111" t="s">
         <v>123</v>
       </c>
-      <c r="B46" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="120" t="s">
+      <c r="B46" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="111" t="s">
         <v>93</v>
       </c>
-      <c r="E46" s="122" t="s">
+      <c r="E46" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F46" s="123">
+      <c r="F46" s="114">
         <v>3.3217592592592591E-3</v>
       </c>
-      <c r="G46" s="120" t="s">
+      <c r="G46" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="H46" s="120"/>
-      <c r="I46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J46" s="120" t="s">
+      <c r="H46" s="111"/>
+      <c r="I46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J46" s="111" t="s">
         <v>33</v>
       </c>
-      <c r="K46" s="128"/>
-      <c r="L46" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M46" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="N46" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="O46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="P46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="R46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="S46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="U46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="V46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="W46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA46" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB46" s="120" t="s">
+      <c r="K46" s="119"/>
+      <c r="L46" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M46" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="N46" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="O46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="P46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="R46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="S46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="U46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="V46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="W46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA46" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB46" s="111" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5429,10 +5425,10 @@
       <c r="J47" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="K47" s="129"/>
-      <c r="L47" s="136"/>
-      <c r="M47" s="138"/>
-      <c r="N47" s="132"/>
+      <c r="K47" s="120"/>
+      <c r="L47" s="127"/>
+      <c r="M47" s="129"/>
+      <c r="N47" s="123"/>
       <c r="O47" s="14"/>
       <c r="P47" s="14"/>
       <c r="Q47" s="14"/>
@@ -5451,72 +5447,72 @@
       <c r="AB47" s="14"/>
     </row>
     <row r="48" spans="1:28" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="120" t="s">
+      <c r="A48" s="111" t="s">
         <v>127</v>
       </c>
-      <c r="B48" s="121" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="121" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="120" t="s">
+      <c r="B48" s="112" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="112" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="111" t="s">
         <v>128</v>
       </c>
-      <c r="E48" s="122" t="s">
+      <c r="E48" s="113" t="s">
         <v>30</v>
       </c>
-      <c r="F48" s="123">
+      <c r="F48" s="114">
         <v>2.0949074074074073E-3</v>
       </c>
-      <c r="G48" s="120" t="s">
+      <c r="G48" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="H48" s="120"/>
-      <c r="I48" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="J48" s="120" t="s">
+      <c r="H48" s="111"/>
+      <c r="I48" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" s="111" t="s">
         <v>56</v>
       </c>
-      <c r="K48" s="128"/>
-      <c r="L48" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="M48" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="N48" s="131" t="s">
-        <v>32</v>
-      </c>
-      <c r="O48" s="120"/>
-      <c r="P48" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q48" s="120"/>
-      <c r="R48" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="S48" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="T48" s="120"/>
-      <c r="U48" s="120"/>
-      <c r="V48" s="120"/>
-      <c r="W48" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="X48" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y48" s="120"/>
-      <c r="Z48" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA48" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB48" s="120" t="s">
+      <c r="K48" s="119"/>
+      <c r="L48" s="128" t="s">
+        <v>32</v>
+      </c>
+      <c r="M48" s="132" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="O48" s="111"/>
+      <c r="P48" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q48" s="111"/>
+      <c r="R48" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="S48" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="T48" s="111"/>
+      <c r="U48" s="111"/>
+      <c r="V48" s="111"/>
+      <c r="W48" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="X48" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y48" s="111"/>
+      <c r="Z48" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA48" s="111" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB48" s="111" t="s">
         <v>32</v>
       </c>
     </row>
@@ -10932,7 +10928,7 @@
         <v>193</v>
       </c>
       <c r="K20" s="62">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="L20" s="14"/>
     </row>
@@ -13647,14 +13643,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="137" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="113"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="138"/>
+      <c r="F1" s="139"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="81" t="s">
@@ -13957,14 +13953,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="114" t="s">
+      <c r="A17" s="140" t="s">
         <v>253</v>
       </c>
-      <c r="B17" s="115"/>
-      <c r="C17" s="115"/>
-      <c r="D17" s="115"/>
-      <c r="E17" s="115"/>
-      <c r="F17" s="116"/>
+      <c r="B17" s="141"/>
+      <c r="C17" s="141"/>
+      <c r="D17" s="141"/>
+      <c r="E17" s="141"/>
+      <c r="F17" s="142"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="89">
@@ -14304,14 +14300,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="143" t="s">
         <v>272</v>
       </c>
-      <c r="B1" s="118"/>
-      <c r="C1" s="118"/>
-      <c r="D1" s="118"/>
-      <c r="E1" s="118"/>
-      <c r="F1" s="119"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="145"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="69" t="s">

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B3C77D9-6CE3-EA46-81D1-EBEC0FD62205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2397D385-E139-0742-8329-FE050BA22B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4760" yWindow="4580" windowWidth="27380" windowHeight="16920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4760" yWindow="4580" windowWidth="27380" windowHeight="16920" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="275">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -696,9 +696,6 @@
     <t>Cortez the Killer</t>
   </si>
   <si>
-    <t>Jim</t>
-  </si>
-  <si>
     <t>Down By the River replacement</t>
   </si>
   <si>
@@ -709,9 +706,6 @@
   </si>
   <si>
     <t>Cake</t>
-  </si>
-  <si>
-    <t>Drew / Matt</t>
   </si>
   <si>
     <t>Matt will sing</t>
@@ -902,6 +896,15 @@
   <si>
     <t>2026-05-16
 Fat Shallot</t>
+  </si>
+  <si>
+    <t>Honest Mistake</t>
+  </si>
+  <si>
+    <t>The Bravery</t>
+  </si>
+  <si>
+    <t>Drea</t>
   </si>
 </sst>
 </file>
@@ -2691,7 +2694,7 @@
         <v>11</v>
       </c>
       <c r="L2" s="136" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="M2" s="135" t="s">
         <v>12</v>
@@ -2848,7 +2851,7 @@
     </row>
     <row r="5" spans="1:28" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B5" s="48" t="s">
         <v>2</v>
@@ -5674,7 +5677,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -5684,7 +5687,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -5696,7 +5699,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -5704,7 +5707,7 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>104</v>
@@ -5936,7 +5939,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C15" s="37" t="s">
         <v>2</v>
@@ -6042,7 +6045,7 @@
     <row r="21" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="33"/>
       <c r="B21" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C21" s="35"/>
       <c r="D21" s="35"/>
@@ -6106,7 +6109,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -6116,7 +6119,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -6128,7 +6131,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -6345,7 +6348,7 @@
     <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
       <c r="B14" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C14" s="35"/>
       <c r="D14" s="35"/>
@@ -6397,7 +6400,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -6407,7 +6410,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -6419,7 +6422,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -6810,7 +6813,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C22" s="37" t="s">
         <v>2</v>
@@ -7054,7 +7057,7 @@
     <row r="35" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A35" s="33"/>
       <c r="B35" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C35" s="35"/>
       <c r="D35" s="35"/>
@@ -7146,7 +7149,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -7156,7 +7159,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -7168,7 +7171,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -7447,7 +7450,7 @@
     <row r="17" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33"/>
       <c r="B17" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C17" s="35"/>
       <c r="D17" s="35"/>
@@ -7505,7 +7508,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -7515,7 +7518,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -7527,7 +7530,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -7815,7 +7818,7 @@
     <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="33"/>
       <c r="B18" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
@@ -7870,7 +7873,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -7880,7 +7883,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -7892,7 +7895,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -8281,7 +8284,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C22" s="37" t="s">
         <v>2</v>
@@ -8467,7 +8470,7 @@
     <row r="32" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="33"/>
       <c r="B32" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C32" s="35"/>
       <c r="D32" s="35"/>
@@ -8551,7 +8554,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -8561,7 +8564,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -8573,7 +8576,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -8960,7 +8963,7 @@
     </row>
     <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="39" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>103</v>
@@ -8989,7 +8992,7 @@
     <row r="24" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="33"/>
       <c r="B24" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C24" s="35"/>
       <c r="D24" s="35"/>
@@ -9059,7 +9062,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -9069,7 +9072,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -9081,7 +9084,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -9312,7 +9315,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C14" s="37" t="s">
         <v>2</v>
@@ -9349,7 +9352,7 @@
     </row>
     <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="39" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>103</v>
@@ -9378,7 +9381,7 @@
     <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="33"/>
       <c r="B18" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C18" s="35"/>
       <c r="D18" s="35"/>
@@ -9437,7 +9440,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -9447,7 +9450,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -9459,7 +9462,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -9694,7 +9697,7 @@
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C15" s="35"/>
       <c r="D15" s="35"/>
@@ -9746,7 +9749,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -9756,7 +9759,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -9768,7 +9771,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -9899,7 +9902,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C9" s="37" t="s">
         <v>2</v>
@@ -10310,7 +10313,7 @@
     <row r="30" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="33"/>
       <c r="B30" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C30" s="35"/>
       <c r="D30" s="35"/>
@@ -11047,7 +11050,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -11057,7 +11060,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -11069,7 +11072,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -11200,7 +11203,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C9" s="37" t="s">
         <v>2</v>
@@ -11507,7 +11510,7 @@
     <row r="25" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33"/>
       <c r="B25" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C25" s="35"/>
       <c r="D25" s="35"/>
@@ -11579,7 +11582,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -11589,7 +11592,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -11601,7 +11604,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -11839,7 +11842,7 @@
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C15" s="35"/>
       <c r="D15" s="35"/>
@@ -11893,7 +11896,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -11903,7 +11906,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -11915,7 +11918,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -12046,7 +12049,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C9" s="37" t="s">
         <v>2</v>
@@ -12251,7 +12254,7 @@
     <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33"/>
       <c r="B20" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C20" s="35"/>
       <c r="D20" s="35"/>
@@ -12314,7 +12317,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -12324,7 +12327,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -12336,7 +12339,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -12575,7 +12578,7 @@
     <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C15" s="35"/>
       <c r="D15" s="35"/>
@@ -12629,7 +12632,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -12639,7 +12642,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -12651,7 +12654,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -12869,7 +12872,7 @@
     <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
       <c r="B14" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C14" s="35"/>
       <c r="D14" s="35"/>
@@ -12961,48 +12964,48 @@
         <v>53</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>205</v>
+        <v>39</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>33</v>
       </c>
       <c r="E3" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>206</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>207</v>
       </c>
       <c r="G3" s="16"/>
       <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>209</v>
-      </c>
       <c r="C4" s="14" t="s">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>40</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>36</v>
@@ -13012,17 +13015,17 @@
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="16" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>36</v>
@@ -13031,34 +13034,42 @@
         <v>40</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
     </row>
     <row r="7" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="C7" s="16"/>
+        <v>219</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>48</v>
+      </c>
       <c r="D7" s="16"/>
       <c r="E7" s="16"/>
       <c r="F7" s="16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
+      <c r="A8" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>48</v>
+      </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
@@ -13097,7 +13108,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="4" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B1" s="55"/>
       <c r="C1" s="55"/>
@@ -13111,19 +13122,19 @@
         <v>132</v>
       </c>
       <c r="B2" s="56" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="56" t="s">
+        <v>223</v>
+      </c>
+      <c r="D2" s="56" t="s">
         <v>224</v>
       </c>
-      <c r="C2" s="56" t="s">
+      <c r="E2" s="56" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="56" t="s">
+      <c r="F2" s="56" t="s">
         <v>226</v>
-      </c>
-      <c r="E2" s="56" t="s">
-        <v>227</v>
-      </c>
-      <c r="F2" s="56" t="s">
-        <v>228</v>
       </c>
       <c r="G2" s="56" t="s">
         <v>141</v>
@@ -13131,46 +13142,46 @@
     </row>
     <row r="3" spans="1:7" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>230</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>232</v>
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C4" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="D4" s="14" t="s">
         <v>236</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>238</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>166</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -13193,7 +13204,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="40" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B1" s="42"/>
       <c r="C1" s="42"/>
@@ -13208,13 +13219,13 @@
         <v>130</v>
       </c>
       <c r="B2" s="63" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" s="63" t="s">
+        <v>240</v>
+      </c>
+      <c r="D2" s="63" t="s">
         <v>241</v>
-      </c>
-      <c r="C2" s="63" t="s">
-        <v>242</v>
-      </c>
-      <c r="D2" s="63" t="s">
-        <v>243</v>
       </c>
       <c r="E2" s="63" t="s">
         <v>141</v>
@@ -13228,7 +13239,7 @@
         <v>46154</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>31</v>
@@ -13237,7 +13248,7 @@
         <v>86.99</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F3" s="16"/>
       <c r="G3" s="16"/>
@@ -13506,7 +13517,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -13516,7 +13527,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -13528,7 +13539,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -13545,7 +13556,7 @@
     <row r="4" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33"/>
       <c r="B4" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
@@ -13575,7 +13586,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B1" s="20"/>
       <c r="C1" s="29"/>
@@ -13585,7 +13596,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -13597,7 +13608,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>6</v>
@@ -13614,7 +13625,7 @@
     <row r="4" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33"/>
       <c r="B4" s="34" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
@@ -13644,7 +13655,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="137" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="138"/>
       <c r="C1" s="138"/>
@@ -13654,7 +13665,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="81" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="82" t="s">
         <v>1</v>
@@ -13666,7 +13677,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="82" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="83" t="s">
         <v>6</v>
@@ -13857,7 +13868,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="90" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C12" s="93" t="s">
         <v>2</v>
@@ -13954,7 +13965,7 @@
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="140" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B17" s="141"/>
       <c r="C17" s="141"/>
@@ -14205,7 +14216,7 @@
     <row r="30" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="100"/>
       <c r="B30" s="101" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C30" s="101"/>
       <c r="D30" s="101"/>
@@ -14301,7 +14312,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="143" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B1" s="144"/>
       <c r="C1" s="144"/>
@@ -14311,7 +14322,7 @@
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="69" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B2" s="21" t="s">
         <v>1</v>
@@ -14323,7 +14334,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="70" t="s">
         <v>6</v>
@@ -14553,7 +14564,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C14" s="37" t="s">
         <v>2</v>
@@ -14659,7 +14670,7 @@
     <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="75"/>
       <c r="B20" s="76" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C20" s="77"/>
       <c r="D20" s="77"/>

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4984FF6-2F75-8B49-A640-7000928D3701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77248D52-1412-BB4D-88BC-FA96F528D925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4540" yWindow="3660" windowWidth="28920" windowHeight="16920" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="3660" windowWidth="28980" windowHeight="17200" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="276">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -816,9 +816,6 @@
     <t>Total Set Length</t>
   </si>
   <si>
-    <t>2026-06-21 — Chicago Union FC — ETHS Lazier Field — 5:00 PM</t>
-  </si>
-  <si>
     <t>2026-05-16 — Fat Shallot — 7:00-9:00 PM</t>
   </si>
   <si>
@@ -905,6 +902,13 @@
   </si>
   <si>
     <t>gig fee</t>
+  </si>
+  <si>
+    <t>2026-06-21
+Chicago Union</t>
+  </si>
+  <si>
+    <t>2026-06-21 | Chicago Union FC | 5:00 PM</t>
   </si>
 </sst>
 </file>
@@ -1098,7 +1102,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="56">
+  <borders count="62">
     <border>
       <left/>
       <right/>
@@ -1819,13 +1823,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2178,33 +2260,6 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2235,13 +2290,539 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="58">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE0E0E0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2269,6 +2850,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2556,7 +3141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AD49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="42.83203125" bestFit="1" customWidth="1"/>
@@ -2570,13 +3155,13 @@
     <col min="10" max="10" width="16" style="1" customWidth="1"/>
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
-    <col min="13" max="25" width="16" customWidth="1"/>
-    <col min="26" max="26" width="23.5" customWidth="1"/>
-    <col min="27" max="27" width="16.83203125" customWidth="1"/>
-    <col min="28" max="29" width="16.33203125" customWidth="1"/>
+    <col min="13" max="26" width="16" customWidth="1"/>
+    <col min="27" max="27" width="23.5" customWidth="1"/>
+    <col min="28" max="28" width="16.83203125" customWidth="1"/>
+    <col min="29" max="30" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -2608,8 +3193,9 @@
       <c r="AA1" s="37"/>
       <c r="AB1" s="37"/>
       <c r="AC1" s="37"/>
-    </row>
-    <row r="2" spans="1:29" s="3" customFormat="1" ht="56" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="AD1" s="37"/>
+    </row>
+    <row r="2" spans="1:30" s="3" customFormat="1" ht="56" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="126" t="s">
         <v>1</v>
       </c>
@@ -2644,61 +3230,64 @@
         <v>11</v>
       </c>
       <c r="L2" s="127" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="M2" s="128" t="s">
-        <v>268</v>
-      </c>
-      <c r="N2" s="129" t="s">
+        <v>267</v>
+      </c>
+      <c r="N2" s="128" t="s">
+        <v>274</v>
+      </c>
+      <c r="O2" s="129" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="129" t="s">
+      <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="129" t="s">
+      <c r="Q2" s="129" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="129" t="s">
+      <c r="R2" s="129" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="129" t="s">
+      <c r="S2" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="S2" s="129" t="s">
+      <c r="T2" s="129" t="s">
         <v>17</v>
       </c>
-      <c r="T2" s="129" t="s">
+      <c r="U2" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="129" t="s">
+      <c r="V2" s="129" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="129" t="s">
+      <c r="W2" s="129" t="s">
         <v>20</v>
       </c>
-      <c r="W2" s="129" t="s">
+      <c r="X2" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="X2" s="129" t="s">
+      <c r="Y2" s="129" t="s">
         <v>22</v>
       </c>
-      <c r="Y2" s="129" t="s">
+      <c r="Z2" s="129" t="s">
         <v>23</v>
       </c>
-      <c r="Z2" s="129" t="s">
+      <c r="AA2" s="129" t="s">
         <v>24</v>
       </c>
-      <c r="AA2" s="129" t="s">
+      <c r="AB2" s="129" t="s">
         <v>25</v>
       </c>
-      <c r="AB2" s="129" t="s">
+      <c r="AC2" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="AC2" s="129" t="s">
+      <c r="AD2" s="129" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
@@ -2729,22 +3318,22 @@
       </c>
       <c r="K3" s="108"/>
       <c r="L3" s="125">
-        <f t="shared" ref="L3:L48" si="0">COUNTIF(M3:AC3,"✓")</f>
+        <f t="shared" ref="L3:L48" si="0">COUNTIF(M3:AD3,"✓")</f>
         <v>2</v>
       </c>
       <c r="M3" s="119"/>
-      <c r="N3" s="118"/>
-      <c r="O3" s="111"/>
-      <c r="P3" s="9"/>
+      <c r="N3" s="119"/>
+      <c r="O3" s="118"/>
+      <c r="P3" s="111"/>
       <c r="Q3" s="9"/>
       <c r="R3" s="9"/>
-      <c r="S3" s="9" t="s">
-        <v>32</v>
-      </c>
+      <c r="S3" s="9"/>
       <c r="T3" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="U3" s="9"/>
+      <c r="U3" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="V3" s="9"/>
       <c r="W3" s="9"/>
       <c r="X3" s="9"/>
@@ -2753,8 +3342,9 @@
       <c r="AA3" s="9"/>
       <c r="AB3" s="9"/>
       <c r="AC3" s="9"/>
-    </row>
-    <row r="4" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD3" s="9"/>
+    </row>
+    <row r="4" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="101" t="s">
         <v>34</v>
       </c>
@@ -2787,32 +3377,33 @@
         <v>3</v>
       </c>
       <c r="M4" s="120"/>
-      <c r="N4" s="115"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="101"/>
+      <c r="N4" s="120"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="112"/>
       <c r="Q4" s="101"/>
       <c r="R4" s="101"/>
       <c r="S4" s="101"/>
-      <c r="T4" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="U4" s="101"/>
+      <c r="T4" s="101"/>
+      <c r="U4" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="V4" s="101"/>
       <c r="W4" s="101"/>
-      <c r="X4" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="X4" s="101"/>
       <c r="Y4" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="Z4" s="101"/>
+      <c r="Z4" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="AA4" s="101"/>
       <c r="AB4" s="101"/>
       <c r="AC4" s="101"/>
-    </row>
-    <row r="5" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD4" s="101"/>
+    </row>
+    <row r="5" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B5" s="40" t="s">
         <v>2</v>
@@ -2842,45 +3433,48 @@
       <c r="K5" s="110"/>
       <c r="L5" s="122">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M5" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N5" s="116" t="s">
-        <v>32</v>
-      </c>
-      <c r="O5" s="113" t="s">
-        <v>32</v>
-      </c>
-      <c r="P5" s="10"/>
-      <c r="Q5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" s="10"/>
+      <c r="N5" s="121" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" s="113" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="S5" s="10"/>
-      <c r="T5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="U5" s="10"/>
-      <c r="V5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="X5" s="10"/>
       <c r="Y5" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB5" s="10"/>
+      <c r="Z5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="AC5" s="10"/>
-    </row>
-    <row r="6" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD5" s="10"/>
+    </row>
+    <row r="6" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="101" t="s">
         <v>41</v>
       </c>
@@ -2917,20 +3511,20 @@
       <c r="M6" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="115"/>
-      <c r="O6" s="112"/>
-      <c r="P6" s="101"/>
-      <c r="Q6" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="N6" s="120"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="112"/>
+      <c r="Q6" s="101"/>
       <c r="R6" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="S6" s="101"/>
-      <c r="T6" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="U6" s="101"/>
+      <c r="S6" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="T6" s="101"/>
+      <c r="U6" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="V6" s="101"/>
       <c r="W6" s="101"/>
       <c r="X6" s="101"/>
@@ -2939,8 +3533,9 @@
       <c r="AA6" s="101"/>
       <c r="AB6" s="101"/>
       <c r="AC6" s="101"/>
-    </row>
-    <row r="7" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD6" s="101"/>
+    </row>
+    <row r="7" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>44</v>
       </c>
@@ -2972,24 +3567,26 @@
       <c r="K7" s="110"/>
       <c r="L7" s="122">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M7" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N7" s="116" t="s">
-        <v>32</v>
-      </c>
-      <c r="O7" s="113" t="s">
-        <v>32</v>
-      </c>
-      <c r="P7" s="10" t="s">
+      <c r="N7" s="121" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" s="113" t="s">
         <v>32</v>
       </c>
       <c r="Q7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="R7" s="10"/>
+      <c r="R7" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="S7" s="10"/>
       <c r="T7" s="10"/>
       <c r="U7" s="10"/>
@@ -3001,8 +3598,9 @@
       <c r="AA7" s="10"/>
       <c r="AB7" s="10"/>
       <c r="AC7" s="10"/>
-    </row>
-    <row r="8" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD7" s="10"/>
+    </row>
+    <row r="8" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="101" t="s">
         <v>46</v>
       </c>
@@ -3039,17 +3637,15 @@
         <v>9</v>
       </c>
       <c r="M8" s="120"/>
-      <c r="N8" s="115"/>
-      <c r="O8" s="112"/>
-      <c r="P8" s="101"/>
-      <c r="Q8" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" s="101"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="115"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="101"/>
+      <c r="R8" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="S8" s="101"/>
-      <c r="T8" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="T8" s="101"/>
       <c r="U8" s="101" t="s">
         <v>32</v>
       </c>
@@ -3065,16 +3661,19 @@
       <c r="Y8" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="Z8" s="101"/>
-      <c r="AA8" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB8" s="101"/>
-      <c r="AC8" s="101" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Z8" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA8" s="101"/>
+      <c r="AB8" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC8" s="101"/>
+      <c r="AD8" s="101" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>49</v>
       </c>
@@ -3106,18 +3705,18 @@
       <c r="K9" s="110"/>
       <c r="L9" s="122">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M9" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="116" t="s">
-        <v>32</v>
-      </c>
-      <c r="O9" s="113" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" s="10" t="s">
+      <c r="N9" s="121" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="113" t="s">
         <v>32</v>
       </c>
       <c r="Q9" s="10" t="s">
@@ -3159,8 +3758,11 @@
       <c r="AC9" s="10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD9" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="101" t="s">
         <v>50</v>
       </c>
@@ -3195,9 +3797,9 @@
         <v>1</v>
       </c>
       <c r="M10" s="120"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="112"/>
-      <c r="P10" s="101"/>
+      <c r="N10" s="120"/>
+      <c r="O10" s="115"/>
+      <c r="P10" s="112"/>
       <c r="Q10" s="101"/>
       <c r="R10" s="101"/>
       <c r="S10" s="101"/>
@@ -3205,16 +3807,17 @@
       <c r="U10" s="101"/>
       <c r="V10" s="101"/>
       <c r="W10" s="101"/>
-      <c r="X10" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y10" s="101"/>
+      <c r="X10" s="101"/>
+      <c r="Y10" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="Z10" s="101"/>
       <c r="AA10" s="101"/>
       <c r="AB10" s="101"/>
       <c r="AC10" s="101"/>
-    </row>
-    <row r="11" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD10" s="101"/>
+    </row>
+    <row r="11" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10" t="s">
         <v>52</v>
       </c>
@@ -3247,22 +3850,20 @@
         <v>9</v>
       </c>
       <c r="M11" s="121"/>
-      <c r="N11" s="114"/>
-      <c r="O11" s="113"/>
-      <c r="P11" s="10"/>
+      <c r="N11" s="121"/>
+      <c r="O11" s="114"/>
+      <c r="P11" s="113"/>
       <c r="Q11" s="10"/>
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
-      <c r="T11" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="T11" s="10"/>
       <c r="U11" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="V11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W11" s="10"/>
       <c r="X11" s="10" t="s">
         <v>32</v>
       </c>
@@ -3281,8 +3882,11 @@
       <c r="AC11" s="10" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD11" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="101" t="s">
         <v>54</v>
       </c>
@@ -3314,18 +3918,18 @@
       <c r="K12" s="109"/>
       <c r="L12" s="123">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M12" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N12" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="O12" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="P12" s="101" t="s">
+      <c r="N12" s="120" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" s="117" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" s="112" t="s">
         <v>32</v>
       </c>
       <c r="Q12" s="101" t="s">
@@ -3334,7 +3938,9 @@
       <c r="R12" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="S12" s="101"/>
+      <c r="S12" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="T12" s="101"/>
       <c r="U12" s="101"/>
       <c r="V12" s="101"/>
@@ -3345,8 +3951,9 @@
       <c r="AA12" s="101"/>
       <c r="AB12" s="101"/>
       <c r="AC12" s="101"/>
-    </row>
-    <row r="13" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD12" s="101"/>
+    </row>
+    <row r="13" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
         <v>57</v>
       </c>
@@ -3381,19 +3988,19 @@
         <v>2</v>
       </c>
       <c r="M13" s="121"/>
-      <c r="N13" s="114"/>
-      <c r="O13" s="113"/>
-      <c r="P13" s="10"/>
+      <c r="N13" s="121"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="113"/>
       <c r="Q13" s="10"/>
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
-      <c r="T13" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="T13" s="10"/>
       <c r="U13" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="V13" s="10"/>
+      <c r="V13" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="W13" s="10"/>
       <c r="X13" s="10"/>
       <c r="Y13" s="10"/>
@@ -3401,8 +4008,9 @@
       <c r="AA13" s="10"/>
       <c r="AB13" s="10"/>
       <c r="AC13" s="10"/>
-    </row>
-    <row r="14" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD13" s="10"/>
+    </row>
+    <row r="14" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="101" t="s">
         <v>61</v>
       </c>
@@ -3435,9 +4043,9 @@
         <v>1</v>
       </c>
       <c r="M14" s="120"/>
-      <c r="N14" s="115"/>
-      <c r="O14" s="112"/>
-      <c r="P14" s="101"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="115"/>
+      <c r="P14" s="112"/>
       <c r="Q14" s="101"/>
       <c r="R14" s="101"/>
       <c r="S14" s="101"/>
@@ -3450,11 +4058,12 @@
       <c r="Z14" s="101"/>
       <c r="AA14" s="101"/>
       <c r="AB14" s="101"/>
-      <c r="AC14" s="101" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC14" s="101"/>
+      <c r="AD14" s="101" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
         <v>63</v>
       </c>
@@ -3486,25 +4095,25 @@
       <c r="K15" s="110"/>
       <c r="L15" s="122">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N15" s="116" t="s">
-        <v>32</v>
-      </c>
-      <c r="O15" s="113" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="N15" s="121" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="113" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" s="10"/>
       <c r="T15" s="10" t="s">
         <v>32</v>
       </c>
@@ -3514,10 +4123,10 @@
       <c r="V15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="W15" s="10"/>
-      <c r="X15" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="W15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="X15" s="10"/>
       <c r="Y15" s="10" t="s">
         <v>32</v>
       </c>
@@ -3530,9 +4139,12 @@
       <c r="AB15" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AC15" s="10"/>
-    </row>
-    <row r="16" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD15" s="10"/>
+    </row>
+    <row r="16" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="101" t="s">
         <v>65</v>
       </c>
@@ -3569,23 +4181,21 @@
       <c r="M16" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N16" s="115"/>
-      <c r="O16" s="112"/>
-      <c r="P16" s="101"/>
-      <c r="Q16" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="R16" s="101"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="115"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="101"/>
+      <c r="R16" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="S16" s="101"/>
-      <c r="T16" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="U16" s="101"/>
+      <c r="T16" s="101"/>
+      <c r="U16" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="V16" s="101"/>
       <c r="W16" s="101"/>
-      <c r="X16" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="X16" s="101"/>
       <c r="Y16" s="101" t="s">
         <v>32</v>
       </c>
@@ -3595,12 +4205,15 @@
       <c r="AA16" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="AB16" s="101"/>
-      <c r="AC16" s="101" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB16" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC16" s="101"/>
+      <c r="AD16" s="101" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
         <v>67</v>
       </c>
@@ -3635,13 +4248,13 @@
         <v>1</v>
       </c>
       <c r="M17" s="121"/>
-      <c r="N17" s="114"/>
-      <c r="O17" s="113"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R17" s="10"/>
+      <c r="N17" s="121"/>
+      <c r="O17" s="114"/>
+      <c r="P17" s="113"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="S17" s="10"/>
       <c r="T17" s="10"/>
       <c r="U17" s="10"/>
@@ -3653,8 +4266,9 @@
       <c r="AA17" s="10"/>
       <c r="AB17" s="10"/>
       <c r="AC17" s="10"/>
-    </row>
-    <row r="18" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD17" s="10"/>
+    </row>
+    <row r="18" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="101" t="s">
         <v>70</v>
       </c>
@@ -3686,21 +4300,21 @@
       <c r="K18" s="109"/>
       <c r="L18" s="123">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M18" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N18" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="O18" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="P18" s="101"/>
-      <c r="Q18" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="N18" s="120" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" s="117" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" s="112" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q18" s="101"/>
       <c r="R18" s="101" t="s">
         <v>32</v>
       </c>
@@ -3713,7 +4327,9 @@
       <c r="U18" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="V18" s="101"/>
+      <c r="V18" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="W18" s="101"/>
       <c r="X18" s="101"/>
       <c r="Y18" s="101"/>
@@ -3721,8 +4337,9 @@
       <c r="AA18" s="101"/>
       <c r="AB18" s="101"/>
       <c r="AC18" s="101"/>
-    </row>
-    <row r="19" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD18" s="101"/>
+    </row>
+    <row r="19" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>72</v>
       </c>
@@ -3754,24 +4371,26 @@
       <c r="K19" s="110"/>
       <c r="L19" s="122">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M19" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N19" s="116" t="s">
-        <v>32</v>
-      </c>
-      <c r="O19" s="113" t="s">
-        <v>32</v>
-      </c>
-      <c r="P19" s="10" t="s">
+      <c r="N19" s="121" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="P19" s="113" t="s">
         <v>32</v>
       </c>
       <c r="Q19" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="R19" s="10"/>
+      <c r="R19" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="S19" s="10"/>
       <c r="T19" s="10"/>
       <c r="U19" s="10"/>
@@ -3783,8 +4402,9 @@
       <c r="AA19" s="10"/>
       <c r="AB19" s="10"/>
       <c r="AC19" s="10"/>
-    </row>
-    <row r="20" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD19" s="10"/>
+    </row>
+    <row r="20" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="101" t="s">
         <v>74</v>
       </c>
@@ -3821,40 +4441,41 @@
       <c r="M20" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N20" s="115"/>
-      <c r="O20" s="112"/>
-      <c r="P20" s="101"/>
-      <c r="Q20" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="R20" s="101"/>
+      <c r="N20" s="120"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="112"/>
+      <c r="Q20" s="101"/>
+      <c r="R20" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="S20" s="101"/>
-      <c r="T20" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="T20" s="101"/>
       <c r="U20" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="V20" s="101"/>
+      <c r="V20" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="W20" s="101"/>
-      <c r="X20" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="X20" s="101"/>
       <c r="Y20" s="101" t="s">
         <v>32</v>
       </c>
       <c r="Z20" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="AA20" s="101"/>
-      <c r="AB20" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="AA20" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB20" s="101"/>
       <c r="AC20" s="101" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD20" s="101" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="10" t="s">
         <v>76</v>
       </c>
@@ -3887,9 +4508,9 @@
         <v>1</v>
       </c>
       <c r="M21" s="121"/>
-      <c r="N21" s="114"/>
-      <c r="O21" s="113"/>
-      <c r="P21" s="10"/>
+      <c r="N21" s="121"/>
+      <c r="O21" s="114"/>
+      <c r="P21" s="113"/>
       <c r="Q21" s="10"/>
       <c r="R21" s="10"/>
       <c r="S21" s="10"/>
@@ -3897,16 +4518,17 @@
       <c r="U21" s="10"/>
       <c r="V21" s="10"/>
       <c r="W21" s="10"/>
-      <c r="X21" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="Z21" s="10"/>
       <c r="AA21" s="10"/>
       <c r="AB21" s="10"/>
       <c r="AC21" s="10"/>
-    </row>
-    <row r="22" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD21" s="10"/>
+    </row>
+    <row r="22" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="101" t="s">
         <v>78</v>
       </c>
@@ -3938,27 +4560,27 @@
       <c r="K22" s="109"/>
       <c r="L22" s="123">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M22" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N22" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="O22" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="P22" s="101" t="s">
+      <c r="N22" s="120" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" s="117" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" s="112" t="s">
         <v>32</v>
       </c>
       <c r="Q22" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="R22" s="101"/>
-      <c r="S22" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="R22" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" s="101"/>
       <c r="T22" s="101" t="s">
         <v>32</v>
       </c>
@@ -3989,8 +4611,11 @@
       <c r="AC22" s="101" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD22" s="101" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>80</v>
       </c>
@@ -4025,16 +4650,14 @@
         <v>8</v>
       </c>
       <c r="M23" s="121"/>
-      <c r="N23" s="114"/>
-      <c r="O23" s="113"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="N23" s="121"/>
+      <c r="O23" s="114"/>
+      <c r="P23" s="113"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="S23" s="10"/>
       <c r="T23" s="10" t="s">
         <v>32</v>
       </c>
@@ -4053,12 +4676,15 @@
       <c r="Y23" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="Z23" s="10"/>
+      <c r="Z23" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="AA23" s="10"/>
       <c r="AB23" s="10"/>
       <c r="AC23" s="10"/>
-    </row>
-    <row r="24" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD23" s="10"/>
+    </row>
+    <row r="24" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="101" t="s">
         <v>82</v>
       </c>
@@ -4091,40 +4717,41 @@
         <v>8</v>
       </c>
       <c r="M24" s="120"/>
-      <c r="N24" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="O24" s="112"/>
-      <c r="P24" s="101"/>
-      <c r="Q24" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="R24" s="101"/>
+      <c r="N24" s="120"/>
+      <c r="O24" s="117" t="s">
+        <v>32</v>
+      </c>
+      <c r="P24" s="112"/>
+      <c r="Q24" s="101"/>
+      <c r="R24" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="S24" s="101"/>
-      <c r="T24" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="T24" s="101"/>
       <c r="U24" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="V24" s="101"/>
-      <c r="W24" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="V24" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="W24" s="101"/>
       <c r="X24" s="101" t="s">
         <v>32</v>
       </c>
       <c r="Y24" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="Z24" s="101"/>
-      <c r="AA24" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB24" s="101"/>
+      <c r="Z24" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA24" s="101"/>
+      <c r="AB24" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="AC24" s="101"/>
-    </row>
-    <row r="25" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD24" s="101"/>
+    </row>
+    <row r="25" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="10" t="s">
         <v>85</v>
       </c>
@@ -4163,26 +4790,24 @@
       <c r="M25" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N25" s="114"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="N25" s="121"/>
+      <c r="O25" s="114"/>
+      <c r="P25" s="8"/>
       <c r="Q25" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="R25" s="10"/>
+      <c r="R25" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="S25" s="10"/>
-      <c r="T25" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="T25" s="10"/>
       <c r="U25" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="V25" s="10"/>
-      <c r="W25" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="V25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W25" s="10"/>
       <c r="X25" s="10" t="s">
         <v>32</v>
       </c>
@@ -4195,10 +4820,13 @@
       <c r="AA25" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AB25" s="10"/>
+      <c r="AB25" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="AC25" s="10"/>
-    </row>
-    <row r="26" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD25" s="10"/>
+    </row>
+    <row r="26" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="101" t="s">
         <v>87</v>
       </c>
@@ -4235,8 +4863,8 @@
       <c r="M26" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N26" s="115"/>
-      <c r="O26" s="105"/>
+      <c r="N26" s="120"/>
+      <c r="O26" s="115"/>
       <c r="P26" s="105"/>
       <c r="Q26" s="105"/>
       <c r="R26" s="105"/>
@@ -4251,8 +4879,9 @@
       <c r="AA26" s="105"/>
       <c r="AB26" s="105"/>
       <c r="AC26" s="105"/>
-    </row>
-    <row r="27" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD26" s="105"/>
+    </row>
+    <row r="27" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>89</v>
       </c>
@@ -4291,13 +4920,13 @@
       <c r="M27" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N27" s="116"/>
-      <c r="O27" s="113"/>
-      <c r="P27" s="10"/>
-      <c r="Q27" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R27" s="10"/>
+      <c r="N27" s="121"/>
+      <c r="O27" s="116"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="S27" s="10"/>
       <c r="T27" s="10"/>
       <c r="U27" s="10"/>
@@ -4309,8 +4938,9 @@
       <c r="AA27" s="10"/>
       <c r="AB27" s="10"/>
       <c r="AC27" s="10"/>
-    </row>
-    <row r="28" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD27" s="10"/>
+    </row>
+    <row r="28" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="101" t="s">
         <v>90</v>
       </c>
@@ -4342,25 +4972,27 @@
       <c r="K28" s="109"/>
       <c r="L28" s="123">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M28" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N28" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="O28" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="P28" s="101"/>
-      <c r="Q28" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="N28" s="120" t="s">
+        <v>32</v>
+      </c>
+      <c r="O28" s="117" t="s">
+        <v>32</v>
+      </c>
+      <c r="P28" s="112" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q28" s="101"/>
       <c r="R28" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="S28" s="101"/>
+      <c r="S28" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="T28" s="101"/>
       <c r="U28" s="101"/>
       <c r="V28" s="101"/>
@@ -4371,8 +5003,9 @@
       <c r="AA28" s="101"/>
       <c r="AB28" s="101"/>
       <c r="AC28" s="101"/>
-    </row>
-    <row r="29" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD28" s="101"/>
+    </row>
+    <row r="29" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
         <v>92</v>
       </c>
@@ -4409,19 +5042,17 @@
       <c r="M29" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N29" s="114"/>
-      <c r="O29" s="113"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="N29" s="121"/>
+      <c r="O29" s="114"/>
+      <c r="P29" s="113"/>
+      <c r="Q29" s="10"/>
       <c r="R29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="S29" s="10"/>
-      <c r="T29" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="S29" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T29" s="10"/>
       <c r="U29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4446,9 +5077,12 @@
       <c r="AB29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AC29" s="10"/>
-    </row>
-    <row r="30" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC29" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD29" s="10"/>
+    </row>
+    <row r="30" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="101" t="s">
         <v>94</v>
       </c>
@@ -4480,18 +5114,18 @@
       <c r="K30" s="109"/>
       <c r="L30" s="123">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M30" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N30" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="O30" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="P30" s="101" t="s">
+      <c r="N30" s="120" t="s">
+        <v>32</v>
+      </c>
+      <c r="O30" s="117" t="s">
+        <v>32</v>
+      </c>
+      <c r="P30" s="112" t="s">
         <v>32</v>
       </c>
       <c r="Q30" s="101" t="s">
@@ -4527,10 +5161,13 @@
       <c r="AA30" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="AB30" s="101"/>
+      <c r="AB30" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="AC30" s="101"/>
-    </row>
-    <row r="31" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD30" s="101"/>
+    </row>
+    <row r="31" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="10" t="s">
         <v>96</v>
       </c>
@@ -4565,9 +5202,9 @@
         <v>2</v>
       </c>
       <c r="M31" s="121"/>
-      <c r="N31" s="114"/>
-      <c r="O31" s="113"/>
-      <c r="P31" s="10"/>
+      <c r="N31" s="121"/>
+      <c r="O31" s="114"/>
+      <c r="P31" s="113"/>
       <c r="Q31" s="10"/>
       <c r="R31" s="10"/>
       <c r="S31" s="10"/>
@@ -4575,18 +5212,19 @@
       <c r="U31" s="10"/>
       <c r="V31" s="10"/>
       <c r="W31" s="10"/>
-      <c r="X31" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y31" s="10"/>
+      <c r="X31" s="10"/>
+      <c r="Y31" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="Z31" s="10"/>
       <c r="AA31" s="10"/>
       <c r="AB31" s="10"/>
-      <c r="AC31" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC31" s="10"/>
+      <c r="AD31" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="101" t="s">
         <v>97</v>
       </c>
@@ -4623,23 +5261,21 @@
       <c r="M32" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N32" s="115"/>
-      <c r="O32" s="112"/>
-      <c r="P32" s="101"/>
-      <c r="Q32" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="R32" s="101"/>
+      <c r="N32" s="120"/>
+      <c r="O32" s="115"/>
+      <c r="P32" s="112"/>
+      <c r="Q32" s="101"/>
+      <c r="R32" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="S32" s="101"/>
-      <c r="T32" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="U32" s="101"/>
+      <c r="T32" s="101"/>
+      <c r="U32" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="V32" s="101"/>
       <c r="W32" s="101"/>
-      <c r="X32" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="X32" s="101"/>
       <c r="Y32" s="101" t="s">
         <v>32</v>
       </c>
@@ -4649,10 +5285,13 @@
       <c r="AA32" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="AB32" s="101"/>
+      <c r="AB32" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="AC32" s="101"/>
-    </row>
-    <row r="33" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD32" s="101"/>
+    </row>
+    <row r="33" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="10" t="s">
         <v>99</v>
       </c>
@@ -4684,18 +5323,18 @@
       <c r="K33" s="110"/>
       <c r="L33" s="122">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M33" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N33" s="116" t="s">
-        <v>32</v>
-      </c>
-      <c r="O33" s="113" t="s">
-        <v>32</v>
-      </c>
-      <c r="P33" s="10" t="s">
+      <c r="N33" s="121" t="s">
+        <v>32</v>
+      </c>
+      <c r="O33" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="P33" s="113" t="s">
         <v>32</v>
       </c>
       <c r="Q33" s="10" t="s">
@@ -4722,13 +5361,16 @@
       <c r="X33" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="Y33" s="10"/>
+      <c r="Y33" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="Z33" s="10"/>
       <c r="AA33" s="10"/>
       <c r="AB33" s="10"/>
       <c r="AC33" s="10"/>
-    </row>
-    <row r="34" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD33" s="10"/>
+    </row>
+    <row r="34" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="101" t="s">
         <v>101</v>
       </c>
@@ -4761,40 +5403,41 @@
         <v>8</v>
       </c>
       <c r="M34" s="120"/>
-      <c r="N34" s="115"/>
-      <c r="O34" s="112"/>
-      <c r="P34" s="101"/>
-      <c r="Q34" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="R34" s="101"/>
-      <c r="S34" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="N34" s="120"/>
+      <c r="O34" s="115"/>
+      <c r="P34" s="112"/>
+      <c r="Q34" s="101"/>
+      <c r="R34" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="S34" s="101"/>
       <c r="T34" s="101" t="s">
         <v>32</v>
       </c>
       <c r="U34" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="V34" s="101"/>
+      <c r="V34" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="W34" s="101"/>
-      <c r="X34" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="X34" s="101"/>
       <c r="Y34" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="Z34" s="101"/>
-      <c r="AA34" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="Z34" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA34" s="101"/>
       <c r="AB34" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="AC34" s="101"/>
-    </row>
-    <row r="35" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC34" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD34" s="101"/>
+    </row>
+    <row r="35" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
         <v>103</v>
       </c>
@@ -4831,40 +5474,41 @@
       <c r="M35" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N35" s="114"/>
-      <c r="O35" s="113"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R35" s="10"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="114"/>
+      <c r="P35" s="113"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="S35" s="10"/>
-      <c r="T35" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="T35" s="10"/>
       <c r="U35" s="10" t="s">
         <v>32</v>
       </c>
       <c r="V35" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="W35" s="10"/>
-      <c r="X35" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="W35" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="X35" s="10"/>
       <c r="Y35" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="Z35" s="10"/>
-      <c r="AA35" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="Z35" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA35" s="10"/>
       <c r="AB35" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="AC35" s="10"/>
-    </row>
-    <row r="36" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC35" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD35" s="10"/>
+    </row>
+    <row r="36" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="101" t="s">
         <v>104</v>
       </c>
@@ -4897,11 +5541,11 @@
         <v>4</v>
       </c>
       <c r="M36" s="120"/>
-      <c r="N36" s="115"/>
-      <c r="O36" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="P36" s="101"/>
+      <c r="N36" s="120"/>
+      <c r="O36" s="115"/>
+      <c r="P36" s="112" t="s">
+        <v>32</v>
+      </c>
       <c r="Q36" s="101"/>
       <c r="R36" s="101"/>
       <c r="S36" s="101"/>
@@ -4909,20 +5553,21 @@
       <c r="U36" s="101"/>
       <c r="V36" s="101"/>
       <c r="W36" s="101"/>
-      <c r="X36" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="X36" s="101"/>
       <c r="Y36" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="Z36" s="101"/>
+      <c r="Z36" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="AA36" s="101"/>
-      <c r="AB36" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC36" s="101"/>
-    </row>
-    <row r="37" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB36" s="101"/>
+      <c r="AC36" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD36" s="101"/>
+    </row>
+    <row r="37" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="10" t="s">
         <v>106</v>
       </c>
@@ -4954,21 +5599,21 @@
       <c r="K37" s="110"/>
       <c r="L37" s="122">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M37" s="121" t="s">
         <v>32</v>
       </c>
-      <c r="N37" s="116" t="s">
-        <v>32</v>
-      </c>
-      <c r="O37" s="113" t="s">
-        <v>32</v>
-      </c>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="N37" s="121" t="s">
+        <v>32</v>
+      </c>
+      <c r="O37" s="116" t="s">
+        <v>32</v>
+      </c>
+      <c r="P37" s="113" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q37" s="10"/>
       <c r="R37" s="10" t="s">
         <v>32</v>
       </c>
@@ -4984,15 +5629,18 @@
       <c r="V37" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="W37" s="10"/>
+      <c r="W37" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="X37" s="10"/>
       <c r="Y37" s="10"/>
       <c r="Z37" s="10"/>
       <c r="AA37" s="10"/>
       <c r="AB37" s="10"/>
       <c r="AC37" s="10"/>
-    </row>
-    <row r="38" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD37" s="10"/>
+    </row>
+    <row r="38" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="101" t="s">
         <v>108</v>
       </c>
@@ -5029,19 +5677,19 @@
       <c r="M38" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N38" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="O38" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="P38" s="101" t="s">
+      <c r="N38" s="120"/>
+      <c r="O38" s="117" t="s">
+        <v>32</v>
+      </c>
+      <c r="P38" s="112" t="s">
         <v>32</v>
       </c>
       <c r="Q38" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="R38" s="101"/>
+      <c r="R38" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="S38" s="101"/>
       <c r="T38" s="101"/>
       <c r="U38" s="101"/>
@@ -5053,8 +5701,9 @@
       <c r="AA38" s="101"/>
       <c r="AB38" s="101"/>
       <c r="AC38" s="101"/>
-    </row>
-    <row r="39" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD38" s="101"/>
+    </row>
+    <row r="39" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="10" t="s">
         <v>110</v>
       </c>
@@ -5087,9 +5736,9 @@
         <v>2</v>
       </c>
       <c r="M39" s="121"/>
-      <c r="N39" s="114"/>
-      <c r="O39" s="113"/>
-      <c r="P39" s="10"/>
+      <c r="N39" s="121"/>
+      <c r="O39" s="114"/>
+      <c r="P39" s="113"/>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
       <c r="S39" s="10"/>
@@ -5097,18 +5746,19 @@
       <c r="U39" s="10"/>
       <c r="V39" s="10"/>
       <c r="W39" s="10"/>
-      <c r="X39" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="X39" s="10"/>
       <c r="Y39" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="Z39" s="10"/>
+      <c r="Z39" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="AA39" s="10"/>
       <c r="AB39" s="10"/>
       <c r="AC39" s="10"/>
-    </row>
-    <row r="40" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD39" s="10"/>
+    </row>
+    <row r="40" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="101" t="s">
         <v>113</v>
       </c>
@@ -5141,14 +5791,14 @@
         <v>1</v>
       </c>
       <c r="M40" s="120"/>
-      <c r="N40" s="115"/>
-      <c r="O40" s="112"/>
-      <c r="P40" s="101"/>
+      <c r="N40" s="120"/>
+      <c r="O40" s="115"/>
+      <c r="P40" s="112"/>
       <c r="Q40" s="101"/>
-      <c r="R40" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="S40" s="101"/>
+      <c r="R40" s="101"/>
+      <c r="S40" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="T40" s="101"/>
       <c r="U40" s="101"/>
       <c r="V40" s="101"/>
@@ -5159,8 +5809,9 @@
       <c r="AA40" s="101"/>
       <c r="AB40" s="101"/>
       <c r="AC40" s="101"/>
-    </row>
-    <row r="41" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD40" s="101"/>
+    </row>
+    <row r="41" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="10" t="s">
         <v>114</v>
       </c>
@@ -5195,21 +5846,21 @@
         <v>3</v>
       </c>
       <c r="M41" s="121"/>
-      <c r="N41" s="114"/>
-      <c r="O41" s="113"/>
-      <c r="P41" s="10"/>
-      <c r="Q41" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R41" s="10"/>
+      <c r="N41" s="121"/>
+      <c r="O41" s="114"/>
+      <c r="P41" s="113"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="S41" s="10"/>
-      <c r="T41" s="10" t="s">
-        <v>32</v>
-      </c>
+      <c r="T41" s="10"/>
       <c r="U41" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="V41" s="10"/>
+      <c r="V41" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="W41" s="10"/>
       <c r="X41" s="10"/>
       <c r="Y41" s="10"/>
@@ -5217,8 +5868,9 @@
       <c r="AA41" s="10"/>
       <c r="AB41" s="10"/>
       <c r="AC41" s="10"/>
-    </row>
-    <row r="42" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD41" s="10"/>
+    </row>
+    <row r="42" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="101" t="s">
         <v>116</v>
       </c>
@@ -5255,34 +5907,35 @@
       <c r="M42" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N42" s="115"/>
-      <c r="O42" s="112"/>
-      <c r="P42" s="101"/>
-      <c r="Q42" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="N42" s="120"/>
+      <c r="O42" s="115"/>
+      <c r="P42" s="112"/>
+      <c r="Q42" s="101"/>
       <c r="R42" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="S42" s="101"/>
-      <c r="T42" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="S42" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="T42" s="101"/>
       <c r="U42" s="101" t="s">
         <v>32</v>
       </c>
       <c r="V42" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="W42" s="101"/>
+      <c r="W42" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="X42" s="101"/>
       <c r="Y42" s="101"/>
       <c r="Z42" s="101"/>
       <c r="AA42" s="101"/>
       <c r="AB42" s="101"/>
       <c r="AC42" s="101"/>
-    </row>
-    <row r="43" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD42" s="101"/>
+    </row>
+    <row r="43" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
         <v>118</v>
       </c>
@@ -5315,28 +5968,29 @@
         <v>2</v>
       </c>
       <c r="M43" s="121"/>
-      <c r="N43" s="114"/>
-      <c r="O43" s="113"/>
-      <c r="P43" s="10"/>
-      <c r="Q43" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="R43" s="10"/>
+      <c r="N43" s="121"/>
+      <c r="O43" s="114"/>
+      <c r="P43" s="113"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="S43" s="10"/>
       <c r="T43" s="10"/>
       <c r="U43" s="10"/>
       <c r="V43" s="10"/>
       <c r="W43" s="10"/>
-      <c r="X43" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y43" s="10"/>
+      <c r="X43" s="10"/>
+      <c r="Y43" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="Z43" s="10"/>
       <c r="AA43" s="10"/>
       <c r="AB43" s="10"/>
       <c r="AC43" s="10"/>
-    </row>
-    <row r="44" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD43" s="10"/>
+    </row>
+    <row r="44" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="101" t="s">
         <v>120</v>
       </c>
@@ -5373,32 +6027,33 @@
       <c r="M44" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N44" s="115"/>
-      <c r="O44" s="112"/>
-      <c r="P44" s="101"/>
+      <c r="N44" s="120"/>
+      <c r="O44" s="115"/>
+      <c r="P44" s="112"/>
       <c r="Q44" s="101"/>
-      <c r="R44" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="R44" s="101"/>
       <c r="S44" s="101" t="s">
         <v>32</v>
       </c>
       <c r="T44" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="U44" s="101"/>
-      <c r="V44" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="W44" s="101"/>
+      <c r="U44" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="V44" s="101"/>
+      <c r="W44" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="X44" s="101"/>
       <c r="Y44" s="101"/>
       <c r="Z44" s="101"/>
       <c r="AA44" s="101"/>
       <c r="AB44" s="101"/>
       <c r="AC44" s="101"/>
-    </row>
-    <row r="45" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD44" s="101"/>
+    </row>
+    <row r="45" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="10" t="s">
         <v>121</v>
       </c>
@@ -5433,9 +6088,9 @@
         <v>0</v>
       </c>
       <c r="M45" s="121"/>
-      <c r="N45" s="114"/>
-      <c r="O45" s="113"/>
-      <c r="P45" s="10"/>
+      <c r="N45" s="121"/>
+      <c r="O45" s="114"/>
+      <c r="P45" s="113"/>
       <c r="Q45" s="10"/>
       <c r="R45" s="10"/>
       <c r="S45" s="10"/>
@@ -5449,8 +6104,9 @@
       <c r="AA45" s="10"/>
       <c r="AB45" s="10"/>
       <c r="AC45" s="10"/>
-    </row>
-    <row r="46" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD45" s="10"/>
+    </row>
+    <row r="46" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="101" t="s">
         <v>123</v>
       </c>
@@ -5482,18 +6138,18 @@
       <c r="K46" s="109"/>
       <c r="L46" s="123">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M46" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N46" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="O46" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="P46" s="101" t="s">
+      <c r="N46" s="120" t="s">
+        <v>32</v>
+      </c>
+      <c r="O46" s="117" t="s">
+        <v>32</v>
+      </c>
+      <c r="P46" s="112" t="s">
         <v>32</v>
       </c>
       <c r="Q46" s="101" t="s">
@@ -5535,8 +6191,11 @@
       <c r="AC46" s="101" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="47" spans="1:29" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD46" s="101" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
         <v>124</v>
       </c>
@@ -5563,15 +6222,15 @@
         <v>1</v>
       </c>
       <c r="M47" s="121"/>
-      <c r="N47" s="114"/>
-      <c r="O47" s="113"/>
-      <c r="P47" s="10"/>
+      <c r="N47" s="121"/>
+      <c r="O47" s="114"/>
+      <c r="P47" s="113"/>
       <c r="Q47" s="10"/>
       <c r="R47" s="10"/>
-      <c r="S47" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="U47" s="10"/>
       <c r="V47" s="10"/>
       <c r="W47" s="10"/>
@@ -5581,8 +6240,9 @@
       <c r="AA47" s="10"/>
       <c r="AB47" s="10"/>
       <c r="AC47" s="10"/>
-    </row>
-    <row r="48" spans="1:29" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AD47" s="10"/>
+    </row>
+    <row r="48" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="101" t="s">
         <v>127</v>
       </c>
@@ -5614,49 +6274,52 @@
       <c r="K48" s="109"/>
       <c r="L48" s="123">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M48" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="N48" s="117" t="s">
-        <v>32</v>
-      </c>
-      <c r="O48" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="P48" s="101"/>
-      <c r="Q48" s="101" t="s">
-        <v>32</v>
-      </c>
-      <c r="R48" s="101"/>
-      <c r="S48" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="N48" s="120" t="s">
+        <v>32</v>
+      </c>
+      <c r="O48" s="117" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" s="112" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q48" s="101"/>
+      <c r="R48" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="S48" s="101"/>
       <c r="T48" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="U48" s="101"/>
+      <c r="U48" s="101" t="s">
+        <v>32</v>
+      </c>
       <c r="V48" s="101"/>
       <c r="W48" s="101"/>
-      <c r="X48" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="X48" s="101"/>
       <c r="Y48" s="101" t="s">
         <v>32</v>
       </c>
-      <c r="Z48" s="101"/>
-      <c r="AA48" s="101" t="s">
-        <v>32</v>
-      </c>
+      <c r="Z48" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA48" s="101"/>
       <c r="AB48" s="101" t="s">
         <v>32</v>
       </c>
       <c r="AC48" s="101" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="101" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -5686,25 +6349,26 @@
       <c r="AA49" s="8"/>
       <c r="AB49" s="8"/>
       <c r="AC49" s="8"/>
+      <c r="AD49" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="N2" location="'2026-05-14 Fat Shallot'!A1" display="2026-05-14_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="O2" location="'2026-05-02 Lincolnwood'!A1" display="2026-05-02_x000a_Lincolnwood" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="P2" location="'2026-04-22 Spring Cha Ching'!A1" display="2026-04-22_x000a_Spring Cha Ching" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="Q2" location="'2026-01-24 Goat Village'!A1" display="2026-01-24_x000a_Goat Village" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="R2" location="'2025-11-16 Double Clutch'!A1" display="2025-11-16_x000a_Double Clutch" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="S2" location="'2025-09-06 Block Party'!A1" display="2025-09-06_x000a_Block Party" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="T2" location="'2025-06-25 American Legion'!A1" display="2025-06-25_x000a_American Legion" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="U2" location="'2025-06-07 Fat Shallot'!A1" display="2025-06-07_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="V2" location="'2025-05-03 Lincolnwood'!A1" display="2025-05-03_x000a_Lincolnwood" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="W2" location="'2024-10-09 Fat Shallot'!A1" display="2024-10-09_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="X2" location="'2024-09-07 Block Party'!A1" display="2024-09-07_x000a_Block Party" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="Y2" location="'2024-08-10 Fat Shallot'!A1" display="2024-08-10_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="Z2" location="'2024-07-13 Chicago Union'!A1" display="2024-07-13_x000a_Chicago Union" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="AA2" location="'2024-06-08 Fat Shallot'!A1" display="2024-06-08_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="AB2" location="'2024-04-27 Lincolnwood'!A1" display="2024-04-27_x000a_Lincolnwood" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="AC2" location="'2023-09-09 Block Party'!A1" display="2023-09-09_x000a_Block Party" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="O2" location="'2026-05-14 Fat Shallot'!A1" display="2026-05-14_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="P2" location="'2026-05-02 Lincolnwood'!A1" display="2026-05-02_x000a_Lincolnwood" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="Q2" location="'2026-04-22 Spring Cha Ching'!A1" display="2026-04-22_x000a_Spring Cha Ching" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="R2" location="'2026-01-24 Goat Village'!A1" display="2026-01-24_x000a_Goat Village" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="S2" location="'2025-11-16 Double Clutch'!A1" display="2025-11-16_x000a_Double Clutch" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="T2" location="'2025-09-06 Block Party'!A1" display="2025-09-06_x000a_Block Party" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="U2" location="'2025-06-25 American Legion'!A1" display="2025-06-25_x000a_American Legion" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="V2" location="'2025-06-07 Fat Shallot'!A1" display="2025-06-07_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="W2" location="'2025-05-03 Lincolnwood'!A1" display="2025-05-03_x000a_Lincolnwood" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="X2" location="'2024-10-09 Fat Shallot'!A1" display="2024-10-09_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="Y2" location="'2024-09-07 Block Party'!A1" display="2024-09-07_x000a_Block Party" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="Z2" location="'2024-08-10 Fat Shallot'!A1" display="2024-08-10_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="AA2" location="'2024-07-13 Chicago Union'!A1" display="2024-07-13_x000a_Chicago Union" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="AB2" location="'2024-06-08 Fat Shallot'!A1" display="2024-06-08_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="AC2" location="'2024-04-27 Lincolnwood'!A1" display="2024-04-27_x000a_Lincolnwood" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="AD2" location="'2023-09-09 Block Party'!A1" display="2023-09-09_x000a_Block Party" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
     <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
@@ -5815,7 +6479,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -5845,7 +6509,7 @@
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B3" s="20" t="s">
         <v>104</v>
@@ -6077,7 +6741,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C15" s="33" t="s">
         <v>2</v>
@@ -6247,7 +6911,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -6538,7 +7202,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -6951,7 +7615,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>2</v>
@@ -7287,7 +7951,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -7646,7 +8310,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -8011,7 +8675,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -8422,7 +9086,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C22" s="33" t="s">
         <v>2</v>
@@ -8692,7 +9356,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -9101,7 +9765,7 @@
     </row>
     <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B22" s="20" t="s">
         <v>103</v>
@@ -9200,7 +9864,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -9453,7 +10117,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>2</v>
@@ -9490,7 +10154,7 @@
     </row>
     <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="35" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B16" s="20" t="s">
         <v>103</v>
@@ -9578,7 +10242,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -9887,7 +10551,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -10040,7 +10704,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>2</v>
@@ -11086,8 +11750,12 @@
       <c r="D21" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E21" s="10"/>
-      <c r="F21" s="14"/>
+      <c r="E21" s="10">
+        <v>14</v>
+      </c>
+      <c r="F21" s="14">
+        <v>60</v>
+      </c>
       <c r="G21" s="10" t="s">
         <v>156</v>
       </c>
@@ -11188,7 +11856,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -11341,7 +12009,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>2</v>
@@ -11720,7 +12388,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -12034,7 +12702,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -12187,7 +12855,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C9" s="33" t="s">
         <v>2</v>
@@ -12455,7 +13123,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -12770,7 +13438,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="25"/>
@@ -13124,7 +13792,7 @@
         <v>208</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>40</v>
@@ -13200,10 +13868,10 @@
     </row>
     <row r="8" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>269</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>48</v>
@@ -13341,9 +14009,9 @@
     <col min="6" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="139" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="130" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="36" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
@@ -13353,7 +14021,7 @@
       <c r="G1" s="38"/>
       <c r="H1" s="38"/>
     </row>
-    <row r="2" spans="1:8" s="139" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="130" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
         <v>130</v>
       </c>
@@ -13374,273 +14042,273 @@
       <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="140">
+      <c r="A3" s="131">
         <v>45486</v>
       </c>
-      <c r="B3" s="141" t="s">
-        <v>274</v>
-      </c>
-      <c r="C3" s="141" t="s">
+      <c r="B3" s="132" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="132" t="s">
         <v>154</v>
       </c>
-      <c r="D3" s="142">
+      <c r="D3" s="133">
         <v>100</v>
       </c>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="132"/>
     </row>
     <row r="4" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="143">
+      <c r="A4" s="134">
         <v>46158</v>
       </c>
-      <c r="B4" s="144" t="s">
-        <v>274</v>
-      </c>
-      <c r="C4" s="144" t="s">
+      <c r="B4" s="135" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="135" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="145">
+      <c r="D4" s="136">
         <v>250</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
+      <c r="E4" s="135"/>
+      <c r="F4" s="135"/>
+      <c r="G4" s="135"/>
+      <c r="H4" s="135"/>
     </row>
     <row r="5" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="144"/>
-      <c r="B5" s="144"/>
-      <c r="C5" s="144"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="144"/>
-      <c r="F5" s="144"/>
-      <c r="G5" s="144"/>
-      <c r="H5" s="144"/>
+      <c r="A5" s="135"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="135"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="135"/>
+      <c r="F5" s="135"/>
+      <c r="G5" s="135"/>
+      <c r="H5" s="135"/>
     </row>
     <row r="6" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="144"/>
-      <c r="B6" s="144"/>
-      <c r="C6" s="144"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="144"/>
-      <c r="F6" s="144"/>
-      <c r="G6" s="144"/>
-      <c r="H6" s="144"/>
+      <c r="A6" s="135"/>
+      <c r="B6" s="135"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="135"/>
+      <c r="F6" s="135"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="135"/>
     </row>
     <row r="7" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="144"/>
-      <c r="B7" s="144"/>
-      <c r="C7" s="144"/>
-      <c r="D7" s="145"/>
-      <c r="E7" s="144"/>
-      <c r="F7" s="144"/>
-      <c r="G7" s="144"/>
-      <c r="H7" s="144"/>
+      <c r="A7" s="135"/>
+      <c r="B7" s="135"/>
+      <c r="C7" s="135"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="135"/>
+      <c r="F7" s="135"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="135"/>
     </row>
     <row r="8" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="144"/>
-      <c r="B8" s="144"/>
-      <c r="C8" s="144"/>
-      <c r="D8" s="145"/>
-      <c r="E8" s="144"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="144"/>
-      <c r="H8" s="144"/>
+      <c r="A8" s="135"/>
+      <c r="B8" s="135"/>
+      <c r="C8" s="135"/>
+      <c r="D8" s="136"/>
+      <c r="E8" s="135"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="135"/>
+      <c r="H8" s="135"/>
     </row>
     <row r="9" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
-      <c r="B9" s="144"/>
-      <c r="C9" s="144"/>
-      <c r="D9" s="145"/>
-      <c r="E9" s="144"/>
-      <c r="F9" s="144"/>
-      <c r="G9" s="144"/>
-      <c r="H9" s="144"/>
+      <c r="A9" s="135"/>
+      <c r="B9" s="135"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="135"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="135"/>
     </row>
     <row r="10" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="144"/>
-      <c r="B10" s="144"/>
-      <c r="C10" s="144"/>
-      <c r="D10" s="145"/>
-      <c r="E10" s="144"/>
-      <c r="F10" s="144"/>
-      <c r="G10" s="144"/>
-      <c r="H10" s="144"/>
+      <c r="A10" s="135"/>
+      <c r="B10" s="135"/>
+      <c r="C10" s="135"/>
+      <c r="D10" s="136"/>
+      <c r="E10" s="135"/>
+      <c r="F10" s="135"/>
+      <c r="G10" s="135"/>
+      <c r="H10" s="135"/>
     </row>
     <row r="11" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="144"/>
-      <c r="B11" s="144"/>
-      <c r="C11" s="144"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
+      <c r="A11" s="135"/>
+      <c r="B11" s="135"/>
+      <c r="C11" s="135"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="135"/>
+      <c r="F11" s="135"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="135"/>
     </row>
     <row r="12" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="144"/>
-      <c r="B12" s="144"/>
-      <c r="C12" s="144"/>
-      <c r="D12" s="145"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="144"/>
+      <c r="A12" s="135"/>
+      <c r="B12" s="135"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
     </row>
     <row r="13" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144"/>
-      <c r="B13" s="144"/>
-      <c r="C13" s="144"/>
-      <c r="D13" s="145"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="144"/>
+      <c r="A13" s="135"/>
+      <c r="B13" s="135"/>
+      <c r="C13" s="135"/>
+      <c r="D13" s="136"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
     </row>
     <row r="14" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="144"/>
-      <c r="B14" s="144"/>
-      <c r="C14" s="144"/>
-      <c r="D14" s="145"/>
-      <c r="E14" s="144"/>
-      <c r="F14" s="144"/>
-      <c r="G14" s="144"/>
-      <c r="H14" s="144"/>
+      <c r="A14" s="135"/>
+      <c r="B14" s="135"/>
+      <c r="C14" s="135"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
     </row>
     <row r="15" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="144"/>
-      <c r="B15" s="144"/>
-      <c r="C15" s="144"/>
-      <c r="D15" s="145"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="144"/>
+      <c r="A15" s="135"/>
+      <c r="B15" s="135"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
     </row>
     <row r="16" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="144"/>
-      <c r="B16" s="144"/>
-      <c r="C16" s="144"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="144"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="144"/>
+      <c r="A16" s="135"/>
+      <c r="B16" s="135"/>
+      <c r="C16" s="135"/>
+      <c r="D16" s="136"/>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
     </row>
     <row r="17" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="144"/>
-      <c r="B17" s="144"/>
-      <c r="C17" s="144"/>
-      <c r="D17" s="145"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="144"/>
-      <c r="G17" s="144"/>
-      <c r="H17" s="144"/>
+      <c r="A17" s="135"/>
+      <c r="B17" s="135"/>
+      <c r="C17" s="135"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
     </row>
     <row r="18" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="144"/>
-      <c r="B18" s="144"/>
-      <c r="C18" s="144"/>
-      <c r="D18" s="145"/>
-      <c r="E18" s="144"/>
-      <c r="F18" s="144"/>
-      <c r="G18" s="144"/>
-      <c r="H18" s="144"/>
+      <c r="A18" s="135"/>
+      <c r="B18" s="135"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="136"/>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
     </row>
     <row r="19" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="144"/>
-      <c r="B19" s="144"/>
-      <c r="C19" s="144"/>
-      <c r="D19" s="145"/>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
-      <c r="G19" s="144"/>
-      <c r="H19" s="144"/>
+      <c r="A19" s="135"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="135"/>
+      <c r="D19" s="136"/>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
     </row>
     <row r="20" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="144"/>
-      <c r="B20" s="144"/>
-      <c r="C20" s="144"/>
-      <c r="D20" s="145"/>
-      <c r="E20" s="144"/>
-      <c r="F20" s="144"/>
-      <c r="G20" s="144"/>
-      <c r="H20" s="144"/>
+      <c r="A20" s="135"/>
+      <c r="B20" s="135"/>
+      <c r="C20" s="135"/>
+      <c r="D20" s="136"/>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
     </row>
     <row r="21" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="144"/>
-      <c r="B21" s="144"/>
-      <c r="C21" s="144"/>
-      <c r="D21" s="145"/>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="144"/>
+      <c r="A21" s="135"/>
+      <c r="B21" s="135"/>
+      <c r="C21" s="135"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="135"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="135"/>
     </row>
     <row r="22" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="144"/>
-      <c r="B22" s="144"/>
-      <c r="C22" s="144"/>
-      <c r="D22" s="145"/>
-      <c r="E22" s="144"/>
-      <c r="F22" s="144"/>
-      <c r="G22" s="144"/>
-      <c r="H22" s="144"/>
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="135"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="135"/>
+      <c r="F22" s="135"/>
+      <c r="G22" s="135"/>
+      <c r="H22" s="135"/>
     </row>
     <row r="23" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="144"/>
-      <c r="B23" s="144"/>
-      <c r="C23" s="144"/>
-      <c r="D23" s="145"/>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="144"/>
+      <c r="A23" s="135"/>
+      <c r="B23" s="135"/>
+      <c r="C23" s="135"/>
+      <c r="D23" s="136"/>
+      <c r="E23" s="135"/>
+      <c r="F23" s="135"/>
+      <c r="G23" s="135"/>
+      <c r="H23" s="135"/>
     </row>
     <row r="24" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="144"/>
-      <c r="B24" s="144"/>
-      <c r="C24" s="144"/>
-      <c r="D24" s="145"/>
-      <c r="E24" s="144"/>
-      <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="144"/>
+      <c r="A24" s="135"/>
+      <c r="B24" s="135"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="136"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
     </row>
     <row r="25" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="144"/>
-      <c r="B25" s="144"/>
-      <c r="C25" s="144"/>
-      <c r="D25" s="145"/>
-      <c r="E25" s="144"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="144"/>
-      <c r="H25" s="144"/>
+      <c r="A25" s="135"/>
+      <c r="B25" s="135"/>
+      <c r="C25" s="135"/>
+      <c r="D25" s="136"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="135"/>
+      <c r="H25" s="135"/>
     </row>
     <row r="26" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="144"/>
-      <c r="B26" s="144"/>
-      <c r="C26" s="144"/>
-      <c r="D26" s="145"/>
-      <c r="E26" s="144"/>
-      <c r="F26" s="144"/>
-      <c r="G26" s="144"/>
-      <c r="H26" s="144"/>
+      <c r="A26" s="135"/>
+      <c r="B26" s="135"/>
+      <c r="C26" s="135"/>
+      <c r="D26" s="136"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="135"/>
+      <c r="G26" s="135"/>
+      <c r="H26" s="135"/>
     </row>
     <row r="27" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="146"/>
-      <c r="B27" s="146"/>
-      <c r="C27" s="146"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="146"/>
-      <c r="F27" s="146"/>
-      <c r="G27" s="146"/>
-      <c r="H27" s="146"/>
+      <c r="A27" s="137"/>
+      <c r="B27" s="137"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="138"/>
+      <c r="E27" s="137"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="137"/>
+      <c r="H27" s="137"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D28" s="148"/>
+      <c r="D28" s="139"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13719,68 +14387,705 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="4" width="6.6640625" style="15" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" customWidth="1"/>
-    <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
+    <col min="1" max="1" width="4.83203125" style="15" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="27"/>
+    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="149" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="155" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="156" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="17" t="s">
+      <c r="C2" s="156" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="156" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="156" t="s">
         <v>243</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="73" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="24"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="28"/>
-    </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30" t="s">
+    <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A3" s="157">
+        <v>1</v>
+      </c>
+      <c r="B3" s="157" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="157" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="159">
+        <v>2.1875000000000002E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="160">
+        <v>2</v>
+      </c>
+      <c r="B4" s="160" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="160" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="162">
+        <v>2.60416666666667E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A5" s="157">
+        <v>3</v>
+      </c>
+      <c r="B5" s="157" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="157" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="159">
+        <v>3.4143518518518498E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A6" s="160">
+        <v>4</v>
+      </c>
+      <c r="B6" s="160" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="160" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="162">
+        <v>2.8587962962962998E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A7" s="157">
+        <v>5</v>
+      </c>
+      <c r="B7" s="157" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="157" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="159">
+        <v>2.4305555555555599E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A8" s="160">
+        <v>6</v>
+      </c>
+      <c r="B8" s="160" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="160" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="162">
+        <v>3.59953703703704E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A9" s="157">
+        <v>7</v>
+      </c>
+      <c r="B9" s="157" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="157" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="159">
+        <v>2.7893518518518502E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10" s="160">
+        <v>8</v>
+      </c>
+      <c r="B10" s="160" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="160" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="162">
+        <v>3.3680555555555599E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A11" s="157">
+        <v>9</v>
+      </c>
+      <c r="B11" s="157" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="157" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="159">
+        <v>2.0949074074074099E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12" s="160">
+        <v>10</v>
+      </c>
+      <c r="B12" s="160" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="163" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="164" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="160" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="162">
+        <v>2.5810185185185198E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A13" s="157">
+        <v>11</v>
+      </c>
+      <c r="B13" s="157" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="157" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="159">
+        <v>2.7430555555555602E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A14" s="160">
+        <v>12</v>
+      </c>
+      <c r="B14" s="160" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="160" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="162">
+        <v>2.5810185185185198E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A15" s="157">
+        <v>13</v>
+      </c>
+      <c r="B15" s="157" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="158" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="158" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="157" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="159">
+        <v>2.9513888888888901E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="165">
+        <v>14</v>
+      </c>
+      <c r="B16" s="165" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="166" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="166" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="165" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="167">
+        <v>3.32175925925926E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="152"/>
+      <c r="B17" s="153" t="s">
         <v>244</v>
       </c>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="32">
-        <f>SUM(F3:F3)</f>
-        <v>0</v>
-      </c>
-    </row>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="154">
+        <f>SUM(F3:F16)</f>
+        <v>3.9525462962962991E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25"/>
+      <c r="C25"/>
+      <c r="D25"/>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28"/>
+      <c r="C28"/>
+      <c r="D28"/>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29"/>
+      <c r="C29"/>
+      <c r="D29"/>
+      <c r="F29"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="F31"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="F32"/>
+    </row>
+    <row r="33" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="35" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="38" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C3">
+    <cfRule type="expression" dxfId="57" priority="55">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="56">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3">
+    <cfRule type="expression" dxfId="55" priority="53">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="54" priority="54">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C4">
+    <cfRule type="expression" dxfId="53" priority="51">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="52">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D4">
+    <cfRule type="expression" dxfId="51" priority="49">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="50">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C5">
+    <cfRule type="expression" dxfId="49" priority="47">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="48">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="expression" dxfId="47" priority="45">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="46" priority="46">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6">
+    <cfRule type="expression" dxfId="45" priority="43">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="44">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6">
+    <cfRule type="expression" dxfId="43" priority="41">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="42" priority="42">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7">
+    <cfRule type="expression" dxfId="41" priority="39">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="40">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
+    <cfRule type="expression" dxfId="39" priority="37">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="38">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8">
+    <cfRule type="expression" dxfId="37" priority="35">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="36">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="35" priority="33">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="34">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9">
+    <cfRule type="expression" dxfId="33" priority="31">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="32">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9">
+    <cfRule type="expression" dxfId="31" priority="29">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="30">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C10">
+    <cfRule type="expression" dxfId="29" priority="27">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="28">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10">
+    <cfRule type="expression" dxfId="27" priority="25">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="26">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11">
+    <cfRule type="expression" dxfId="25" priority="23">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="24">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="expression" dxfId="23" priority="21">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="22">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C12">
+    <cfRule type="expression" dxfId="21" priority="19">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="20">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D12">
+    <cfRule type="expression" dxfId="19" priority="17">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="18">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="expression" dxfId="17" priority="15">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="16">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="expression" dxfId="15" priority="13">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="14">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14">
+    <cfRule type="expression" dxfId="13" priority="11">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="12">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="expression" dxfId="11" priority="9">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="10">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C15">
+    <cfRule type="expression" dxfId="9" priority="7">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="8">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>MOD(ROW(),2)=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>MOD(ROW(),2)=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{25410629-9926-A94A-8DEA-173796F462EF}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{51A86A37-4D80-C742-9F9D-DBAB1BBBF262}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{1BB26EAD-BC11-8F41-AAB4-2AB641D5E159}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{3C469BEB-F1C9-7E4E-B2C4-91B89BD3FBE0}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{4C4BB4C6-D7A9-5448-8D70-C170771329C2}"/>
+    <hyperlink ref="D5" r:id="rId6" xr:uid="{DEB078E8-28BF-7C4E-8BEA-FF9AB7AE0B93}"/>
+    <hyperlink ref="C6" r:id="rId7" xr:uid="{D5B568C3-87D4-A94C-949B-127BA6F87614}"/>
+    <hyperlink ref="D6" r:id="rId8" xr:uid="{B15C33EF-691B-9D4F-A3BC-9B3982227CDE}"/>
+    <hyperlink ref="C7" r:id="rId9" xr:uid="{36088FEC-E769-0C44-8A49-92B2647BFB83}"/>
+    <hyperlink ref="D7" r:id="rId10" xr:uid="{2C94AEC3-3E53-294C-B1AB-F84AE5BC1D80}"/>
+    <hyperlink ref="C8" r:id="rId11" xr:uid="{06F0413F-F712-AC4C-9F0E-13F202CC7B6A}"/>
+    <hyperlink ref="D8" r:id="rId12" xr:uid="{8A75058B-1B7E-3F4D-BB4A-94700B5E83DD}"/>
+    <hyperlink ref="C9" r:id="rId13" xr:uid="{8A56B0FC-40A7-E94A-8D95-B9CBC050B784}"/>
+    <hyperlink ref="D9" r:id="rId14" xr:uid="{5C3A2765-3BEE-7042-92FE-EF34ADA8D968}"/>
+    <hyperlink ref="C10" r:id="rId15" xr:uid="{FBFCCA03-69E4-CB41-B7FB-3382EF84E574}"/>
+    <hyperlink ref="D10" r:id="rId16" xr:uid="{15DBDF7B-7D4A-C541-9657-A8CFCC3FF71E}"/>
+    <hyperlink ref="C11" r:id="rId17" xr:uid="{E41F4D2A-B475-114E-BBB7-42E522418218}"/>
+    <hyperlink ref="D11" r:id="rId18" xr:uid="{259D3AFB-D92F-B444-A10A-6756580F9930}"/>
+    <hyperlink ref="C12" r:id="rId19" xr:uid="{EF75B0D6-8328-8F4C-9AE8-9ECF606C459A}"/>
+    <hyperlink ref="D12" r:id="rId20" xr:uid="{1C5CCE95-3106-CB4E-A846-1F7787B725D0}"/>
+    <hyperlink ref="C13" r:id="rId21" xr:uid="{FEF1C916-BC48-A443-81A8-28247F42A2A2}"/>
+    <hyperlink ref="D13" r:id="rId22" xr:uid="{D854AB63-19A5-6745-8468-B6C1D632F760}"/>
+    <hyperlink ref="C14" r:id="rId23" xr:uid="{1080BC69-4EDF-6841-9B5B-F8B92C46F498}"/>
+    <hyperlink ref="D14" r:id="rId24" xr:uid="{7CCA3E16-A9BC-0E44-AFF4-0DD5D6BAF56D}"/>
+    <hyperlink ref="C15" r:id="rId25" xr:uid="{FCA2E2D6-0ED8-F347-A02E-366EE169C5CD}"/>
+    <hyperlink ref="D15" r:id="rId26" xr:uid="{70AE9A16-25BE-FE40-808F-6E47A2F5FCA9}"/>
+    <hyperlink ref="C16" r:id="rId27" xr:uid="{BEC67237-B25D-0147-BB2F-633884A6E50D}"/>
+    <hyperlink ref="D16" r:id="rId28" xr:uid="{DEE84DE1-B608-0A4F-8CB0-2A4C8BACB00A}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -13799,14 +15104,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="130" t="s">
-        <v>246</v>
-      </c>
-      <c r="B1" s="131"/>
-      <c r="C1" s="131"/>
-      <c r="D1" s="131"/>
-      <c r="E1" s="131"/>
-      <c r="F1" s="132"/>
+      <c r="A1" s="140" t="s">
+        <v>245</v>
+      </c>
+      <c r="B1" s="141"/>
+      <c r="C1" s="141"/>
+      <c r="D1" s="141"/>
+      <c r="E1" s="141"/>
+      <c r="F1" s="142"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
@@ -14013,7 +15318,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C12" s="83" t="s">
         <v>2</v>
@@ -14109,14 +15414,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="133" t="s">
-        <v>248</v>
-      </c>
-      <c r="B17" s="134"/>
-      <c r="C17" s="134"/>
-      <c r="D17" s="134"/>
-      <c r="E17" s="134"/>
-      <c r="F17" s="135"/>
+      <c r="A17" s="143" t="s">
+        <v>247</v>
+      </c>
+      <c r="B17" s="144"/>
+      <c r="C17" s="144"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="144"/>
+      <c r="F17" s="145"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="79">
@@ -14456,14 +15761,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="136" t="s">
-        <v>267</v>
-      </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="138"/>
+      <c r="A1" s="146" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
@@ -14709,7 +16014,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C14" s="33" t="s">
         <v>2</v>

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77248D52-1412-BB4D-88BC-FA96F528D925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AB469F-44D0-C04C-B134-2B26CDF0C520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="3660" windowWidth="28980" windowHeight="17200" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3820" yWindow="3660" windowWidth="29580" windowHeight="17160" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -41,6 +41,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'2026-05-14 Fat Shallot'!$A$1:$F$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'2026-05-16 Fat Shallot'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'2026-06-21 Chicago Union'!$A$1:$F$18</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="276">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -915,11 +916,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[m]:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="m:ss"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -1907,7 +1909,7 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2290,6 +2292,41 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2317,55 +2354,25 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2374,439 +2381,7 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="58">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE0E0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -11751,7 +11326,7 @@
         <v>155</v>
       </c>
       <c r="E21" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" s="14">
         <v>60</v>
@@ -14387,7 +13962,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="15" customWidth="1"/>
@@ -14398,29 +13973,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="150" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="152"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="142" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="156" t="s">
+      <c r="B2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="156" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="156" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="156" t="s">
+      <c r="C2" s="143" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="143" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="143" t="s">
         <v>243</v>
       </c>
       <c r="F2" s="73" t="s">
@@ -14428,303 +14003,317 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A3" s="157">
+      <c r="A3" s="144">
         <v>1</v>
       </c>
-      <c r="B3" s="157" t="s">
+      <c r="B3" s="144" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="158" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="158" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="157" t="s">
+      <c r="C3" s="145" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="145" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="159">
+      <c r="F3" s="146">
         <v>2.1875000000000002E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="160">
-        <v>2</v>
-      </c>
-      <c r="B4" s="160" t="s">
+      <c r="A4" s="147">
+        <v>2</v>
+      </c>
+      <c r="B4" s="147" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="160" t="s">
+      <c r="C4" s="148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="148" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="162">
+      <c r="F4" s="149">
         <v>2.60416666666667E-3</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A5" s="157">
-        <v>3</v>
-      </c>
-      <c r="B5" s="157" t="s">
+      <c r="A5" s="144">
+        <v>3</v>
+      </c>
+      <c r="B5" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="158" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="158" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="157" t="s">
+      <c r="C5" s="145" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="145" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="159">
+      <c r="F5" s="146">
         <v>3.4143518518518498E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A6" s="160">
+      <c r="A6" s="147">
         <v>4</v>
       </c>
-      <c r="B6" s="160" t="s">
+      <c r="B6" s="147" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="160" t="s">
+      <c r="C6" s="148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="148" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="162">
+      <c r="F6" s="149">
         <v>2.8587962962962998E-3</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A7" s="157">
+      <c r="A7" s="144">
         <v>5</v>
       </c>
-      <c r="B7" s="157" t="s">
+      <c r="B7" s="144" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="158" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="158" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="157" t="s">
+      <c r="C7" s="145" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="145" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="159">
+      <c r="F7" s="146">
         <v>2.4305555555555599E-3</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A8" s="160">
+      <c r="A8" s="147">
         <v>6</v>
       </c>
-      <c r="B8" s="160" t="s">
+      <c r="B8" s="147" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="160" t="s">
+      <c r="C8" s="148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="148" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="162">
+      <c r="F8" s="149">
         <v>3.59953703703704E-3</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A9" s="157">
+      <c r="A9" s="144">
         <v>7</v>
       </c>
-      <c r="B9" s="157" t="s">
+      <c r="B9" s="144" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="158" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="158" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="157" t="s">
+      <c r="C9" s="145" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="145" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="159">
+      <c r="F9" s="146">
         <v>2.7893518518518502E-3</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A10" s="160">
+      <c r="A10" s="147">
         <v>8</v>
       </c>
-      <c r="B10" s="160" t="s">
+      <c r="B10" s="147" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="160" t="s">
+      <c r="C10" s="148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="148" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="162">
+      <c r="F10" s="149">
         <v>3.3680555555555599E-3</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A11" s="157">
+      <c r="A11" s="144">
         <v>9</v>
       </c>
-      <c r="B11" s="157" t="s">
+      <c r="B11" s="144" t="s">
         <v>127</v>
       </c>
-      <c r="C11" s="158" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="158" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="157" t="s">
+      <c r="C11" s="145" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="145" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="159">
+      <c r="F11" s="146">
         <v>2.0949074074074099E-3</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A12" s="160">
+      <c r="A12" s="147">
         <v>10</v>
       </c>
-      <c r="B12" s="160" t="s">
+      <c r="B12" s="147" t="s">
+        <v>85</v>
+      </c>
+      <c r="C12" s="148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="148" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="147" t="s">
+        <v>48</v>
+      </c>
+      <c r="F12" s="162">
+        <v>1.9791666666666668E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A13" s="144">
+        <v>11</v>
+      </c>
+      <c r="B13" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="C12" s="163" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="164" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="160" t="s">
+      <c r="C13" s="163" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="164" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="162">
+      <c r="F13" s="146">
         <v>2.5810185185185198E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A13" s="157">
-        <v>11</v>
-      </c>
-      <c r="B13" s="157" t="s">
+    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A14" s="147">
+        <v>12</v>
+      </c>
+      <c r="B14" s="147" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="158" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="158" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="157" t="s">
+      <c r="C14" s="148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="148" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="159">
+      <c r="F14" s="149">
         <v>2.7430555555555602E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A14" s="160">
-        <v>12</v>
-      </c>
-      <c r="B14" s="160" t="s">
+    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A15" s="144">
+        <v>13</v>
+      </c>
+      <c r="B15" s="144" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="160" t="s">
+      <c r="C15" s="145" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="145" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="162">
+      <c r="F15" s="146">
         <v>2.5810185185185198E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A15" s="157">
-        <v>13</v>
-      </c>
-      <c r="B15" s="157" t="s">
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A16" s="147">
+        <v>14</v>
+      </c>
+      <c r="B16" s="147" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="158" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="158" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="157" t="s">
+      <c r="C16" s="148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="148" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="159">
+      <c r="F16" s="149">
         <v>2.9513888888888901E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="165">
-        <v>14</v>
-      </c>
-      <c r="B16" s="165" t="s">
+    <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="165">
+        <v>15</v>
+      </c>
+      <c r="B17" s="165" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="166" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="166" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="165" t="s">
+      <c r="C17" s="166" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="166" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="165" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="167">
+      <c r="F17" s="167">
         <v>3.32175925925926E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="152"/>
-      <c r="B17" s="153" t="s">
+    <row r="18" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="140"/>
+      <c r="B18" s="141" t="s">
         <v>244</v>
       </c>
-      <c r="C17" s="153"/>
-      <c r="D17" s="153"/>
-      <c r="E17" s="153"/>
-      <c r="F17" s="154">
-        <f>SUM(F3:F16)</f>
-        <v>3.9525462962962991E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="F18"/>
+      <c r="C18" s="141"/>
+      <c r="D18" s="141"/>
+      <c r="E18" s="141"/>
+      <c r="F18" s="168">
+        <f>SUM(F3:F17)</f>
+        <v>4.1504629629629655E-2</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19"/>
@@ -14828,227 +14417,12 @@
     <row r="48" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3">
-    <cfRule type="expression" dxfId="57" priority="55">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="56" priority="56">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3">
-    <cfRule type="expression" dxfId="55" priority="53">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="54">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C4">
-    <cfRule type="expression" dxfId="53" priority="51">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="52">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="expression" dxfId="51" priority="49">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="50">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C5">
-    <cfRule type="expression" dxfId="49" priority="47">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="48">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="expression" dxfId="47" priority="45">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="46">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6">
-    <cfRule type="expression" dxfId="45" priority="43">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="44" priority="44">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="43" priority="41">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="42">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
-    <cfRule type="expression" dxfId="41" priority="39">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="40">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7">
-    <cfRule type="expression" dxfId="39" priority="37">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="38">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8">
-    <cfRule type="expression" dxfId="37" priority="35">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="36">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="35" priority="33">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="34">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9">
-    <cfRule type="expression" dxfId="33" priority="31">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="32" priority="32">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9">
-    <cfRule type="expression" dxfId="31" priority="29">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C10">
-    <cfRule type="expression" dxfId="29" priority="27">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="28">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10">
-    <cfRule type="expression" dxfId="27" priority="25">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11">
-    <cfRule type="expression" dxfId="25" priority="23">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="24">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D11">
-    <cfRule type="expression" dxfId="23" priority="21">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="22">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12">
-    <cfRule type="expression" dxfId="21" priority="19">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="20" priority="20">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D12">
-    <cfRule type="expression" dxfId="19" priority="17">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="18">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C13">
-    <cfRule type="expression" dxfId="17" priority="15">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="16">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13">
-    <cfRule type="expression" dxfId="15" priority="13">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="14" priority="14">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="expression" dxfId="13" priority="11">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="12">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D14">
-    <cfRule type="expression" dxfId="11" priority="9">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="10">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C15">
-    <cfRule type="expression" dxfId="9" priority="7">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="8">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="expression" dxfId="7" priority="5">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="6">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16">
-    <cfRule type="expression" dxfId="5" priority="3">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16">
+  <conditionalFormatting sqref="C3:D17">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -15075,16 +14449,16 @@
     <hyperlink ref="D10" r:id="rId16" xr:uid="{15DBDF7B-7D4A-C541-9657-A8CFCC3FF71E}"/>
     <hyperlink ref="C11" r:id="rId17" xr:uid="{E41F4D2A-B475-114E-BBB7-42E522418218}"/>
     <hyperlink ref="D11" r:id="rId18" xr:uid="{259D3AFB-D92F-B444-A10A-6756580F9930}"/>
-    <hyperlink ref="C12" r:id="rId19" xr:uid="{EF75B0D6-8328-8F4C-9AE8-9ECF606C459A}"/>
-    <hyperlink ref="D12" r:id="rId20" xr:uid="{1C5CCE95-3106-CB4E-A846-1F7787B725D0}"/>
-    <hyperlink ref="C13" r:id="rId21" xr:uid="{FEF1C916-BC48-A443-81A8-28247F42A2A2}"/>
-    <hyperlink ref="D13" r:id="rId22" xr:uid="{D854AB63-19A5-6745-8468-B6C1D632F760}"/>
-    <hyperlink ref="C14" r:id="rId23" xr:uid="{1080BC69-4EDF-6841-9B5B-F8B92C46F498}"/>
-    <hyperlink ref="D14" r:id="rId24" xr:uid="{7CCA3E16-A9BC-0E44-AFF4-0DD5D6BAF56D}"/>
-    <hyperlink ref="C15" r:id="rId25" xr:uid="{FCA2E2D6-0ED8-F347-A02E-366EE169C5CD}"/>
-    <hyperlink ref="D15" r:id="rId26" xr:uid="{70AE9A16-25BE-FE40-808F-6E47A2F5FCA9}"/>
-    <hyperlink ref="C16" r:id="rId27" xr:uid="{BEC67237-B25D-0147-BB2F-633884A6E50D}"/>
-    <hyperlink ref="D16" r:id="rId28" xr:uid="{DEE84DE1-B608-0A4F-8CB0-2A4C8BACB00A}"/>
+    <hyperlink ref="C13" r:id="rId19" xr:uid="{EF75B0D6-8328-8F4C-9AE8-9ECF606C459A}"/>
+    <hyperlink ref="D13" r:id="rId20" xr:uid="{1C5CCE95-3106-CB4E-A846-1F7787B725D0}"/>
+    <hyperlink ref="C14" r:id="rId21" xr:uid="{FEF1C916-BC48-A443-81A8-28247F42A2A2}"/>
+    <hyperlink ref="D14" r:id="rId22" xr:uid="{D854AB63-19A5-6745-8468-B6C1D632F760}"/>
+    <hyperlink ref="C15" r:id="rId23" xr:uid="{1080BC69-4EDF-6841-9B5B-F8B92C46F498}"/>
+    <hyperlink ref="D15" r:id="rId24" xr:uid="{7CCA3E16-A9BC-0E44-AFF4-0DD5D6BAF56D}"/>
+    <hyperlink ref="C16" r:id="rId25" xr:uid="{FCA2E2D6-0ED8-F347-A02E-366EE169C5CD}"/>
+    <hyperlink ref="D16" r:id="rId26" xr:uid="{70AE9A16-25BE-FE40-808F-6E47A2F5FCA9}"/>
+    <hyperlink ref="C17" r:id="rId27" xr:uid="{BEC67237-B25D-0147-BB2F-633884A6E50D}"/>
+    <hyperlink ref="D17" r:id="rId28" xr:uid="{DEE84DE1-B608-0A4F-8CB0-2A4C8BACB00A}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -15104,14 +14478,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="140" t="s">
+      <c r="A1" s="153" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="141"/>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
-      <c r="F1" s="142"/>
+      <c r="B1" s="154"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="155"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
@@ -15414,14 +14788,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="143" t="s">
+      <c r="A17" s="156" t="s">
         <v>247</v>
       </c>
-      <c r="B17" s="144"/>
-      <c r="C17" s="144"/>
-      <c r="D17" s="144"/>
-      <c r="E17" s="144"/>
-      <c r="F17" s="145"/>
+      <c r="B17" s="157"/>
+      <c r="C17" s="157"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="157"/>
+      <c r="F17" s="158"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="79">
@@ -15761,14 +15135,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="159" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148"/>
+      <c r="B1" s="160"/>
+      <c r="C1" s="160"/>
+      <c r="D1" s="160"/>
+      <c r="E1" s="160"/>
+      <c r="F1" s="161"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14AB469F-44D0-C04C-B134-2B26CDF0C520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5126F96E-E329-EE48-BC56-1DDA34667B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3820" yWindow="3660" windowWidth="29580" windowHeight="17160" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="3660" windowWidth="29580" windowHeight="17160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -916,12 +916,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[m]:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="m:ss"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -1909,7 +1908,7 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2303,19 +2302,16 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="7" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2354,27 +2350,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2425,10 +2401,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2714,6 +2686,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{D9F25F04-5CE3-F24E-8562-3BBFBB697FF2}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;36b42ed8-0a47-4139-8b53-ba6df3068491&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD49"/>
@@ -13973,14 +13967,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="149" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="152"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="142" t="s">
@@ -14009,37 +14003,39 @@
       <c r="B3" s="144" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="145" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="145" t="s">
+      <c r="C3" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="161" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="146">
+      <c r="F3" s="145">
+        <f>VLOOKUP(B3,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.1875000000000002E-3</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="147">
-        <v>2</v>
-      </c>
-      <c r="B4" s="147" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="148" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="148" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="147" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="149">
-        <v>2.60416666666667E-3</v>
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="146" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="146" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="145">
+        <f>VLOOKUP(B4,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>2.9513888888888888E-3</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.25">
@@ -14049,37 +14045,39 @@
       <c r="B5" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="145" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="145" t="s">
+      <c r="C5" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="161" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="146">
-        <v>3.4143518518518498E-3</v>
+      <c r="F5" s="145">
+        <f>VLOOKUP(B5,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>3.414351851851852E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A6" s="147">
+      <c r="A6" s="146">
         <v>4</v>
       </c>
-      <c r="B6" s="147" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="148" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="148" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="147" t="s">
+      <c r="B6" s="146" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="146" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="149">
-        <v>2.8587962962962998E-3</v>
+      <c r="F6" s="145">
+        <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>2.6041666666666665E-3</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.25">
@@ -14089,37 +14087,39 @@
       <c r="B7" s="144" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="145" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="145" t="s">
+      <c r="C7" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="161" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="146">
-        <v>2.4305555555555599E-3</v>
+      <c r="F7" s="145">
+        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>2.4305555555555556E-3</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A8" s="147">
+      <c r="A8" s="146">
         <v>6</v>
       </c>
-      <c r="B8" s="147" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="148" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="148" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="147" t="s">
+      <c r="B8" s="146" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="149">
-        <v>3.59953703703704E-3</v>
+      <c r="F8" s="145">
+        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>2.5810185185185185E-3</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.25">
@@ -14127,39 +14127,41 @@
         <v>7</v>
       </c>
       <c r="B9" s="144" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="145" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="145" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="161" t="s">
         <v>3</v>
       </c>
       <c r="E9" s="144" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="146">
-        <v>2.7893518518518502E-3</v>
+        <v>36</v>
+      </c>
+      <c r="F9" s="145">
+        <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>2.6041666666666665E-3</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A10" s="147">
+      <c r="A10" s="146">
         <v>8</v>
       </c>
-      <c r="B10" s="147" t="s">
-        <v>106</v>
-      </c>
-      <c r="C10" s="148" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="148" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="147" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="149">
-        <v>3.3680555555555599E-3</v>
+      <c r="B10" s="146" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="146" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="145">
+        <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>1.9791666666666668E-3</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.25">
@@ -14167,39 +14169,41 @@
         <v>9</v>
       </c>
       <c r="B11" s="144" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="145" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="145" t="s">
+        <v>106</v>
+      </c>
+      <c r="C11" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="161" t="s">
         <v>3</v>
       </c>
       <c r="E11" s="144" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="145">
+        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>3.3680555555555556E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="146" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="146" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="146">
-        <v>2.0949074074074099E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A12" s="147">
-        <v>10</v>
-      </c>
-      <c r="B12" s="147" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="148" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="148" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="147" t="s">
-        <v>48</v>
-      </c>
-      <c r="F12" s="162">
-        <v>1.9791666666666668E-3</v>
+      <c r="F12" s="145">
+        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>2.7893518518518519E-3</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.25">
@@ -14209,37 +14213,39 @@
       <c r="B13" s="144" t="s">
         <v>246</v>
       </c>
-      <c r="C13" s="163" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="164" t="s">
+      <c r="C13" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="161" t="s">
         <v>3</v>
       </c>
       <c r="E13" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="146">
-        <v>2.5810185185185198E-3</v>
+      <c r="F13" s="145">
+        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>2.5810185185185185E-3</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A14" s="147">
+      <c r="A14" s="146">
         <v>12</v>
       </c>
-      <c r="B14" s="147" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="148" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="148" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="147" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="149">
-        <v>2.7430555555555602E-3</v>
+      <c r="B14" s="146" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="146" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="145">
+        <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>2.8587962962962963E-3</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.25">
@@ -14247,59 +14253,62 @@
         <v>13</v>
       </c>
       <c r="B15" s="144" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="145" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="145" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="161" t="s">
         <v>3</v>
       </c>
       <c r="E15" s="144" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="145">
+        <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>2.0949074074074073E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="146" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="146" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="146">
-        <v>2.5810185185185198E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A16" s="147">
-        <v>14</v>
-      </c>
-      <c r="B16" s="147" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="148" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="148" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="147" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="149">
-        <v>2.9513888888888901E-3</v>
+      <c r="F16" s="145">
+        <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>2.7430555555555554E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="165">
+      <c r="A17" s="147">
         <v>15</v>
       </c>
-      <c r="B17" s="165" t="s">
+      <c r="B17" s="147" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="166" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="166" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="165" t="s">
+      <c r="C17" s="161" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="161" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="167">
-        <v>3.32175925925926E-3</v>
+      <c r="F17" s="145">
+        <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+        <v>3.3217592592592591E-3</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
@@ -14310,9 +14319,9 @@
       <c r="C18" s="141"/>
       <c r="D18" s="141"/>
       <c r="E18" s="141"/>
-      <c r="F18" s="168">
+      <c r="F18" s="148">
         <f>SUM(F3:F17)</f>
-        <v>4.1504629629629655E-2</v>
+        <v>4.0509259259259259E-2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -14459,6 +14468,8 @@
     <hyperlink ref="D16" r:id="rId26" xr:uid="{70AE9A16-25BE-FE40-808F-6E47A2F5FCA9}"/>
     <hyperlink ref="C17" r:id="rId27" xr:uid="{BEC67237-B25D-0147-BB2F-633884A6E50D}"/>
     <hyperlink ref="D17" r:id="rId28" xr:uid="{DEE84DE1-B608-0A4F-8CB0-2A4C8BACB00A}"/>
+    <hyperlink ref="C12" r:id="rId29" xr:uid="{A801D906-C97B-7647-85DE-7AC62D3FDE24}"/>
+    <hyperlink ref="D12" r:id="rId30" xr:uid="{FD4DE05E-0EBA-B341-B198-8973B5FC18C1}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -14478,14 +14489,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="153" t="s">
+      <c r="A1" s="152" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="154"/>
-      <c r="C1" s="154"/>
-      <c r="D1" s="154"/>
-      <c r="E1" s="154"/>
-      <c r="F1" s="155"/>
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="154"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
@@ -14788,14 +14799,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="156" t="s">
+      <c r="A17" s="155" t="s">
         <v>247</v>
       </c>
-      <c r="B17" s="157"/>
-      <c r="C17" s="157"/>
-      <c r="D17" s="157"/>
-      <c r="E17" s="157"/>
-      <c r="F17" s="158"/>
+      <c r="B17" s="156"/>
+      <c r="C17" s="156"/>
+      <c r="D17" s="156"/>
+      <c r="E17" s="156"/>
+      <c r="F17" s="157"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="79">
@@ -15135,14 +15146,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="159" t="s">
+      <c r="A1" s="158" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="160"/>
-      <c r="C1" s="160"/>
-      <c r="D1" s="160"/>
-      <c r="E1" s="160"/>
-      <c r="F1" s="161"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="160"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5126F96E-E329-EE48-BC56-1DDA34667B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1D19171-38FB-794F-8C52-5E7CC0C9AB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="3660" windowWidth="29580" windowHeight="17160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -922,7 +922,7 @@
     <numFmt numFmtId="165" formatCode="[m]:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1070,8 +1070,15 @@
       <name val="Courier New"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1102,8 +1109,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="62">
+  <borders count="71">
     <border>
       <left/>
       <right/>
@@ -1864,16 +1877,75 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1883,14 +1955,72 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -1908,7 +2038,7 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="174">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2292,36 +2422,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2350,7 +2455,64 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -13966,360 +14128,360 @@
     <col min="6" max="6" width="11.83203125" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="149" t="s">
+    <row r="1" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="152" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
-    </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="142" t="s">
+      <c r="B1" s="153"/>
+      <c r="C1" s="153"/>
+      <c r="D1" s="153"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="154"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="163" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="164" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="143" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="143" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="143" t="s">
+      <c r="C2" s="164" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="164" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="164" t="s">
         <v>243</v>
       </c>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="165" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A3" s="144">
+      <c r="A3" s="156">
         <v>1</v>
       </c>
-      <c r="B3" s="144" t="s">
+      <c r="B3" s="155" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="144" t="s">
+      <c r="C3" s="170" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="170" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="145">
+      <c r="F3" s="157">
         <f>VLOOKUP(B3,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.1875000000000002E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="146">
-        <v>2</v>
-      </c>
-      <c r="B4" s="146" t="s">
+    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+      <c r="A4" s="158">
+        <v>2</v>
+      </c>
+      <c r="B4" s="168" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="146" t="s">
+      <c r="C4" s="171" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="168" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="145">
+      <c r="F4" s="169">
         <f>VLOOKUP(B4,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A5" s="144">
-        <v>3</v>
-      </c>
-      <c r="B5" s="144" t="s">
+      <c r="A5" s="160">
+        <v>3</v>
+      </c>
+      <c r="B5" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="144" t="s">
+      <c r="C5" s="172" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="172" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="145">
+      <c r="F5" s="159">
         <f>VLOOKUP(B5,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.414351851851852E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A6" s="146">
+      <c r="A6" s="158">
         <v>4</v>
       </c>
-      <c r="B6" s="146" t="s">
+      <c r="B6" s="168" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="146" t="s">
+      <c r="C6" s="171" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="168" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="145">
+      <c r="F6" s="169">
         <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A7" s="144">
+      <c r="A7" s="160">
         <v>5</v>
       </c>
-      <c r="B7" s="144" t="s">
+      <c r="B7" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="144" t="s">
+      <c r="C7" s="172" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="172" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="145">
+      <c r="F7" s="159">
         <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A8" s="146">
+      <c r="A8" s="158">
         <v>6</v>
       </c>
-      <c r="B8" s="146" t="s">
+      <c r="B8" s="168" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="146" t="s">
+      <c r="C8" s="171" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="168" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="145">
+      <c r="F8" s="169">
         <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A9" s="144">
+      <c r="A9" s="160">
         <v>7</v>
       </c>
-      <c r="B9" s="144" t="s">
+      <c r="B9" s="141" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="144" t="s">
+      <c r="C9" s="172" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="172" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="145">
+      <c r="F9" s="159">
         <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A10" s="146">
+      <c r="A10" s="158">
         <v>8</v>
       </c>
-      <c r="B10" s="146" t="s">
+      <c r="B10" s="168" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="146" t="s">
+      <c r="C10" s="171" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="168" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="145">
+      <c r="F10" s="169">
         <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A11" s="144">
+      <c r="A11" s="160">
         <v>9</v>
       </c>
-      <c r="B11" s="144" t="s">
+      <c r="B11" s="141" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="144" t="s">
+      <c r="C11" s="172" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="172" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="145">
+      <c r="F11" s="159">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A12" s="146">
+      <c r="A12" s="158">
         <v>10</v>
       </c>
-      <c r="B12" s="146" t="s">
+      <c r="B12" s="168" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="146" t="s">
+      <c r="C12" s="171" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="168" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="145">
+      <c r="F12" s="169">
         <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A13" s="144">
+      <c r="A13" s="160">
         <v>11</v>
       </c>
-      <c r="B13" s="144" t="s">
+      <c r="B13" s="141" t="s">
         <v>246</v>
       </c>
-      <c r="C13" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="144" t="s">
+      <c r="C13" s="172" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="172" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="145">
+      <c r="F13" s="159">
         <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A14" s="146">
+      <c r="A14" s="158">
         <v>12</v>
       </c>
-      <c r="B14" s="146" t="s">
+      <c r="B14" s="168" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="146" t="s">
+      <c r="C14" s="171" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="168" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="145">
+      <c r="F14" s="169">
         <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A15" s="144">
+      <c r="A15" s="160">
         <v>13</v>
       </c>
-      <c r="B15" s="144" t="s">
+      <c r="B15" s="141" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="144" t="s">
+      <c r="C15" s="172" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="172" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="145">
+      <c r="F15" s="159">
         <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A16" s="146">
+      <c r="A16" s="158">
         <v>14</v>
       </c>
-      <c r="B16" s="146" t="s">
+      <c r="B16" s="168" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="146" t="s">
+      <c r="C16" s="171" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="168" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="145">
+      <c r="F16" s="169">
         <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="147">
+      <c r="A17" s="161">
         <v>15</v>
       </c>
-      <c r="B17" s="147" t="s">
+      <c r="B17" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="161" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="161" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="147" t="s">
+      <c r="C17" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="145">
+      <c r="F17" s="162">
         <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.3217592592592591E-3</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="140"/>
-      <c r="B18" s="141" t="s">
+      <c r="B18" s="166" t="s">
         <v>244</v>
       </c>
-      <c r="C18" s="141"/>
-      <c r="D18" s="141"/>
-      <c r="E18" s="141"/>
-      <c r="F18" s="148">
+      <c r="C18" s="166"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="166"/>
+      <c r="F18" s="167">
         <f>SUM(F3:F17)</f>
         <v>4.0509259259259259E-2</v>
       </c>
@@ -14428,8 +14590,9 @@
     <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B18:E18"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:D17">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -14489,14 +14652,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="143" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="154"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
+      <c r="F1" s="145"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
@@ -14799,14 +14962,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="155" t="s">
+      <c r="A17" s="146" t="s">
         <v>247</v>
       </c>
-      <c r="B17" s="156"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="156"/>
-      <c r="E17" s="156"/>
-      <c r="F17" s="157"/>
+      <c r="B17" s="147"/>
+      <c r="C17" s="147"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="148"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="79">
@@ -15146,14 +15309,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="149" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="160"/>
+      <c r="B1" s="150"/>
+      <c r="C1" s="150"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
+      <c r="F1" s="151"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1D19171-38FB-794F-8C52-5E7CC0C9AB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{47D57BCE-B2EE-9944-87DE-03D431F0FE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="3660" windowWidth="29580" windowHeight="17160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'2026-05-14 Fat Shallot'!$A$1:$F$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'2026-05-16 Fat Shallot'!$A$1:$F$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'2026-06-21 Chicago Union'!$A$1:$F$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'2026-06-21 Chicago Union'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2247" uniqueCount="276">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -922,7 +922,7 @@
     <numFmt numFmtId="165" formatCode="[m]:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1077,8 +1077,20 @@
       <name val="Courier New"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Bradley Hand Bold"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color rgb="FF000000"/>
+      <name val="Brush Script MT"/>
+      <family val="4"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1106,12 +1118,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2038,7 +2044,7 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="174">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2428,42 +2434,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2497,22 +2467,67 @@
     <xf numFmtId="0" fontId="20" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="59" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2873,7 +2888,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="6" customWidth="1"/>
@@ -2892,7 +2907,7 @@
     <col min="29" max="30" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -2926,7 +2941,7 @@
       <c r="AC1" s="37"/>
       <c r="AD1" s="37"/>
     </row>
-    <row r="2" spans="1:30" s="3" customFormat="1" ht="56" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" s="3" customFormat="1" ht="56" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="126" t="s">
         <v>1</v>
       </c>
@@ -3018,7 +3033,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="22" customHeight="1" thickTop="1">
       <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
@@ -3075,7 +3090,7 @@
       <c r="AC3" s="9"/>
       <c r="AD3" s="9"/>
     </row>
-    <row r="4" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="22" customHeight="1">
       <c r="A4" s="101" t="s">
         <v>34</v>
       </c>
@@ -3132,7 +3147,7 @@
       <c r="AC4" s="101"/>
       <c r="AD4" s="101"/>
     </row>
-    <row r="5" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="22" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>246</v>
       </c>
@@ -3205,7 +3220,7 @@
       <c r="AC5" s="10"/>
       <c r="AD5" s="10"/>
     </row>
-    <row r="6" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="22" customHeight="1">
       <c r="A6" s="101" t="s">
         <v>41</v>
       </c>
@@ -3266,7 +3281,7 @@
       <c r="AC6" s="101"/>
       <c r="AD6" s="101"/>
     </row>
-    <row r="7" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="22" customHeight="1">
       <c r="A7" s="10" t="s">
         <v>44</v>
       </c>
@@ -3331,7 +3346,7 @@
       <c r="AC7" s="10"/>
       <c r="AD7" s="10"/>
     </row>
-    <row r="8" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="22" customHeight="1">
       <c r="A8" s="101" t="s">
         <v>46</v>
       </c>
@@ -3404,7 +3419,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="22" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>49</v>
       </c>
@@ -3493,7 +3508,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="22" customHeight="1">
       <c r="A10" s="101" t="s">
         <v>50</v>
       </c>
@@ -3548,7 +3563,7 @@
       <c r="AC10" s="101"/>
       <c r="AD10" s="101"/>
     </row>
-    <row r="11" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="22" customHeight="1">
       <c r="A11" s="10" t="s">
         <v>52</v>
       </c>
@@ -3617,7 +3632,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="22" customHeight="1">
       <c r="A12" s="101" t="s">
         <v>54</v>
       </c>
@@ -3684,7 +3699,7 @@
       <c r="AC12" s="101"/>
       <c r="AD12" s="101"/>
     </row>
-    <row r="13" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="22" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>57</v>
       </c>
@@ -3741,7 +3756,7 @@
       <c r="AC13" s="10"/>
       <c r="AD13" s="10"/>
     </row>
-    <row r="14" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="22" customHeight="1">
       <c r="A14" s="101" t="s">
         <v>61</v>
       </c>
@@ -3794,7 +3809,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="22" customHeight="1">
       <c r="A15" s="10" t="s">
         <v>63</v>
       </c>
@@ -3875,7 +3890,7 @@
       </c>
       <c r="AD15" s="10"/>
     </row>
-    <row r="16" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="22" customHeight="1">
       <c r="A16" s="101" t="s">
         <v>65</v>
       </c>
@@ -3944,7 +3959,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="22" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>67</v>
       </c>
@@ -3999,7 +4014,7 @@
       <c r="AC17" s="10"/>
       <c r="AD17" s="10"/>
     </row>
-    <row r="18" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="22" customHeight="1">
       <c r="A18" s="101" t="s">
         <v>70</v>
       </c>
@@ -4070,7 +4085,7 @@
       <c r="AC18" s="101"/>
       <c r="AD18" s="101"/>
     </row>
-    <row r="19" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="22" customHeight="1">
       <c r="A19" s="10" t="s">
         <v>72</v>
       </c>
@@ -4135,7 +4150,7 @@
       <c r="AC19" s="10"/>
       <c r="AD19" s="10"/>
     </row>
-    <row r="20" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="22" customHeight="1">
       <c r="A20" s="101" t="s">
         <v>74</v>
       </c>
@@ -4206,7 +4221,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" ht="22" customHeight="1">
       <c r="A21" s="10" t="s">
         <v>76</v>
       </c>
@@ -4259,7 +4274,7 @@
       <c r="AC21" s="10"/>
       <c r="AD21" s="10"/>
     </row>
-    <row r="22" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="22" customHeight="1">
       <c r="A22" s="101" t="s">
         <v>78</v>
       </c>
@@ -4346,7 +4361,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" ht="22" customHeight="1">
       <c r="A23" s="10" t="s">
         <v>80</v>
       </c>
@@ -4415,7 +4430,7 @@
       <c r="AC23" s="10"/>
       <c r="AD23" s="10"/>
     </row>
-    <row r="24" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" ht="22" customHeight="1">
       <c r="A24" s="101" t="s">
         <v>82</v>
       </c>
@@ -4482,7 +4497,7 @@
       <c r="AC24" s="101"/>
       <c r="AD24" s="101"/>
     </row>
-    <row r="25" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" ht="22" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>85</v>
       </c>
@@ -4557,7 +4572,7 @@
       <c r="AC25" s="10"/>
       <c r="AD25" s="10"/>
     </row>
-    <row r="26" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" ht="22" customHeight="1">
       <c r="A26" s="101" t="s">
         <v>87</v>
       </c>
@@ -4612,7 +4627,7 @@
       <c r="AC26" s="105"/>
       <c r="AD26" s="105"/>
     </row>
-    <row r="27" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" ht="22" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>89</v>
       </c>
@@ -4671,7 +4686,7 @@
       <c r="AC27" s="10"/>
       <c r="AD27" s="10"/>
     </row>
-    <row r="28" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" ht="22" customHeight="1">
       <c r="A28" s="101" t="s">
         <v>90</v>
       </c>
@@ -4736,7 +4751,7 @@
       <c r="AC28" s="101"/>
       <c r="AD28" s="101"/>
     </row>
-    <row r="29" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" ht="22" customHeight="1">
       <c r="A29" s="10" t="s">
         <v>92</v>
       </c>
@@ -4813,7 +4828,7 @@
       </c>
       <c r="AD29" s="10"/>
     </row>
-    <row r="30" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" ht="22" customHeight="1">
       <c r="A30" s="101" t="s">
         <v>94</v>
       </c>
@@ -4898,7 +4913,7 @@
       <c r="AC30" s="101"/>
       <c r="AD30" s="101"/>
     </row>
-    <row r="31" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" ht="22" customHeight="1">
       <c r="A31" s="10" t="s">
         <v>96</v>
       </c>
@@ -4955,7 +4970,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" ht="22" customHeight="1">
       <c r="A32" s="101" t="s">
         <v>97</v>
       </c>
@@ -5022,7 +5037,7 @@
       <c r="AC32" s="101"/>
       <c r="AD32" s="101"/>
     </row>
-    <row r="33" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:30" ht="22" customHeight="1">
       <c r="A33" s="10" t="s">
         <v>99</v>
       </c>
@@ -5101,7 +5116,7 @@
       <c r="AC33" s="10"/>
       <c r="AD33" s="10"/>
     </row>
-    <row r="34" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:30" ht="22" customHeight="1">
       <c r="A34" s="101" t="s">
         <v>101</v>
       </c>
@@ -5168,7 +5183,7 @@
       </c>
       <c r="AD34" s="101"/>
     </row>
-    <row r="35" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" ht="22" customHeight="1">
       <c r="A35" s="10" t="s">
         <v>103</v>
       </c>
@@ -5239,7 +5254,7 @@
       </c>
       <c r="AD35" s="10"/>
     </row>
-    <row r="36" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" ht="22" customHeight="1">
       <c r="A36" s="101" t="s">
         <v>104</v>
       </c>
@@ -5298,7 +5313,7 @@
       </c>
       <c r="AD36" s="101"/>
     </row>
-    <row r="37" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:30" ht="22" customHeight="1">
       <c r="A37" s="10" t="s">
         <v>106</v>
       </c>
@@ -5371,7 +5386,7 @@
       <c r="AC37" s="10"/>
       <c r="AD37" s="10"/>
     </row>
-    <row r="38" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:30" ht="22" customHeight="1">
       <c r="A38" s="101" t="s">
         <v>108</v>
       </c>
@@ -5434,7 +5449,7 @@
       <c r="AC38" s="101"/>
       <c r="AD38" s="101"/>
     </row>
-    <row r="39" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" ht="22" customHeight="1">
       <c r="A39" s="10" t="s">
         <v>110</v>
       </c>
@@ -5489,7 +5504,7 @@
       <c r="AC39" s="10"/>
       <c r="AD39" s="10"/>
     </row>
-    <row r="40" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" ht="22" customHeight="1">
       <c r="A40" s="101" t="s">
         <v>113</v>
       </c>
@@ -5542,7 +5557,7 @@
       <c r="AC40" s="101"/>
       <c r="AD40" s="101"/>
     </row>
-    <row r="41" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:30" ht="22" customHeight="1">
       <c r="A41" s="10" t="s">
         <v>114</v>
       </c>
@@ -5601,7 +5616,7 @@
       <c r="AC41" s="10"/>
       <c r="AD41" s="10"/>
     </row>
-    <row r="42" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" ht="22" customHeight="1">
       <c r="A42" s="101" t="s">
         <v>116</v>
       </c>
@@ -5666,7 +5681,7 @@
       <c r="AC42" s="101"/>
       <c r="AD42" s="101"/>
     </row>
-    <row r="43" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:30" ht="22" customHeight="1">
       <c r="A43" s="10" t="s">
         <v>118</v>
       </c>
@@ -5721,7 +5736,7 @@
       <c r="AC43" s="10"/>
       <c r="AD43" s="10"/>
     </row>
-    <row r="44" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:30" ht="22" customHeight="1">
       <c r="A44" s="101" t="s">
         <v>120</v>
       </c>
@@ -5784,7 +5799,7 @@
       <c r="AC44" s="101"/>
       <c r="AD44" s="101"/>
     </row>
-    <row r="45" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:30" ht="22" customHeight="1">
       <c r="A45" s="10" t="s">
         <v>121</v>
       </c>
@@ -5837,7 +5852,7 @@
       <c r="AC45" s="10"/>
       <c r="AD45" s="10"/>
     </row>
-    <row r="46" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:30" ht="22" customHeight="1">
       <c r="A46" s="101" t="s">
         <v>123</v>
       </c>
@@ -5926,7 +5941,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:30" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:30" ht="22" customHeight="1">
       <c r="A47" s="10" t="s">
         <v>124</v>
       </c>
@@ -5973,7 +5988,7 @@
       <c r="AC47" s="10"/>
       <c r="AD47" s="10"/>
     </row>
-    <row r="48" spans="1:30" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" ht="17" customHeight="1">
       <c r="A48" s="101" t="s">
         <v>127</v>
       </c>
@@ -6050,7 +6065,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -6199,7 +6214,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -6208,7 +6223,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>248</v>
       </c>
@@ -6218,7 +6233,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -6238,7 +6253,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35" t="s">
         <v>249</v>
       </c>
@@ -6259,7 +6274,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>1</v>
       </c>
@@ -6279,7 +6294,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>2</v>
       </c>
@@ -6299,7 +6314,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>3</v>
       </c>
@@ -6319,7 +6334,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>4</v>
       </c>
@@ -6339,7 +6354,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>5</v>
       </c>
@@ -6359,7 +6374,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>6</v>
       </c>
@@ -6379,7 +6394,7 @@
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>7</v>
       </c>
@@ -6399,7 +6414,7 @@
         <v>3.414351851851852E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35"/>
       <c r="B11" s="20"/>
       <c r="C11" s="33"/>
@@ -6407,7 +6422,7 @@
       <c r="E11" s="20"/>
       <c r="F11" s="57"/>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>9</v>
       </c>
@@ -6427,7 +6442,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>10</v>
       </c>
@@ -6447,7 +6462,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="35">
         <v>11</v>
       </c>
@@ -6467,7 +6482,7 @@
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="35">
         <v>12</v>
       </c>
@@ -6487,7 +6502,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="35">
         <v>13</v>
       </c>
@@ -6507,7 +6522,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="22" customHeight="1">
       <c r="A17" s="35">
         <v>14</v>
       </c>
@@ -6527,7 +6542,7 @@
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="35">
         <v>15</v>
       </c>
@@ -6547,7 +6562,7 @@
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="22" customHeight="1">
       <c r="A19" s="35">
         <v>16</v>
       </c>
@@ -6567,7 +6582,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20" s="24"/>
       <c r="B20" s="19"/>
       <c r="C20" s="26"/>
@@ -6575,7 +6590,7 @@
       <c r="E20" s="19"/>
       <c r="F20" s="58"/>
     </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A21" s="29"/>
       <c r="B21" s="30" t="s">
         <v>244</v>
@@ -6631,7 +6646,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -6640,7 +6655,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>250</v>
       </c>
@@ -6650,7 +6665,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -6670,7 +6685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -6690,7 +6705,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -6710,7 +6725,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -6730,7 +6745,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -6750,7 +6765,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -6770,7 +6785,7 @@
         <v>3.414351851851852E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -6790,7 +6805,7 @@
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -6810,7 +6825,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -6830,7 +6845,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -6850,7 +6865,7 @@
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -6870,7 +6885,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" s="24"/>
       <c r="B13" s="19"/>
       <c r="C13" s="26"/>
@@ -6878,7 +6893,7 @@
       <c r="E13" s="19"/>
       <c r="F13" s="58"/>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A14" s="29"/>
       <c r="B14" s="30" t="s">
         <v>244</v>
@@ -6922,7 +6937,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -6931,7 +6946,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>251</v>
       </c>
@@ -6941,7 +6956,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -6961,7 +6976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -6981,7 +6996,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -7001,7 +7016,7 @@
         <v>2.488425925925926E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -7021,7 +7036,7 @@
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -7041,7 +7056,7 @@
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -7061,7 +7076,7 @@
         <v>3.0439814814814817E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -7081,7 +7096,7 @@
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -7101,7 +7116,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -7121,7 +7136,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -7141,7 +7156,7 @@
         <v>1.9328703703703704E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -7161,7 +7176,7 @@
         <v>3.4606481481481485E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -7181,7 +7196,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="35">
         <v>12</v>
       </c>
@@ -7201,7 +7216,7 @@
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="35">
         <v>13</v>
       </c>
@@ -7221,7 +7236,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="35">
         <v>14</v>
       </c>
@@ -7241,7 +7256,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="22" customHeight="1">
       <c r="A17" s="35">
         <v>15</v>
       </c>
@@ -7261,7 +7276,7 @@
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="35">
         <v>16</v>
       </c>
@@ -7281,7 +7296,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="22" customHeight="1">
       <c r="A19" s="35">
         <v>17</v>
       </c>
@@ -7301,7 +7316,7 @@
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="22" customHeight="1">
       <c r="A20" s="35">
         <v>18</v>
       </c>
@@ -7321,7 +7336,7 @@
         <v>3.414351851851852E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="22" customHeight="1">
       <c r="A21" s="35">
         <v>19</v>
       </c>
@@ -7341,7 +7356,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="22" customHeight="1">
       <c r="A22" s="35">
         <v>20</v>
       </c>
@@ -7361,7 +7376,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="22" customHeight="1">
       <c r="A23" s="35">
         <v>21</v>
       </c>
@@ -7379,7 +7394,7 @@
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="22" customHeight="1">
       <c r="A24" s="35">
         <v>22</v>
       </c>
@@ -7399,7 +7414,7 @@
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="22" customHeight="1">
       <c r="A25" s="35">
         <v>23</v>
       </c>
@@ -7419,7 +7434,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="22" customHeight="1">
       <c r="A26" s="35">
         <v>24</v>
       </c>
@@ -7439,7 +7454,7 @@
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="22" customHeight="1">
       <c r="A27" s="35">
         <v>25</v>
       </c>
@@ -7459,7 +7474,7 @@
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="22" customHeight="1">
       <c r="A28" s="35">
         <v>26</v>
       </c>
@@ -7479,7 +7494,7 @@
         <v>2.7199074074074074E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="22" customHeight="1">
       <c r="A29" s="35">
         <v>27</v>
       </c>
@@ -7499,7 +7514,7 @@
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="22" customHeight="1">
       <c r="A30" s="35">
         <v>28</v>
       </c>
@@ -7518,7 +7533,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="22" customHeight="1">
       <c r="A31" s="35">
         <v>29</v>
       </c>
@@ -7538,7 +7553,7 @@
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="22" customHeight="1">
       <c r="A32" s="35">
         <v>30</v>
       </c>
@@ -7558,7 +7573,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="22" customHeight="1">
       <c r="A33" s="35">
         <v>31</v>
       </c>
@@ -7579,7 +7594,7 @@
         <v>3.472222222222222E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="22" customHeight="1">
       <c r="A34" s="24"/>
       <c r="B34" s="19"/>
       <c r="C34" s="26"/>
@@ -7587,7 +7602,7 @@
       <c r="E34" s="19"/>
       <c r="F34" s="58"/>
     </row>
-    <row r="35" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A35" s="29"/>
       <c r="B35" s="30" t="s">
         <v>244</v>
@@ -7671,7 +7686,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -7680,7 +7695,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>252</v>
       </c>
@@ -7690,7 +7705,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -7710,7 +7725,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -7730,7 +7745,7 @@
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -7750,7 +7765,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -7770,7 +7785,7 @@
         <v>2.7199074074074074E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -7790,7 +7805,7 @@
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -7811,7 +7826,7 @@
         <v>2.0023148148148148E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -7831,7 +7846,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -7851,7 +7866,7 @@
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -7871,7 +7886,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -7891,7 +7906,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -7912,7 +7927,7 @@
         <v>2.0833333333333333E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -7932,7 +7947,7 @@
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="35">
         <v>12</v>
       </c>
@@ -7952,7 +7967,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="35">
         <v>13</v>
       </c>
@@ -7972,7 +7987,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6">
       <c r="A16" s="24"/>
       <c r="B16" s="19"/>
       <c r="C16" s="26"/>
@@ -7980,7 +7995,7 @@
       <c r="E16" s="19"/>
       <c r="F16" s="58"/>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A17" s="29"/>
       <c r="B17" s="30" t="s">
         <v>244</v>
@@ -8030,7 +8045,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -8039,7 +8054,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>253</v>
       </c>
@@ -8049,7 +8064,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -8069,7 +8084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -8089,7 +8104,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -8109,7 +8124,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -8129,7 +8144,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>5</v>
       </c>
@@ -8149,7 +8164,7 @@
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>6</v>
       </c>
@@ -8166,7 +8181,7 @@
         <v>2.7662037037037039E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>7</v>
       </c>
@@ -8186,7 +8201,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>8</v>
       </c>
@@ -8206,7 +8221,7 @@
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>9</v>
       </c>
@@ -8226,7 +8241,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>10</v>
       </c>
@@ -8246,7 +8261,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>11</v>
       </c>
@@ -8265,7 +8280,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>12</v>
       </c>
@@ -8285,7 +8300,7 @@
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="35">
         <v>13</v>
       </c>
@@ -8306,7 +8321,7 @@
         <v>2.0833333333333333E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="35">
         <v>14</v>
       </c>
@@ -8326,7 +8341,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="35">
         <v>15</v>
       </c>
@@ -8340,7 +8355,7 @@
       </c>
       <c r="F16" s="57"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="24"/>
       <c r="B17" s="19"/>
       <c r="C17" s="26"/>
@@ -8348,7 +8363,7 @@
       <c r="E17" s="19"/>
       <c r="F17" s="58"/>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A18" s="29"/>
       <c r="B18" s="30" t="s">
         <v>244</v>
@@ -8395,7 +8410,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -8404,7 +8419,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>254</v>
       </c>
@@ -8414,7 +8429,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -8434,7 +8449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -8454,7 +8469,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -8474,7 +8489,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -8494,7 +8509,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -8515,7 +8530,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -8535,7 +8550,7 @@
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -8555,7 +8570,7 @@
         <v>3.4606481481481485E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -8575,7 +8590,7 @@
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -8592,7 +8607,7 @@
         <v>2.7662037037037039E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -8612,7 +8627,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -8633,7 +8648,7 @@
         <v>2.3032407407407407E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -8653,7 +8668,7 @@
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="35">
         <v>12</v>
       </c>
@@ -8673,7 +8688,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="35">
         <v>13</v>
       </c>
@@ -8693,7 +8708,7 @@
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="35">
         <v>14</v>
       </c>
@@ -8713,7 +8728,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="22" customHeight="1">
       <c r="A17" s="35">
         <v>15</v>
       </c>
@@ -8733,7 +8748,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="35">
         <v>16</v>
       </c>
@@ -8753,7 +8768,7 @@
         <v>2.488425925925926E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="22" customHeight="1">
       <c r="A19" s="35">
         <v>17</v>
       </c>
@@ -8772,7 +8787,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="22" customHeight="1">
       <c r="A20" s="35">
         <v>18</v>
       </c>
@@ -8792,7 +8807,7 @@
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="22" customHeight="1">
       <c r="A21" s="35">
         <v>19</v>
       </c>
@@ -8812,7 +8827,7 @@
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="22" customHeight="1">
       <c r="A22" s="35">
         <v>20</v>
       </c>
@@ -8832,7 +8847,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="22" customHeight="1">
       <c r="A23" s="35">
         <v>21</v>
       </c>
@@ -8852,7 +8867,7 @@
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="22" customHeight="1">
       <c r="A24" s="35">
         <v>22</v>
       </c>
@@ -8870,7 +8885,7 @@
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="22" customHeight="1">
       <c r="A25" s="35">
         <v>23</v>
       </c>
@@ -8891,7 +8906,7 @@
         <v>3.9583333333333337E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="22" customHeight="1">
       <c r="A26" s="35">
         <v>24</v>
       </c>
@@ -8911,7 +8926,7 @@
         <v>2.7199074074074074E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="22" customHeight="1">
       <c r="A27" s="35">
         <v>25</v>
       </c>
@@ -8932,7 +8947,7 @@
         <v>2.0833333333333333E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="22" customHeight="1">
       <c r="A28" s="35">
         <v>26</v>
       </c>
@@ -8952,7 +8967,7 @@
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="22" customHeight="1">
       <c r="A29" s="35">
         <v>27</v>
       </c>
@@ -8972,7 +8987,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="22" customHeight="1">
       <c r="A30" s="35">
         <v>28</v>
       </c>
@@ -8992,7 +9007,7 @@
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6">
       <c r="A31" s="24"/>
       <c r="B31" s="19"/>
       <c r="C31" s="26"/>
@@ -9000,7 +9015,7 @@
       <c r="E31" s="19"/>
       <c r="F31" s="58"/>
     </row>
-    <row r="32" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A32" s="29"/>
       <c r="B32" s="30" t="s">
         <v>244</v>
@@ -9076,7 +9091,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -9085,7 +9100,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>255</v>
       </c>
@@ -9095,7 +9110,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -9115,7 +9130,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -9135,7 +9150,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -9155,7 +9170,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -9175,7 +9190,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -9196,7 +9211,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -9216,7 +9231,7 @@
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -9236,7 +9251,7 @@
         <v>3.4606481481481485E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -9257,7 +9272,7 @@
         <v>2.3032407407407407E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -9277,7 +9292,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -9297,7 +9312,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -9317,7 +9332,7 @@
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -9337,7 +9352,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="35">
         <v>12</v>
       </c>
@@ -9357,7 +9372,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="35">
         <v>13</v>
       </c>
@@ -9376,7 +9391,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="35">
         <v>14</v>
       </c>
@@ -9396,7 +9411,7 @@
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="22" customHeight="1">
       <c r="A17" s="35">
         <v>15</v>
       </c>
@@ -9416,7 +9431,7 @@
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="35">
         <v>16</v>
       </c>
@@ -9436,7 +9451,7 @@
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="22" customHeight="1">
       <c r="A19" s="35">
         <v>17</v>
       </c>
@@ -9454,7 +9469,7 @@
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="22" customHeight="1">
       <c r="A20" s="35">
         <v>18</v>
       </c>
@@ -9474,7 +9489,7 @@
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="22" customHeight="1">
       <c r="A21" s="35">
         <v>19</v>
       </c>
@@ -9494,7 +9509,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="22" customHeight="1">
       <c r="A22" s="35" t="s">
         <v>256</v>
       </c>
@@ -9514,7 +9529,7 @@
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23" s="24"/>
       <c r="B23" s="19"/>
       <c r="C23" s="26"/>
@@ -9522,7 +9537,7 @@
       <c r="E23" s="19"/>
       <c r="F23" s="58"/>
     </row>
-    <row r="24" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A24" s="29"/>
       <c r="B24" s="30" t="s">
         <v>244</v>
@@ -9584,7 +9599,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -9593,7 +9608,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>257</v>
       </c>
@@ -9603,7 +9618,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -9623,7 +9638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -9644,7 +9659,7 @@
         <v>2.0833333333333333E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -9664,7 +9679,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -9684,7 +9699,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -9704,7 +9719,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -9724,7 +9739,7 @@
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -9744,7 +9759,7 @@
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -9764,7 +9779,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -9783,7 +9798,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -9803,7 +9818,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -9823,7 +9838,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -9843,7 +9858,7 @@
         <v>2.2569444444444442E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="35">
         <v>12</v>
       </c>
@@ -9863,7 +9878,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="35">
         <v>13</v>
       </c>
@@ -9883,7 +9898,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="35" t="s">
         <v>258</v>
       </c>
@@ -9903,7 +9918,7 @@
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6">
       <c r="A17" s="24"/>
       <c r="B17" s="19"/>
       <c r="C17" s="26"/>
@@ -9911,7 +9926,7 @@
       <c r="E17" s="19"/>
       <c r="F17" s="58"/>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A18" s="29"/>
       <c r="B18" s="30" t="s">
         <v>244</v>
@@ -9962,7 +9977,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -9971,7 +9986,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>259</v>
       </c>
@@ -9981,7 +9996,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -10001,7 +10016,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -10021,7 +10036,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -10041,7 +10056,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -10061,7 +10076,7 @@
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -10081,7 +10096,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -10102,7 +10117,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -10122,7 +10137,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -10140,7 +10155,7 @@
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -10160,7 +10175,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -10179,7 +10194,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -10199,7 +10214,7 @@
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -10219,7 +10234,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" s="24"/>
       <c r="B14" s="19"/>
       <c r="C14" s="26"/>
@@ -10227,7 +10242,7 @@
       <c r="E14" s="19"/>
       <c r="F14" s="58"/>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A15" s="29"/>
       <c r="B15" s="30" t="s">
         <v>244</v>
@@ -10271,7 +10286,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -10280,7 +10295,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>260</v>
       </c>
@@ -10290,7 +10305,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -10310,7 +10325,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -10330,7 +10345,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -10350,7 +10365,7 @@
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -10370,7 +10385,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -10390,7 +10405,7 @@
         <v>2.488425925925926E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -10410,7 +10425,7 @@
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -10430,7 +10445,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -10450,7 +10465,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -10471,7 +10486,7 @@
         <v>3.9583333333333337E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -10492,7 +10507,7 @@
         <v>1.9675925925925924E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -10513,7 +10528,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -10531,7 +10546,7 @@
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="35">
         <v>12</v>
       </c>
@@ -10551,7 +10566,7 @@
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="35">
         <v>13</v>
       </c>
@@ -10571,7 +10586,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="35">
         <v>14</v>
       </c>
@@ -10592,7 +10607,7 @@
         <v>3.472222222222222E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="22" customHeight="1">
       <c r="A17" s="35">
         <v>15</v>
       </c>
@@ -10611,7 +10626,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="35">
         <v>16</v>
       </c>
@@ -10632,7 +10647,7 @@
         <v>2.5115740740740741E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="22" customHeight="1">
       <c r="A19" s="35">
         <v>17</v>
       </c>
@@ -10653,7 +10668,7 @@
         <v>3.3449074074074076E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="22" customHeight="1">
       <c r="A20" s="35">
         <v>18</v>
       </c>
@@ -10673,7 +10688,7 @@
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="22" customHeight="1">
       <c r="A21" s="35">
         <v>19</v>
       </c>
@@ -10693,7 +10708,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="22" customHeight="1">
       <c r="A22" s="35">
         <v>20</v>
       </c>
@@ -10714,7 +10729,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="22" customHeight="1">
       <c r="A23" s="35">
         <v>22</v>
       </c>
@@ -10734,7 +10749,7 @@
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="22" customHeight="1">
       <c r="A24" s="35">
         <v>23</v>
       </c>
@@ -10754,7 +10769,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="22" customHeight="1">
       <c r="A25" s="35">
         <v>24</v>
       </c>
@@ -10774,7 +10789,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="22" customHeight="1">
       <c r="A26" s="35">
         <v>25</v>
       </c>
@@ -10794,7 +10809,7 @@
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="22" customHeight="1">
       <c r="A27" s="35">
         <v>26</v>
       </c>
@@ -10814,7 +10829,7 @@
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="22" customHeight="1">
       <c r="A28" s="35">
         <v>27</v>
       </c>
@@ -10835,7 +10850,7 @@
         <v>3.472222222222222E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6">
       <c r="A29" s="24"/>
       <c r="B29" s="19"/>
       <c r="C29" s="26"/>
@@ -10843,7 +10858,7 @@
       <c r="E29" s="19"/>
       <c r="F29" s="58"/>
     </row>
-    <row r="30" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A30" s="29"/>
       <c r="B30" s="30" t="s">
         <v>244</v>
@@ -10917,7 +10932,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -10932,7 +10947,7 @@
     <col min="11" max="11" width="8.1640625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1" s="43" t="s">
         <v>129</v>
       </c>
@@ -10948,7 +10963,7 @@
       <c r="K1" s="49"/>
       <c r="L1" s="37"/>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="2" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="50" t="s">
         <v>130</v>
       </c>
@@ -10986,7 +11001,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="22" customHeight="1" thickTop="1">
       <c r="A3" s="97" t="s">
         <v>142</v>
       </c>
@@ -11010,7 +11025,7 @@
       <c r="K3" s="53"/>
       <c r="L3" s="9"/>
     </row>
-    <row r="4" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="22" customHeight="1">
       <c r="A4" s="97" t="s">
         <v>146</v>
       </c>
@@ -11034,7 +11049,7 @@
       <c r="K4" s="54"/>
       <c r="L4" s="10"/>
     </row>
-    <row r="5" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="22" customHeight="1">
       <c r="A5" s="97" t="s">
         <v>150</v>
       </c>
@@ -11060,7 +11075,7 @@
       <c r="K5" s="54"/>
       <c r="L5" s="10"/>
     </row>
-    <row r="6" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="22" customHeight="1">
       <c r="A6" s="97" t="s">
         <v>153</v>
       </c>
@@ -11090,7 +11105,7 @@
       </c>
       <c r="L6" s="10"/>
     </row>
-    <row r="7" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="22" customHeight="1">
       <c r="A7" s="97" t="s">
         <v>158</v>
       </c>
@@ -11116,7 +11131,7 @@
       <c r="K7" s="54"/>
       <c r="L7" s="10"/>
     </row>
-    <row r="8" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="22" customHeight="1">
       <c r="A8" s="97" t="s">
         <v>159</v>
       </c>
@@ -11140,7 +11155,7 @@
       <c r="K8" s="54"/>
       <c r="L8" s="10"/>
     </row>
-    <row r="9" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="22" customHeight="1">
       <c r="A9" s="97" t="s">
         <v>160</v>
       </c>
@@ -11168,7 +11183,7 @@
       <c r="K9" s="54"/>
       <c r="L9" s="10"/>
     </row>
-    <row r="10" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="22" customHeight="1">
       <c r="A10" s="97" t="s">
         <v>162</v>
       </c>
@@ -11192,7 +11207,7 @@
       <c r="K10" s="54"/>
       <c r="L10" s="10"/>
     </row>
-    <row r="11" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="22" customHeight="1">
       <c r="A11" s="97" t="s">
         <v>163</v>
       </c>
@@ -11218,7 +11233,7 @@
       <c r="K11" s="54"/>
       <c r="L11" s="10"/>
     </row>
-    <row r="12" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="22" customHeight="1">
       <c r="A12" s="97" t="s">
         <v>164</v>
       </c>
@@ -11240,7 +11255,7 @@
       <c r="K12" s="54"/>
       <c r="L12" s="10"/>
     </row>
-    <row r="13" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="22" customHeight="1">
       <c r="A13" s="97" t="s">
         <v>166</v>
       </c>
@@ -11264,7 +11279,7 @@
       <c r="K13" s="54"/>
       <c r="L13" s="10"/>
     </row>
-    <row r="14" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" ht="22" customHeight="1">
       <c r="A14" s="98" t="s">
         <v>167</v>
       </c>
@@ -11288,7 +11303,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="22" customHeight="1">
       <c r="A15" s="97" t="s">
         <v>172</v>
       </c>
@@ -11322,7 +11337,7 @@
       <c r="K15" s="54"/>
       <c r="L15" s="10"/>
     </row>
-    <row r="16" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="22" customHeight="1">
       <c r="A16" s="97" t="s">
         <v>180</v>
       </c>
@@ -11348,7 +11363,7 @@
       <c r="K16" s="54"/>
       <c r="L16" s="10"/>
     </row>
-    <row r="17" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="22" customHeight="1">
       <c r="A17" s="97" t="s">
         <v>183</v>
       </c>
@@ -11374,7 +11389,7 @@
       <c r="K17" s="54"/>
       <c r="L17" s="10"/>
     </row>
-    <row r="18" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="22" customHeight="1">
       <c r="A18" s="97" t="s">
         <v>185</v>
       </c>
@@ -11400,7 +11415,7 @@
       <c r="K18" s="54"/>
       <c r="L18" s="10"/>
     </row>
-    <row r="19" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="22" customHeight="1">
       <c r="A19" s="97" t="s">
         <v>186</v>
       </c>
@@ -11434,7 +11449,7 @@
       <c r="K19" s="54"/>
       <c r="L19" s="10"/>
     </row>
-    <row r="20" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="22" customHeight="1">
       <c r="A20" s="97" t="s">
         <v>190</v>
       </c>
@@ -11468,7 +11483,7 @@
       </c>
       <c r="L20" s="10"/>
     </row>
-    <row r="21" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="22" customHeight="1">
       <c r="A21" s="99">
         <v>46194</v>
       </c>
@@ -11498,7 +11513,7 @@
       <c r="K21" s="54"/>
       <c r="L21" s="10"/>
     </row>
-    <row r="22" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="22" customHeight="1">
       <c r="A22" s="99">
         <v>46197</v>
       </c>
@@ -11522,28 +11537,28 @@
       <c r="K22" s="54"/>
       <c r="L22" s="10"/>
     </row>
-    <row r="23" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" ht="22" customHeight="1">
       <c r="A23" s="100"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12">
       <c r="A24" s="1"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12">
       <c r="A25" s="1"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12">
       <c r="A26" s="1"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12">
       <c r="A27" s="1"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12">
       <c r="A28" s="1"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12">
       <c r="A29" s="1"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12">
       <c r="A30" s="1"/>
     </row>
   </sheetData>
@@ -11576,7 +11591,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -11585,7 +11600,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>261</v>
       </c>
@@ -11595,7 +11610,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -11615,7 +11630,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -11635,7 +11650,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -11655,7 +11670,7 @@
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -11675,7 +11690,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -11695,7 +11710,7 @@
         <v>2.488425925925926E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -11715,7 +11730,7 @@
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -11735,7 +11750,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -11755,7 +11770,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -11776,7 +11791,7 @@
         <v>3.9583333333333337E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -11797,7 +11812,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -11815,7 +11830,7 @@
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -11835,7 +11850,7 @@
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="35">
         <v>1</v>
       </c>
@@ -11856,7 +11871,7 @@
         <v>3.472222222222222E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="35">
         <v>2</v>
       </c>
@@ -11875,7 +11890,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="35">
         <v>3</v>
       </c>
@@ -11895,7 +11910,7 @@
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="22" customHeight="1">
       <c r="A17" s="35">
         <v>4</v>
       </c>
@@ -11916,7 +11931,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="35">
         <v>5</v>
       </c>
@@ -11936,7 +11951,7 @@
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="22" customHeight="1">
       <c r="A19" s="35">
         <v>6</v>
       </c>
@@ -11956,7 +11971,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="22" customHeight="1">
       <c r="A20" s="35">
         <v>7</v>
       </c>
@@ -11976,7 +11991,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="22" customHeight="1">
       <c r="A21" s="35">
         <v>8</v>
       </c>
@@ -11996,7 +12011,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="22" customHeight="1">
       <c r="A22" s="35">
         <v>9</v>
       </c>
@@ -12016,7 +12031,7 @@
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="22" customHeight="1">
       <c r="A23" s="35">
         <v>10</v>
       </c>
@@ -12036,7 +12051,7 @@
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24" s="24"/>
       <c r="B24" s="19"/>
       <c r="C24" s="26"/>
@@ -12044,7 +12059,7 @@
       <c r="E24" s="19"/>
       <c r="F24" s="58"/>
     </row>
-    <row r="25" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A25" s="29"/>
       <c r="B25" s="30" t="s">
         <v>244</v>
@@ -12108,7 +12123,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -12117,7 +12132,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>262</v>
       </c>
@@ -12127,7 +12142,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -12147,7 +12162,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -12167,7 +12182,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -12187,7 +12202,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -12207,7 +12222,7 @@
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -12227,7 +12242,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -12247,7 +12262,7 @@
         <v>2.488425925925926E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -12267,7 +12282,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -12287,7 +12302,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -12307,7 +12322,7 @@
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -12328,7 +12343,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -12348,7 +12363,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -12368,7 +12383,7 @@
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6">
       <c r="A14" s="24"/>
       <c r="B14" s="19"/>
       <c r="C14" s="26"/>
@@ -12376,7 +12391,7 @@
       <c r="E14" s="19"/>
       <c r="F14" s="58"/>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A15" s="29"/>
       <c r="B15" s="30" t="s">
         <v>244</v>
@@ -12422,7 +12437,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -12431,7 +12446,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>263</v>
       </c>
@@ -12441,7 +12456,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -12461,7 +12476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -12481,7 +12496,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -12501,7 +12516,7 @@
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -12521,7 +12536,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -12541,7 +12556,7 @@
         <v>2.488425925925926E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -12561,7 +12576,7 @@
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -12581,7 +12596,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -12601,7 +12616,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -12621,7 +12636,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -12642,7 +12657,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -12660,7 +12675,7 @@
         <v>3.8541666666666663E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -12680,7 +12695,7 @@
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="35">
         <v>12</v>
       </c>
@@ -12700,7 +12715,7 @@
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="35">
         <v>13</v>
       </c>
@@ -12720,7 +12735,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="35">
         <v>14</v>
       </c>
@@ -12740,7 +12755,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="22" customHeight="1">
       <c r="A17" s="35">
         <v>15</v>
       </c>
@@ -12760,7 +12775,7 @@
         <v>3.2291666666666666E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="35">
         <v>16</v>
       </c>
@@ -12780,7 +12795,7 @@
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" s="24"/>
       <c r="B19" s="19"/>
       <c r="C19" s="26"/>
@@ -12788,7 +12803,7 @@
       <c r="E19" s="19"/>
       <c r="F19" s="58"/>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A20" s="29"/>
       <c r="B20" s="30" t="s">
         <v>244</v>
@@ -12843,7 +12858,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -12852,7 +12867,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>264</v>
       </c>
@@ -12862,7 +12877,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -12882,7 +12897,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -12902,7 +12917,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -12922,7 +12937,7 @@
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -12942,7 +12957,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -12962,7 +12977,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -12983,7 +12998,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -13004,7 +13019,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -13024,7 +13039,7 @@
         <v>4.1319444444444442E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -13044,7 +13059,7 @@
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -13064,7 +13079,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -13084,7 +13099,7 @@
         <v>2.0486111111111113E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="35">
         <v>11</v>
       </c>
@@ -13104,7 +13119,7 @@
         <v>5.9606481481481481E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="24"/>
       <c r="B14" s="19"/>
       <c r="C14" s="26"/>
@@ -13112,7 +13127,7 @@
       <c r="E14" s="19"/>
       <c r="F14" s="58"/>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A15" s="29"/>
       <c r="B15" s="30" t="s">
         <v>244</v>
@@ -13158,7 +13173,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -13167,7 +13182,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>265</v>
       </c>
@@ -13177,7 +13192,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -13197,7 +13212,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="35">
         <v>1</v>
       </c>
@@ -13217,7 +13232,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="35">
         <v>2</v>
       </c>
@@ -13237,7 +13252,7 @@
         <v>2.488425925925926E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="35">
         <v>3</v>
       </c>
@@ -13258,7 +13273,7 @@
         <v>1.9675925925925924E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="35">
         <v>4</v>
       </c>
@@ -13279,7 +13294,7 @@
         <v>5.5555555555555558E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="35">
         <v>5</v>
       </c>
@@ -13299,7 +13314,7 @@
         <v>1.7476851851851852E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -13319,7 +13334,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="35">
         <v>7</v>
       </c>
@@ -13338,7 +13353,7 @@
         <v>1.7708333333333332E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="35">
         <v>8</v>
       </c>
@@ -13358,7 +13373,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="35">
         <v>9</v>
       </c>
@@ -13378,7 +13393,7 @@
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="35">
         <v>10</v>
       </c>
@@ -13398,7 +13413,7 @@
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6">
       <c r="A13" s="24"/>
       <c r="B13" s="19"/>
       <c r="C13" s="26"/>
@@ -13406,7 +13421,7 @@
       <c r="E13" s="19"/>
       <c r="F13" s="58"/>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A14" s="29"/>
       <c r="B14" s="30" t="s">
         <v>244</v>
@@ -13449,7 +13464,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
     <col min="2" max="2" width="19.1640625" customWidth="1"/>
@@ -13459,7 +13474,7 @@
     <col min="6" max="6" width="99.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="7" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="7" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1" s="43" t="s">
         <v>197</v>
       </c>
@@ -13471,7 +13486,7 @@
       <c r="G1" s="44"/>
       <c r="H1" s="44"/>
     </row>
-    <row r="2" spans="1:8" s="7" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="7" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="43" t="s">
         <v>198</v>
       </c>
@@ -13493,7 +13508,7 @@
       <c r="G2" s="45"/>
       <c r="H2" s="45"/>
     </row>
-    <row r="3" spans="1:8" ht="20" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="20" customHeight="1" thickTop="1">
       <c r="A3" s="9" t="s">
         <v>204</v>
       </c>
@@ -13515,7 +13530,7 @@
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
     </row>
-    <row r="4" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="20" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>207</v>
       </c>
@@ -13537,7 +13552,7 @@
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="20" customHeight="1">
       <c r="A5" s="10" t="s">
         <v>211</v>
       </c>
@@ -13557,7 +13572,7 @@
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
     </row>
-    <row r="6" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="20" customHeight="1">
       <c r="A6" s="10" t="s">
         <v>214</v>
       </c>
@@ -13579,7 +13594,7 @@
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="17" customHeight="1">
       <c r="A7" s="12" t="s">
         <v>218</v>
       </c>
@@ -13597,7 +13612,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="17" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>268</v>
       </c>
@@ -13613,7 +13628,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
     </row>
-    <row r="9" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="17" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -13632,7 +13647,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -13643,7 +13658,7 @@
     <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="4" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1" s="46" t="s">
         <v>221</v>
       </c>
@@ -13654,7 +13669,7 @@
       <c r="F1" s="47"/>
       <c r="G1" s="47"/>
     </row>
-    <row r="2" spans="1:7" s="4" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" s="4" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="48" t="s">
         <v>132</v>
       </c>
@@ -13677,7 +13692,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="22" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="22" customHeight="1" thickTop="1">
       <c r="A3" s="9" t="s">
         <v>227</v>
       </c>
@@ -13698,7 +13713,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="22" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>233</v>
       </c>
@@ -13730,7 +13745,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" style="1" bestFit="1" customWidth="1"/>
@@ -13740,7 +13755,7 @@
     <col min="6" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="130" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="130" customFormat="1" ht="28" customHeight="1" thickTop="1" thickBot="1">
       <c r="A1" s="36" t="s">
         <v>272</v>
       </c>
@@ -13752,7 +13767,7 @@
       <c r="G1" s="38"/>
       <c r="H1" s="38"/>
     </row>
-    <row r="2" spans="1:8" s="130" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="130" customFormat="1" ht="22" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="55" t="s">
         <v>130</v>
       </c>
@@ -13772,7 +13787,7 @@
       <c r="G2" s="38"/>
       <c r="H2" s="38"/>
     </row>
-    <row r="3" spans="1:8" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="18" customHeight="1" thickTop="1">
       <c r="A3" s="131">
         <v>45486</v>
       </c>
@@ -13790,7 +13805,7 @@
       <c r="G3" s="132"/>
       <c r="H3" s="132"/>
     </row>
-    <row r="4" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="17" customHeight="1">
       <c r="A4" s="134">
         <v>46158</v>
       </c>
@@ -13808,7 +13823,7 @@
       <c r="G4" s="135"/>
       <c r="H4" s="135"/>
     </row>
-    <row r="5" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="17" customHeight="1">
       <c r="A5" s="135"/>
       <c r="B5" s="135"/>
       <c r="C5" s="135"/>
@@ -13818,7 +13833,7 @@
       <c r="G5" s="135"/>
       <c r="H5" s="135"/>
     </row>
-    <row r="6" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="17" customHeight="1">
       <c r="A6" s="135"/>
       <c r="B6" s="135"/>
       <c r="C6" s="135"/>
@@ -13828,7 +13843,7 @@
       <c r="G6" s="135"/>
       <c r="H6" s="135"/>
     </row>
-    <row r="7" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="17" customHeight="1">
       <c r="A7" s="135"/>
       <c r="B7" s="135"/>
       <c r="C7" s="135"/>
@@ -13838,7 +13853,7 @@
       <c r="G7" s="135"/>
       <c r="H7" s="135"/>
     </row>
-    <row r="8" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="17" customHeight="1">
       <c r="A8" s="135"/>
       <c r="B8" s="135"/>
       <c r="C8" s="135"/>
@@ -13848,7 +13863,7 @@
       <c r="G8" s="135"/>
       <c r="H8" s="135"/>
     </row>
-    <row r="9" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="17" customHeight="1">
       <c r="A9" s="135"/>
       <c r="B9" s="135"/>
       <c r="C9" s="135"/>
@@ -13858,7 +13873,7 @@
       <c r="G9" s="135"/>
       <c r="H9" s="135"/>
     </row>
-    <row r="10" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="17" customHeight="1">
       <c r="A10" s="135"/>
       <c r="B10" s="135"/>
       <c r="C10" s="135"/>
@@ -13868,7 +13883,7 @@
       <c r="G10" s="135"/>
       <c r="H10" s="135"/>
     </row>
-    <row r="11" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="17" customHeight="1">
       <c r="A11" s="135"/>
       <c r="B11" s="135"/>
       <c r="C11" s="135"/>
@@ -13878,7 +13893,7 @@
       <c r="G11" s="135"/>
       <c r="H11" s="135"/>
     </row>
-    <row r="12" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="17" customHeight="1">
       <c r="A12" s="135"/>
       <c r="B12" s="135"/>
       <c r="C12" s="135"/>
@@ -13888,7 +13903,7 @@
       <c r="G12" s="135"/>
       <c r="H12" s="135"/>
     </row>
-    <row r="13" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="17" customHeight="1">
       <c r="A13" s="135"/>
       <c r="B13" s="135"/>
       <c r="C13" s="135"/>
@@ -13898,7 +13913,7 @@
       <c r="G13" s="135"/>
       <c r="H13" s="135"/>
     </row>
-    <row r="14" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="17" customHeight="1">
       <c r="A14" s="135"/>
       <c r="B14" s="135"/>
       <c r="C14" s="135"/>
@@ -13908,7 +13923,7 @@
       <c r="G14" s="135"/>
       <c r="H14" s="135"/>
     </row>
-    <row r="15" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="17" customHeight="1">
       <c r="A15" s="135"/>
       <c r="B15" s="135"/>
       <c r="C15" s="135"/>
@@ -13918,7 +13933,7 @@
       <c r="G15" s="135"/>
       <c r="H15" s="135"/>
     </row>
-    <row r="16" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="17" customHeight="1">
       <c r="A16" s="135"/>
       <c r="B16" s="135"/>
       <c r="C16" s="135"/>
@@ -13928,7 +13943,7 @@
       <c r="G16" s="135"/>
       <c r="H16" s="135"/>
     </row>
-    <row r="17" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="17" customHeight="1">
       <c r="A17" s="135"/>
       <c r="B17" s="135"/>
       <c r="C17" s="135"/>
@@ -13938,7 +13953,7 @@
       <c r="G17" s="135"/>
       <c r="H17" s="135"/>
     </row>
-    <row r="18" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="17" customHeight="1">
       <c r="A18" s="135"/>
       <c r="B18" s="135"/>
       <c r="C18" s="135"/>
@@ -13948,7 +13963,7 @@
       <c r="G18" s="135"/>
       <c r="H18" s="135"/>
     </row>
-    <row r="19" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="17" customHeight="1">
       <c r="A19" s="135"/>
       <c r="B19" s="135"/>
       <c r="C19" s="135"/>
@@ -13958,7 +13973,7 @@
       <c r="G19" s="135"/>
       <c r="H19" s="135"/>
     </row>
-    <row r="20" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="17" customHeight="1">
       <c r="A20" s="135"/>
       <c r="B20" s="135"/>
       <c r="C20" s="135"/>
@@ -13968,7 +13983,7 @@
       <c r="G20" s="135"/>
       <c r="H20" s="135"/>
     </row>
-    <row r="21" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="17" customHeight="1">
       <c r="A21" s="135"/>
       <c r="B21" s="135"/>
       <c r="C21" s="135"/>
@@ -13978,7 +13993,7 @@
       <c r="G21" s="135"/>
       <c r="H21" s="135"/>
     </row>
-    <row r="22" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="17" customHeight="1">
       <c r="A22" s="135"/>
       <c r="B22" s="135"/>
       <c r="C22" s="135"/>
@@ -13988,7 +14003,7 @@
       <c r="G22" s="135"/>
       <c r="H22" s="135"/>
     </row>
-    <row r="23" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="17" customHeight="1">
       <c r="A23" s="135"/>
       <c r="B23" s="135"/>
       <c r="C23" s="135"/>
@@ -13998,7 +14013,7 @@
       <c r="G23" s="135"/>
       <c r="H23" s="135"/>
     </row>
-    <row r="24" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="17" customHeight="1">
       <c r="A24" s="135"/>
       <c r="B24" s="135"/>
       <c r="C24" s="135"/>
@@ -14008,7 +14023,7 @@
       <c r="G24" s="135"/>
       <c r="H24" s="135"/>
     </row>
-    <row r="25" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="17" customHeight="1">
       <c r="A25" s="135"/>
       <c r="B25" s="135"/>
       <c r="C25" s="135"/>
@@ -14018,7 +14033,7 @@
       <c r="G25" s="135"/>
       <c r="H25" s="135"/>
     </row>
-    <row r="26" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="17" customHeight="1">
       <c r="A26" s="135"/>
       <c r="B26" s="135"/>
       <c r="C26" s="135"/>
@@ -14028,7 +14043,7 @@
       <c r="G26" s="135"/>
       <c r="H26" s="135"/>
     </row>
-    <row r="27" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="16" customHeight="1">
       <c r="A27" s="137"/>
       <c r="B27" s="137"/>
       <c r="C27" s="137"/>
@@ -14038,7 +14053,7 @@
       <c r="G27" s="137"/>
       <c r="H27" s="137"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8">
       <c r="D28" s="139"/>
     </row>
   </sheetData>
@@ -14050,7 +14065,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -14059,7 +14074,7 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="22" t="s">
         <v>241</v>
       </c>
@@ -14069,7 +14084,7 @@
       <c r="E1" s="16"/>
       <c r="F1" s="27"/>
     </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="23" t="s">
         <v>242</v>
       </c>
@@ -14089,7 +14104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6">
       <c r="A3" s="24"/>
       <c r="B3" s="19"/>
       <c r="C3" s="26"/>
@@ -14097,7 +14112,7 @@
       <c r="E3" s="19"/>
       <c r="F3" s="28"/>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A4" s="29"/>
       <c r="B4" s="30" t="s">
         <v>244</v>
@@ -14118,8 +14133,8 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="15" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
@@ -14128,473 +14143,479 @@
     <col min="6" max="6" width="11.83203125" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="152" t="s">
+    <row r="1" spans="1:6" ht="50" thickBot="1">
+      <c r="A1" s="170" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="169"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" thickBot="1">
+      <c r="A2" s="165" t="s">
         <v>275</v>
       </c>
-      <c r="B1" s="153"/>
-      <c r="C1" s="153"/>
-      <c r="D1" s="153"/>
-      <c r="E1" s="153"/>
-      <c r="F1" s="154"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="163" t="s">
+      <c r="B2" s="166"/>
+      <c r="C2" s="166"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="166"/>
+      <c r="F2" s="167"/>
+    </row>
+    <row r="3" spans="1:6" ht="18" thickBot="1">
+      <c r="A3" s="151" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="164" t="s">
+      <c r="B3" s="152" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="164" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="164" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="164" t="s">
+      <c r="C3" s="152" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="152" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="152" t="s">
         <v>243</v>
       </c>
-      <c r="F2" s="165" t="s">
+      <c r="F3" s="153" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A3" s="156">
+    <row r="4" spans="1:6" ht="17">
+      <c r="A4" s="144">
         <v>1</v>
       </c>
-      <c r="B3" s="155" t="s">
+      <c r="B4" s="143" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="170" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="170" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="155" t="s">
+      <c r="C4" s="171" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="171" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="143" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="157">
-        <f>VLOOKUP(B3,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F4" s="145">
+        <f>VLOOKUP(B4,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.1875000000000002E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A4" s="158">
-        <v>2</v>
-      </c>
-      <c r="B4" s="168" t="s">
+    <row r="5" spans="1:6" ht="17">
+      <c r="A5" s="146">
+        <v>2</v>
+      </c>
+      <c r="B5" s="172" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="171" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="168" t="s">
+      <c r="C5" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="169">
-        <f>VLOOKUP(B4,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F5" s="174">
+        <f>VLOOKUP(B5,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A5" s="160">
-        <v>3</v>
-      </c>
-      <c r="B5" s="141" t="s">
+    <row r="6" spans="1:6" ht="17">
+      <c r="A6" s="148">
+        <v>3</v>
+      </c>
+      <c r="B6" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="172" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="172" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="141" t="s">
+      <c r="C6" s="175" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="175" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="159">
-        <f>VLOOKUP(B5,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F6" s="147">
+        <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.414351851851852E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A6" s="158">
+    <row r="7" spans="1:6" ht="17">
+      <c r="A7" s="146">
         <v>4</v>
       </c>
-      <c r="B6" s="168" t="s">
+      <c r="B7" s="172" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="171" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="168" t="s">
+      <c r="C7" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="172" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="169">
-        <f>VLOOKUP(B6,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F7" s="174">
+        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A7" s="160">
+    <row r="8" spans="1:6" ht="17">
+      <c r="A8" s="148">
         <v>5</v>
       </c>
-      <c r="B7" s="141" t="s">
+      <c r="B8" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="172" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="172" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="141" t="s">
+      <c r="C8" s="175" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="175" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="159">
-        <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F8" s="147">
+        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A8" s="158">
+    <row r="9" spans="1:6" ht="17">
+      <c r="A9" s="146">
         <v>6</v>
       </c>
-      <c r="B8" s="168" t="s">
+      <c r="B9" s="172" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="171" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="168" t="s">
+      <c r="C9" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="169">
-        <f>VLOOKUP(B8,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F9" s="174">
+        <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A9" s="160">
+    <row r="10" spans="1:6" ht="17">
+      <c r="A10" s="148">
         <v>7</v>
       </c>
-      <c r="B9" s="141" t="s">
+      <c r="B10" s="141" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="172" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="172" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="141" t="s">
+      <c r="C10" s="175" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="175" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="159">
-        <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F10" s="147">
+        <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A10" s="158">
+    <row r="11" spans="1:6" ht="17">
+      <c r="A11" s="146">
         <v>8</v>
       </c>
-      <c r="B10" s="168" t="s">
+      <c r="B11" s="172" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="171" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="168" t="s">
+      <c r="C11" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="172" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="169">
-        <f>VLOOKUP(B10,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F11" s="174">
+        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>1.9791666666666668E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A11" s="160">
+    <row r="12" spans="1:6" ht="17">
+      <c r="A12" s="148">
         <v>9</v>
       </c>
-      <c r="B11" s="141" t="s">
+      <c r="B12" s="141" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="172" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="172" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="141" t="s">
+      <c r="C12" s="175" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="175" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="141" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="159">
-        <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F12" s="147">
+        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A12" s="158">
+    <row r="13" spans="1:6" ht="17">
+      <c r="A13" s="146">
         <v>10</v>
       </c>
-      <c r="B12" s="168" t="s">
+      <c r="B13" s="172" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="171" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="168" t="s">
+      <c r="C13" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="172" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="169">
-        <f>VLOOKUP(B12,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F13" s="174">
+        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A13" s="160">
+    <row r="14" spans="1:6" ht="17">
+      <c r="A14" s="148">
         <v>11</v>
       </c>
-      <c r="B13" s="141" t="s">
+      <c r="B14" s="141" t="s">
         <v>246</v>
       </c>
-      <c r="C13" s="172" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="172" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="141" t="s">
+      <c r="C14" s="175" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="175" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="F13" s="159">
-        <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F14" s="147">
+        <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A14" s="158">
+    <row r="15" spans="1:6" ht="17">
+      <c r="A15" s="146">
         <v>12</v>
       </c>
-      <c r="B14" s="168" t="s">
+      <c r="B15" s="172" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="171" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="168" t="s">
+      <c r="C15" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="172" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="169">
-        <f>VLOOKUP(B14,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F15" s="174">
+        <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A15" s="160">
+    <row r="16" spans="1:6" ht="17">
+      <c r="A16" s="148">
         <v>13</v>
       </c>
-      <c r="B15" s="141" t="s">
+      <c r="B16" s="141" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="172" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="172" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="141" t="s">
+      <c r="C16" s="175" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="175" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="141" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="159">
-        <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F16" s="147">
+        <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="17" x14ac:dyDescent="0.25">
-      <c r="A16" s="158">
+    <row r="17" spans="1:6" ht="17">
+      <c r="A17" s="146">
         <v>14</v>
       </c>
-      <c r="B16" s="168" t="s">
+      <c r="B17" s="172" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="171" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="168" t="s">
+      <c r="C17" s="173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="173" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="169">
-        <f>VLOOKUP(B16,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F17" s="174">
+        <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="161">
+    <row r="18" spans="1:6" ht="18" thickBot="1">
+      <c r="A18" s="149">
         <v>15</v>
       </c>
-      <c r="B17" s="142" t="s">
+      <c r="B18" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="173" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="173" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="142" t="s">
+      <c r="C18" s="176" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="176" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="162">
-        <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
+      <c r="F18" s="150">
+        <f>VLOOKUP(B18,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>3.3217592592592591E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="140"/>
-      <c r="B18" s="166" t="s">
+    <row r="19" spans="1:6" ht="18" thickBot="1">
+      <c r="A19" s="140"/>
+      <c r="B19" s="155" t="s">
         <v>244</v>
       </c>
-      <c r="C18" s="166"/>
-      <c r="D18" s="166"/>
-      <c r="E18" s="166"/>
-      <c r="F18" s="167">
-        <f>SUM(F3:F17)</f>
+      <c r="C19" s="155"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="154">
+        <f>SUM(F4:F18)</f>
         <v>4.0509259259259259E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="F19"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="A20"/>
       <c r="C20"/>
       <c r="D20"/>
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="A21"/>
       <c r="C21"/>
       <c r="D21"/>
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="A22"/>
       <c r="C22"/>
       <c r="D22"/>
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="A23"/>
       <c r="C23"/>
       <c r="D23"/>
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="A24"/>
       <c r="C24"/>
       <c r="D24"/>
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="A25"/>
       <c r="C25"/>
       <c r="D25"/>
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6">
       <c r="A26"/>
       <c r="C26"/>
       <c r="D26"/>
       <c r="F26"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6">
       <c r="A27"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="F27"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6">
       <c r="A28"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="F28"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6">
       <c r="A29"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="F29"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6">
       <c r="A30"/>
       <c r="C30"/>
       <c r="D30"/>
       <c r="F30"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6">
       <c r="A31"/>
       <c r="C31"/>
       <c r="D31"/>
       <c r="F31"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6">
       <c r="A32"/>
       <c r="C32"/>
       <c r="D32"/>
       <c r="F32"/>
     </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="33" customFormat="1"/>
+    <row r="34" customFormat="1"/>
+    <row r="35" customFormat="1"/>
+    <row r="36" customFormat="1"/>
+    <row r="37" customFormat="1"/>
+    <row r="38" customFormat="1"/>
+    <row r="39" customFormat="1"/>
+    <row r="40" customFormat="1"/>
+    <row r="41" customFormat="1"/>
+    <row r="42" customFormat="1"/>
+    <row r="43" customFormat="1"/>
+    <row r="44" customFormat="1"/>
+    <row r="45" customFormat="1"/>
+    <row r="46" customFormat="1"/>
+    <row r="47" customFormat="1"/>
+    <row r="48" customFormat="1"/>
+    <row r="49" customFormat="1"/>
+    <row r="50" customFormat="1"/>
+    <row r="51" customFormat="1"/>
+    <row r="52" customFormat="1"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B19:E19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B18:E18"/>
   </mergeCells>
-  <conditionalFormatting sqref="C3:D17">
+  <conditionalFormatting sqref="C4:D18">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -14603,36 +14624,36 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{25410629-9926-A94A-8DEA-173796F462EF}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{51A86A37-4D80-C742-9F9D-DBAB1BBBF262}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{1BB26EAD-BC11-8F41-AAB4-2AB641D5E159}"/>
-    <hyperlink ref="D4" r:id="rId4" xr:uid="{3C469BEB-F1C9-7E4E-B2C4-91B89BD3FBE0}"/>
-    <hyperlink ref="C5" r:id="rId5" xr:uid="{4C4BB4C6-D7A9-5448-8D70-C170771329C2}"/>
-    <hyperlink ref="D5" r:id="rId6" xr:uid="{DEB078E8-28BF-7C4E-8BEA-FF9AB7AE0B93}"/>
-    <hyperlink ref="C6" r:id="rId7" xr:uid="{D5B568C3-87D4-A94C-949B-127BA6F87614}"/>
-    <hyperlink ref="D6" r:id="rId8" xr:uid="{B15C33EF-691B-9D4F-A3BC-9B3982227CDE}"/>
-    <hyperlink ref="C7" r:id="rId9" xr:uid="{36088FEC-E769-0C44-8A49-92B2647BFB83}"/>
-    <hyperlink ref="D7" r:id="rId10" xr:uid="{2C94AEC3-3E53-294C-B1AB-F84AE5BC1D80}"/>
-    <hyperlink ref="C8" r:id="rId11" xr:uid="{06F0413F-F712-AC4C-9F0E-13F202CC7B6A}"/>
-    <hyperlink ref="D8" r:id="rId12" xr:uid="{8A75058B-1B7E-3F4D-BB4A-94700B5E83DD}"/>
-    <hyperlink ref="C9" r:id="rId13" xr:uid="{8A56B0FC-40A7-E94A-8D95-B9CBC050B784}"/>
-    <hyperlink ref="D9" r:id="rId14" xr:uid="{5C3A2765-3BEE-7042-92FE-EF34ADA8D968}"/>
-    <hyperlink ref="C10" r:id="rId15" xr:uid="{FBFCCA03-69E4-CB41-B7FB-3382EF84E574}"/>
-    <hyperlink ref="D10" r:id="rId16" xr:uid="{15DBDF7B-7D4A-C541-9657-A8CFCC3FF71E}"/>
-    <hyperlink ref="C11" r:id="rId17" xr:uid="{E41F4D2A-B475-114E-BBB7-42E522418218}"/>
-    <hyperlink ref="D11" r:id="rId18" xr:uid="{259D3AFB-D92F-B444-A10A-6756580F9930}"/>
-    <hyperlink ref="C13" r:id="rId19" xr:uid="{EF75B0D6-8328-8F4C-9AE8-9ECF606C459A}"/>
-    <hyperlink ref="D13" r:id="rId20" xr:uid="{1C5CCE95-3106-CB4E-A846-1F7787B725D0}"/>
-    <hyperlink ref="C14" r:id="rId21" xr:uid="{FEF1C916-BC48-A443-81A8-28247F42A2A2}"/>
-    <hyperlink ref="D14" r:id="rId22" xr:uid="{D854AB63-19A5-6745-8468-B6C1D632F760}"/>
-    <hyperlink ref="C15" r:id="rId23" xr:uid="{1080BC69-4EDF-6841-9B5B-F8B92C46F498}"/>
-    <hyperlink ref="D15" r:id="rId24" xr:uid="{7CCA3E16-A9BC-0E44-AFF4-0DD5D6BAF56D}"/>
-    <hyperlink ref="C16" r:id="rId25" xr:uid="{FCA2E2D6-0ED8-F347-A02E-366EE169C5CD}"/>
-    <hyperlink ref="D16" r:id="rId26" xr:uid="{70AE9A16-25BE-FE40-808F-6E47A2F5FCA9}"/>
-    <hyperlink ref="C17" r:id="rId27" xr:uid="{BEC67237-B25D-0147-BB2F-633884A6E50D}"/>
-    <hyperlink ref="D17" r:id="rId28" xr:uid="{DEE84DE1-B608-0A4F-8CB0-2A4C8BACB00A}"/>
-    <hyperlink ref="C12" r:id="rId29" xr:uid="{A801D906-C97B-7647-85DE-7AC62D3FDE24}"/>
-    <hyperlink ref="D12" r:id="rId30" xr:uid="{FD4DE05E-0EBA-B341-B198-8973B5FC18C1}"/>
+    <hyperlink ref="C4" r:id="rId1" xr:uid="{25410629-9926-A94A-8DEA-173796F462EF}"/>
+    <hyperlink ref="D4" r:id="rId2" xr:uid="{51A86A37-4D80-C742-9F9D-DBAB1BBBF262}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{1BB26EAD-BC11-8F41-AAB4-2AB641D5E159}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{3C469BEB-F1C9-7E4E-B2C4-91B89BD3FBE0}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{4C4BB4C6-D7A9-5448-8D70-C170771329C2}"/>
+    <hyperlink ref="D6" r:id="rId6" xr:uid="{DEB078E8-28BF-7C4E-8BEA-FF9AB7AE0B93}"/>
+    <hyperlink ref="C7" r:id="rId7" xr:uid="{D5B568C3-87D4-A94C-949B-127BA6F87614}"/>
+    <hyperlink ref="D7" r:id="rId8" xr:uid="{B15C33EF-691B-9D4F-A3BC-9B3982227CDE}"/>
+    <hyperlink ref="C8" r:id="rId9" xr:uid="{36088FEC-E769-0C44-8A49-92B2647BFB83}"/>
+    <hyperlink ref="D8" r:id="rId10" xr:uid="{2C94AEC3-3E53-294C-B1AB-F84AE5BC1D80}"/>
+    <hyperlink ref="C9" r:id="rId11" xr:uid="{06F0413F-F712-AC4C-9F0E-13F202CC7B6A}"/>
+    <hyperlink ref="D9" r:id="rId12" xr:uid="{8A75058B-1B7E-3F4D-BB4A-94700B5E83DD}"/>
+    <hyperlink ref="C10" r:id="rId13" xr:uid="{8A56B0FC-40A7-E94A-8D95-B9CBC050B784}"/>
+    <hyperlink ref="D10" r:id="rId14" xr:uid="{5C3A2765-3BEE-7042-92FE-EF34ADA8D968}"/>
+    <hyperlink ref="C11" r:id="rId15" xr:uid="{FBFCCA03-69E4-CB41-B7FB-3382EF84E574}"/>
+    <hyperlink ref="D11" r:id="rId16" xr:uid="{15DBDF7B-7D4A-C541-9657-A8CFCC3FF71E}"/>
+    <hyperlink ref="C12" r:id="rId17" xr:uid="{E41F4D2A-B475-114E-BBB7-42E522418218}"/>
+    <hyperlink ref="D12" r:id="rId18" xr:uid="{259D3AFB-D92F-B444-A10A-6756580F9930}"/>
+    <hyperlink ref="C14" r:id="rId19" xr:uid="{EF75B0D6-8328-8F4C-9AE8-9ECF606C459A}"/>
+    <hyperlink ref="D14" r:id="rId20" xr:uid="{1C5CCE95-3106-CB4E-A846-1F7787B725D0}"/>
+    <hyperlink ref="C15" r:id="rId21" xr:uid="{FEF1C916-BC48-A443-81A8-28247F42A2A2}"/>
+    <hyperlink ref="D15" r:id="rId22" xr:uid="{D854AB63-19A5-6745-8468-B6C1D632F760}"/>
+    <hyperlink ref="C16" r:id="rId23" xr:uid="{1080BC69-4EDF-6841-9B5B-F8B92C46F498}"/>
+    <hyperlink ref="D16" r:id="rId24" xr:uid="{7CCA3E16-A9BC-0E44-AFF4-0DD5D6BAF56D}"/>
+    <hyperlink ref="C17" r:id="rId25" xr:uid="{FCA2E2D6-0ED8-F347-A02E-366EE169C5CD}"/>
+    <hyperlink ref="D17" r:id="rId26" xr:uid="{70AE9A16-25BE-FE40-808F-6E47A2F5FCA9}"/>
+    <hyperlink ref="C18" r:id="rId27" xr:uid="{BEC67237-B25D-0147-BB2F-633884A6E50D}"/>
+    <hyperlink ref="D18" r:id="rId28" xr:uid="{DEE84DE1-B608-0A4F-8CB0-2A4C8BACB00A}"/>
+    <hyperlink ref="C13" r:id="rId29" xr:uid="{A801D906-C97B-7647-85DE-7AC62D3FDE24}"/>
+    <hyperlink ref="D13" r:id="rId30" xr:uid="{FD4DE05E-0EBA-B341-B198-8973B5FC18C1}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -14642,7 +14663,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="15" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" bestFit="1" customWidth="1"/>
@@ -14651,17 +14672,17 @@
     <col min="6" max="6" width="11.83203125" style="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="143" t="s">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
+      <c r="A1" s="156" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="144"/>
-      <c r="C1" s="144"/>
-      <c r="D1" s="144"/>
-      <c r="E1" s="144"/>
-      <c r="F1" s="145"/>
-    </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="158"/>
+    </row>
+    <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A2" s="71" t="s">
         <v>242</v>
       </c>
@@ -14681,7 +14702,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="74">
         <v>1</v>
       </c>
@@ -14701,7 +14722,7 @@
         <v>2.1875000000000002E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="79">
         <v>2</v>
       </c>
@@ -14721,7 +14742,7 @@
         <v>2.2569444444444399E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="79">
         <v>3</v>
       </c>
@@ -14741,7 +14762,7 @@
         <v>2.6504629629629599E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="79">
         <v>4</v>
       </c>
@@ -14761,7 +14782,7 @@
         <v>2.0833333333333298E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="79">
         <v>5</v>
       </c>
@@ -14781,7 +14802,7 @@
         <v>2.04861111111111E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="79">
         <v>6</v>
       </c>
@@ -14801,7 +14822,7 @@
         <v>3.4143518518518498E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="79">
         <v>7</v>
       </c>
@@ -14821,7 +14842,7 @@
         <v>2.48842592592593E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="79">
         <v>8</v>
       </c>
@@ -14841,7 +14862,7 @@
         <v>3.59953703703704E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="79">
         <v>9</v>
       </c>
@@ -14861,7 +14882,7 @@
         <v>2.0949074074074099E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="79">
         <v>10</v>
       </c>
@@ -14881,7 +14902,7 @@
         <v>2.5810185185185198E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="79">
         <v>11</v>
       </c>
@@ -14901,7 +14922,7 @@
         <v>2.8587962962962998E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="79">
         <v>12</v>
       </c>
@@ -14921,7 +14942,7 @@
         <v>2.4305555555555599E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="79">
         <v>13</v>
       </c>
@@ -14941,7 +14962,7 @@
         <v>3.04398148148148E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="79">
         <v>14</v>
       </c>
@@ -14961,17 +14982,17 @@
         <v>3.32175925925926E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="146" t="s">
+    <row r="17" spans="1:6" ht="22" customHeight="1">
+      <c r="A17" s="159" t="s">
         <v>247</v>
       </c>
-      <c r="B17" s="147"/>
-      <c r="C17" s="147"/>
-      <c r="D17" s="147"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-    </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="160"/>
+      <c r="C17" s="160"/>
+      <c r="D17" s="160"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="161"/>
+    </row>
+    <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="79">
         <v>15</v>
       </c>
@@ -14991,7 +15012,7 @@
         <v>2.71990740740741E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="17" customHeight="1">
       <c r="A19" s="87">
         <v>16</v>
       </c>
@@ -15011,7 +15032,7 @@
         <v>2.7893518518518502E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="22" customHeight="1">
       <c r="A20" s="88">
         <v>17</v>
       </c>
@@ -15031,7 +15052,7 @@
         <v>3.3680555555555599E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="17" customHeight="1">
       <c r="A21" s="79">
         <v>18</v>
       </c>
@@ -15051,7 +15072,7 @@
         <v>2.9513888888888901E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="17" customHeight="1">
       <c r="A22" s="79">
         <v>19</v>
       </c>
@@ -15071,7 +15092,7 @@
         <v>2.60416666666667E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="17" customHeight="1">
       <c r="A23" s="79">
         <v>20</v>
       </c>
@@ -15091,7 +15112,7 @@
         <v>3.2291666666666701E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="17" customHeight="1">
       <c r="A24" s="79">
         <v>21</v>
       </c>
@@ -15111,7 +15132,7 @@
         <v>2.7430555555555602E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="17" customHeight="1">
       <c r="A25" s="79">
         <v>22</v>
       </c>
@@ -15131,7 +15152,7 @@
         <v>2.60416666666667E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="17" customHeight="1">
       <c r="A26" s="79">
         <v>23</v>
       </c>
@@ -15151,7 +15172,7 @@
         <v>1.9791666666666699E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="17" customHeight="1">
       <c r="A27" s="79">
         <v>24</v>
       </c>
@@ -15171,7 +15192,7 @@
         <v>2.5810185185185198E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="17" customHeight="1">
       <c r="A28" s="79">
         <v>25</v>
       </c>
@@ -15191,7 +15212,7 @@
         <v>4.6874999999999998E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="17" customHeight="1" thickBot="1">
       <c r="A29" s="79">
         <v>26</v>
       </c>
@@ -15211,7 +15232,7 @@
         <v>5.9606481481481498E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="17" customHeight="1" thickBot="1">
       <c r="A30" s="90"/>
       <c r="B30" s="91" t="s">
         <v>244</v>
@@ -15299,7 +15320,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="15" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -15308,17 +15329,17 @@
     <col min="6" max="6" width="11.6640625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="149" t="s">
+    <row r="1" spans="1:6" ht="28" customHeight="1">
+      <c r="A1" s="162" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="150"/>
-      <c r="C1" s="150"/>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
-      <c r="F1" s="151"/>
-    </row>
-    <row r="2" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="164"/>
+    </row>
+    <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="59" t="s">
         <v>242</v>
       </c>
@@ -15338,7 +15359,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="61">
         <v>1</v>
       </c>
@@ -15358,7 +15379,7 @@
         <v>2.1874999999999998E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="22" customHeight="1">
       <c r="A4" s="61">
         <v>2</v>
       </c>
@@ -15378,7 +15399,7 @@
         <v>2.9513888888888888E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="22" customHeight="1">
       <c r="A5" s="61">
         <v>3</v>
       </c>
@@ -15398,7 +15419,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="22" customHeight="1">
       <c r="A6" s="61">
         <v>4</v>
       </c>
@@ -15418,7 +15439,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="22" customHeight="1">
       <c r="A7" s="61">
         <v>5</v>
       </c>
@@ -15438,7 +15459,7 @@
         <v>2.4305555555555556E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="22" customHeight="1">
       <c r="A8" s="61">
         <v>6</v>
       </c>
@@ -15458,7 +15479,7 @@
         <v>2.8587962962962963E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="22" customHeight="1">
       <c r="A9" s="61">
         <v>7</v>
       </c>
@@ -15478,7 +15499,7 @@
         <v>3.414351851851852E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="22" customHeight="1">
       <c r="A10" s="61">
         <v>8</v>
       </c>
@@ -15497,7 +15518,7 @@
         <v>3.8541666666666668E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="22" customHeight="1">
       <c r="A11" s="61">
         <v>9</v>
       </c>
@@ -15517,7 +15538,7 @@
         <v>3.5995370370370369E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="22" customHeight="1">
       <c r="A12" s="61">
         <v>10</v>
       </c>
@@ -15537,7 +15558,7 @@
         <v>2.7893518518518519E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="22" customHeight="1">
       <c r="A13" s="61">
         <v>11</v>
       </c>
@@ -15557,7 +15578,7 @@
         <v>3.3680555555555556E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="22" customHeight="1">
       <c r="A14" s="61">
         <v>12</v>
       </c>
@@ -15577,7 +15598,7 @@
         <v>2.5810185185185185E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="22" customHeight="1">
       <c r="A15" s="61">
         <v>13</v>
       </c>
@@ -15597,7 +15618,7 @@
         <v>2.6041666666666665E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="22" customHeight="1">
       <c r="A16" s="61">
         <v>14</v>
       </c>
@@ -15617,7 +15638,7 @@
         <v>2.7430555555555554E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="22" customHeight="1">
       <c r="A17" s="61">
         <v>15</v>
       </c>
@@ -15637,7 +15658,7 @@
         <v>2.0949074074074073E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="61">
         <v>16</v>
       </c>
@@ -15657,7 +15678,7 @@
         <v>3.3217592592592595E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="A19" s="63"/>
       <c r="B19" s="19"/>
       <c r="C19" s="26"/>
@@ -15665,7 +15686,7 @@
       <c r="E19" s="19"/>
       <c r="F19" s="64"/>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A20" s="65"/>
       <c r="B20" s="66" t="s">
         <v>244</v>

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47D57BCE-B2EE-9944-87DE-03D431F0FE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{928C7477-631C-8E46-9D21-E5AD0AFB9C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3840" yWindow="3660" windowWidth="29580" windowHeight="17160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2470,7 +2470,35 @@
     <xf numFmtId="165" fontId="22" fillId="0" borderId="57" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2500,34 +2528,6 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="63" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="59" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -14144,24 +14144,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="165" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="169"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="167"/>
     </row>
     <row r="2" spans="1:6" ht="18" thickBot="1">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="161" t="s">
         <v>275</v>
       </c>
-      <c r="B2" s="166"/>
-      <c r="C2" s="166"/>
-      <c r="D2" s="166"/>
-      <c r="E2" s="166"/>
-      <c r="F2" s="167"/>
+      <c r="B2" s="162"/>
+      <c r="C2" s="162"/>
+      <c r="D2" s="162"/>
+      <c r="E2" s="162"/>
+      <c r="F2" s="163"/>
     </row>
     <row r="3" spans="1:6" ht="18" thickBot="1">
       <c r="A3" s="151" t="s">
@@ -14190,10 +14190,10 @@
       <c r="B4" s="143" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="171" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="171" t="s">
+      <c r="C4" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="155" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="143" t="s">
@@ -14208,19 +14208,19 @@
       <c r="A5" s="146">
         <v>2</v>
       </c>
-      <c r="B5" s="172" t="s">
+      <c r="B5" s="156" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="173" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="173" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="172" t="s">
+      <c r="C5" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="157" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="156" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="174">
+      <c r="F5" s="158">
         <f>VLOOKUP(B5,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.9513888888888888E-3</v>
       </c>
@@ -14232,10 +14232,10 @@
       <c r="B6" s="141" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="175" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="175" t="s">
+      <c r="C6" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="159" t="s">
         <v>3</v>
       </c>
       <c r="E6" s="141" t="s">
@@ -14250,19 +14250,19 @@
       <c r="A7" s="146">
         <v>4</v>
       </c>
-      <c r="B7" s="172" t="s">
+      <c r="B7" s="156" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="173" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="173" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="172" t="s">
+      <c r="C7" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="157" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="156" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="174">
+      <c r="F7" s="158">
         <f>VLOOKUP(B7,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.6041666666666665E-3</v>
       </c>
@@ -14274,10 +14274,10 @@
       <c r="B8" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="175" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="175" t="s">
+      <c r="C8" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="159" t="s">
         <v>3</v>
       </c>
       <c r="E8" s="141" t="s">
@@ -14292,19 +14292,19 @@
       <c r="A9" s="146">
         <v>6</v>
       </c>
-      <c r="B9" s="172" t="s">
+      <c r="B9" s="156" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="173" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="173" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="172" t="s">
+      <c r="C9" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="157" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="156" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="174">
+      <c r="F9" s="158">
         <f>VLOOKUP(B9,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.5810185185185185E-3</v>
       </c>
@@ -14316,10 +14316,10 @@
       <c r="B10" s="141" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="175" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="175" t="s">
+      <c r="C10" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="159" t="s">
         <v>3</v>
       </c>
       <c r="E10" s="141" t="s">
@@ -14334,19 +14334,19 @@
       <c r="A11" s="146">
         <v>8</v>
       </c>
-      <c r="B11" s="172" t="s">
+      <c r="B11" s="156" t="s">
         <v>85</v>
       </c>
-      <c r="C11" s="173" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="173" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="172" t="s">
+      <c r="C11" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="157" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="156" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="174">
+      <c r="F11" s="158">
         <f>VLOOKUP(B11,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>1.9791666666666668E-3</v>
       </c>
@@ -14358,10 +14358,10 @@
       <c r="B12" s="141" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="175" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="175" t="s">
+      <c r="C12" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="159" t="s">
         <v>3</v>
       </c>
       <c r="E12" s="141" t="s">
@@ -14376,19 +14376,19 @@
       <c r="A13" s="146">
         <v>10</v>
       </c>
-      <c r="B13" s="172" t="s">
+      <c r="B13" s="156" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="173" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="173" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="172" t="s">
+      <c r="C13" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="157" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="156" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="174">
+      <c r="F13" s="158">
         <f>VLOOKUP(B13,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.7893518518518519E-3</v>
       </c>
@@ -14400,10 +14400,10 @@
       <c r="B14" s="141" t="s">
         <v>246</v>
       </c>
-      <c r="C14" s="175" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="175" t="s">
+      <c r="C14" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="159" t="s">
         <v>3</v>
       </c>
       <c r="E14" s="141" t="s">
@@ -14418,19 +14418,19 @@
       <c r="A15" s="146">
         <v>12</v>
       </c>
-      <c r="B15" s="172" t="s">
+      <c r="B15" s="156" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="173" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="173" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15" s="172" t="s">
+      <c r="C15" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="157" t="s">
+        <v>3</v>
+      </c>
+      <c r="E15" s="156" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="174">
+      <c r="F15" s="158">
         <f>VLOOKUP(B15,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.8587962962962963E-3</v>
       </c>
@@ -14442,10 +14442,10 @@
       <c r="B16" s="141" t="s">
         <v>127</v>
       </c>
-      <c r="C16" s="175" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="175" t="s">
+      <c r="C16" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="159" t="s">
         <v>3</v>
       </c>
       <c r="E16" s="141" t="s">
@@ -14460,19 +14460,19 @@
       <c r="A17" s="146">
         <v>14</v>
       </c>
-      <c r="B17" s="172" t="s">
+      <c r="B17" s="156" t="s">
         <v>54</v>
       </c>
-      <c r="C17" s="173" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="173" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="172" t="s">
+      <c r="C17" s="157" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="157" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="156" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="174">
+      <c r="F17" s="158">
         <f>VLOOKUP(B17,'Song Tracker'!$A$3:$F$48,6,FALSE)</f>
         <v>2.7430555555555554E-3</v>
       </c>
@@ -14484,10 +14484,10 @@
       <c r="B18" s="142" t="s">
         <v>123</v>
       </c>
-      <c r="C18" s="176" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" s="176" t="s">
+      <c r="C18" s="160" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="160" t="s">
         <v>3</v>
       </c>
       <c r="E18" s="142" t="s">
@@ -14500,12 +14500,12 @@
     </row>
     <row r="19" spans="1:6" ht="18" thickBot="1">
       <c r="A19" s="140"/>
-      <c r="B19" s="155" t="s">
+      <c r="B19" s="164" t="s">
         <v>244</v>
       </c>
-      <c r="C19" s="155"/>
-      <c r="D19" s="155"/>
-      <c r="E19" s="155"/>
+      <c r="C19" s="164"/>
+      <c r="D19" s="164"/>
+      <c r="E19" s="164"/>
       <c r="F19" s="154">
         <f>SUM(F4:F18)</f>
         <v>4.0509259259259259E-2</v>
@@ -14615,14 +14615,6 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="C4:D18">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>MOD(ROW(),2)=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>MOD(ROW(),2)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="C4" r:id="rId1" xr:uid="{25410629-9926-A94A-8DEA-173796F462EF}"/>
     <hyperlink ref="D4" r:id="rId2" xr:uid="{51A86A37-4D80-C742-9F9D-DBAB1BBBF262}"/>
@@ -14673,14 +14665,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="168" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="157"/>
-      <c r="D1" s="157"/>
-      <c r="E1" s="157"/>
-      <c r="F1" s="158"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="170"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A2" s="71" t="s">
@@ -14983,14 +14975,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1">
-      <c r="A17" s="159" t="s">
+      <c r="A17" s="171" t="s">
         <v>247</v>
       </c>
-      <c r="B17" s="160"/>
-      <c r="C17" s="160"/>
-      <c r="D17" s="160"/>
-      <c r="E17" s="160"/>
-      <c r="F17" s="161"/>
+      <c r="B17" s="172"/>
+      <c r="C17" s="172"/>
+      <c r="D17" s="172"/>
+      <c r="E17" s="172"/>
+      <c r="F17" s="173"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="79">
@@ -15330,14 +15322,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
-      <c r="A1" s="162" t="s">
+      <c r="A1" s="174" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="163"/>
-      <c r="C1" s="163"/>
-      <c r="D1" s="163"/>
-      <c r="E1" s="163"/>
-      <c r="F1" s="164"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1">
       <c r="A2" s="59" t="s">

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F087E838-D03D-0847-B4DF-704025EAD432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1C04ED-D604-4C46-8936-B81008FB0AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3820" yWindow="3660" windowWidth="29580" windowHeight="17160" firstSheet="19" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3820" yWindow="3660" windowWidth="29580" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -2466,6 +2466,88 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="72" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2542,88 +2624,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="69" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="44" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="49" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="49" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="72" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -3012,3163 +3012,3163 @@
     <col min="30" max="30" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="195" customFormat="1" ht="28" customHeight="1" thickBot="1">
-      <c r="A1" s="192" t="s">
+    <row r="1" spans="1:30" s="167" customFormat="1" ht="28" customHeight="1" thickBot="1">
+      <c r="A1" s="164" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="193"/>
-      <c r="L1" s="193"/>
-      <c r="M1" s="193"/>
-      <c r="N1" s="193"/>
-      <c r="O1" s="193"/>
-      <c r="P1" s="193"/>
-      <c r="Q1" s="193"/>
-      <c r="R1" s="193"/>
-      <c r="S1" s="193"/>
-      <c r="T1" s="193"/>
-      <c r="U1" s="193"/>
-      <c r="V1" s="193"/>
-      <c r="W1" s="193"/>
-      <c r="X1" s="193"/>
-      <c r="Y1" s="193"/>
-      <c r="Z1" s="193"/>
-      <c r="AA1" s="193"/>
-      <c r="AB1" s="193"/>
-      <c r="AC1" s="193"/>
-      <c r="AD1" s="193"/>
-    </row>
-    <row r="2" spans="1:30" s="201" customFormat="1" ht="56" customHeight="1" thickBot="1">
-      <c r="A2" s="196" t="s">
+      <c r="B1" s="165"/>
+      <c r="C1" s="165"/>
+      <c r="D1" s="165"/>
+      <c r="E1" s="165"/>
+      <c r="F1" s="165"/>
+      <c r="G1" s="165"/>
+      <c r="H1" s="165"/>
+      <c r="I1" s="165"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="165"/>
+      <c r="L1" s="165"/>
+      <c r="M1" s="165"/>
+      <c r="N1" s="165"/>
+      <c r="O1" s="165"/>
+      <c r="P1" s="165"/>
+      <c r="Q1" s="165"/>
+      <c r="R1" s="165"/>
+      <c r="S1" s="165"/>
+      <c r="T1" s="165"/>
+      <c r="U1" s="165"/>
+      <c r="V1" s="165"/>
+      <c r="W1" s="165"/>
+      <c r="X1" s="165"/>
+      <c r="Y1" s="165"/>
+      <c r="Z1" s="165"/>
+      <c r="AA1" s="165"/>
+      <c r="AB1" s="165"/>
+      <c r="AC1" s="165"/>
+      <c r="AD1" s="165"/>
+    </row>
+    <row r="2" spans="1:30" s="173" customFormat="1" ht="56" customHeight="1" thickBot="1">
+      <c r="A2" s="168" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="197" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="197" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="197" t="s">
+      <c r="B2" s="169" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="169" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="169" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="197" t="s">
+      <c r="E2" s="169" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="197" t="s">
+      <c r="F2" s="169" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="197" t="s">
+      <c r="G2" s="169" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="197" t="s">
+      <c r="H2" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="197" t="s">
+      <c r="I2" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="197" t="s">
+      <c r="J2" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="197" t="s">
+      <c r="K2" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="198" t="s">
+      <c r="L2" s="170" t="s">
         <v>254</v>
       </c>
-      <c r="M2" s="199" t="s">
+      <c r="M2" s="171" t="s">
         <v>27</v>
       </c>
-      <c r="N2" s="199" t="s">
+      <c r="N2" s="171" t="s">
         <v>26</v>
       </c>
-      <c r="O2" s="200" t="s">
+      <c r="O2" s="172" t="s">
         <v>25</v>
       </c>
-      <c r="P2" s="200" t="s">
+      <c r="P2" s="172" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="200" t="s">
+      <c r="Q2" s="172" t="s">
         <v>23</v>
       </c>
-      <c r="R2" s="200" t="s">
+      <c r="R2" s="172" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="200" t="s">
+      <c r="S2" s="172" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="200" t="s">
+      <c r="T2" s="172" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="200" t="s">
+      <c r="U2" s="172" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="200" t="s">
+      <c r="V2" s="172" t="s">
         <v>18</v>
       </c>
-      <c r="W2" s="200" t="s">
+      <c r="W2" s="172" t="s">
         <v>17</v>
       </c>
-      <c r="X2" s="200" t="s">
+      <c r="X2" s="172" t="s">
         <v>16</v>
       </c>
-      <c r="Y2" s="200" t="s">
+      <c r="Y2" s="172" t="s">
         <v>15</v>
       </c>
-      <c r="Z2" s="200" t="s">
+      <c r="Z2" s="172" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="200" t="s">
+      <c r="AA2" s="172" t="s">
         <v>13</v>
       </c>
-      <c r="AB2" s="200" t="s">
+      <c r="AB2" s="172" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="200" t="s">
+      <c r="AC2" s="172" t="s">
         <v>250</v>
       </c>
-      <c r="AD2" s="200" t="s">
+      <c r="AD2" s="172" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="191" customFormat="1" ht="22" customHeight="1">
-      <c r="A3" s="186" t="s">
+    <row r="3" spans="1:30" s="163" customFormat="1" ht="22" customHeight="1">
+      <c r="A3" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="187" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="187" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="186" t="s">
+      <c r="B3" s="159" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="159" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="158" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="186" t="s">
+      <c r="E3" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="188">
+      <c r="F3" s="160">
         <v>2.7662037037037039E-3</v>
       </c>
-      <c r="G3" s="186" t="s">
+      <c r="G3" s="158" t="s">
         <v>31</v>
       </c>
-      <c r="H3" s="186"/>
-      <c r="I3" s="186" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="186" t="s">
+      <c r="H3" s="158"/>
+      <c r="I3" s="158" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" s="158" t="s">
         <v>33</v>
       </c>
-      <c r="K3" s="186"/>
-      <c r="L3" s="189">
+      <c r="K3" s="158"/>
+      <c r="L3" s="161">
         <f>COUNTIF(M3:AW3,"✓")</f>
         <v>2</v>
       </c>
-      <c r="M3" s="189"/>
-      <c r="N3" s="189"/>
-      <c r="O3" s="190"/>
-      <c r="P3" s="186"/>
-      <c r="Q3" s="186"/>
-      <c r="R3" s="186"/>
-      <c r="S3" s="186"/>
-      <c r="T3" s="186"/>
-      <c r="U3" s="186"/>
-      <c r="V3" s="186" t="s">
-        <v>32</v>
-      </c>
-      <c r="W3" s="186" t="s">
-        <v>32</v>
-      </c>
-      <c r="X3" s="186"/>
-      <c r="Y3" s="186"/>
-      <c r="Z3" s="186"/>
-      <c r="AA3" s="186"/>
-      <c r="AB3" s="186"/>
-      <c r="AC3" s="186"/>
-      <c r="AD3" s="186"/>
-    </row>
-    <row r="4" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A4" s="176" t="s">
+      <c r="M3" s="161"/>
+      <c r="N3" s="161"/>
+      <c r="O3" s="162"/>
+      <c r="P3" s="158"/>
+      <c r="Q3" s="158"/>
+      <c r="R3" s="158"/>
+      <c r="S3" s="158"/>
+      <c r="T3" s="158"/>
+      <c r="U3" s="158"/>
+      <c r="V3" s="158" t="s">
+        <v>32</v>
+      </c>
+      <c r="W3" s="158" t="s">
+        <v>32</v>
+      </c>
+      <c r="X3" s="158"/>
+      <c r="Y3" s="158"/>
+      <c r="Z3" s="158"/>
+      <c r="AA3" s="158"/>
+      <c r="AB3" s="158"/>
+      <c r="AC3" s="158"/>
+      <c r="AD3" s="158"/>
+    </row>
+    <row r="4" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A4" s="148" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="176" t="s">
+      <c r="B4" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="148" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="176" t="s">
+      <c r="E4" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="178">
+      <c r="F4" s="150">
         <v>3.9583333333333337E-3</v>
       </c>
-      <c r="G4" s="176" t="s">
+      <c r="G4" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="176"/>
-      <c r="I4" s="176"/>
-      <c r="J4" s="176" t="s">
+      <c r="H4" s="148"/>
+      <c r="I4" s="148"/>
+      <c r="J4" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="176"/>
-      <c r="L4" s="189">
+      <c r="K4" s="148"/>
+      <c r="L4" s="161">
         <f t="shared" ref="L4:L48" si="0">COUNTIF(M4:AW4,"✓")</f>
         <v>3</v>
       </c>
-      <c r="M4" s="179"/>
-      <c r="N4" s="179"/>
-      <c r="O4" s="180"/>
-      <c r="P4" s="176"/>
-      <c r="Q4" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" s="176"/>
-      <c r="T4" s="176"/>
-      <c r="U4" s="176"/>
-      <c r="V4" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W4" s="176"/>
-      <c r="X4" s="176"/>
-      <c r="Y4" s="176"/>
-      <c r="Z4" s="176"/>
-      <c r="AA4" s="176"/>
-      <c r="AB4" s="176"/>
-      <c r="AC4" s="176"/>
-      <c r="AD4" s="176"/>
-    </row>
-    <row r="5" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A5" s="170" t="s">
+      <c r="M4" s="151"/>
+      <c r="N4" s="151"/>
+      <c r="O4" s="152"/>
+      <c r="P4" s="148"/>
+      <c r="Q4" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="148"/>
+      <c r="T4" s="148"/>
+      <c r="U4" s="148"/>
+      <c r="V4" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W4" s="148"/>
+      <c r="X4" s="148"/>
+      <c r="Y4" s="148"/>
+      <c r="Z4" s="148"/>
+      <c r="AA4" s="148"/>
+      <c r="AB4" s="148"/>
+      <c r="AC4" s="148"/>
+      <c r="AD4" s="148"/>
+    </row>
+    <row r="5" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A5" s="142" t="s">
         <v>245</v>
       </c>
-      <c r="B5" s="181" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="171" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="170" t="s">
+      <c r="B5" s="153" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="143" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="142" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="170" t="s">
+      <c r="E5" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="172">
+      <c r="F5" s="144">
         <v>2.5810185185185185E-3</v>
       </c>
-      <c r="G5" s="170" t="s">
+      <c r="G5" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="170"/>
-      <c r="I5" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5" s="170" t="s">
+      <c r="H5" s="142"/>
+      <c r="I5" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="170"/>
-      <c r="L5" s="189">
+      <c r="K5" s="142"/>
+      <c r="L5" s="161">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M5" s="173"/>
-      <c r="N5" s="173"/>
-      <c r="O5" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="P5" s="170"/>
-      <c r="Q5" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="R5" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S5" s="170"/>
-      <c r="T5" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="U5" s="170"/>
-      <c r="V5" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W5" s="170"/>
-      <c r="X5" s="170"/>
-      <c r="Y5" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z5" s="170"/>
-      <c r="AA5" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB5" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC5" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD5" s="170" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A6" s="176" t="s">
+      <c r="M5" s="145"/>
+      <c r="N5" s="145"/>
+      <c r="O5" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" s="142"/>
+      <c r="Q5" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="R5" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S5" s="142"/>
+      <c r="T5" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" s="142"/>
+      <c r="V5" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W5" s="142"/>
+      <c r="X5" s="142"/>
+      <c r="Y5" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z5" s="142"/>
+      <c r="AA5" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB5" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC5" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD5" s="142" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A6" s="148" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="176" t="s">
+      <c r="B6" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="148" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="176" t="s">
+      <c r="E6" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="178">
+      <c r="F6" s="150">
         <v>2.7199074074074074E-3</v>
       </c>
-      <c r="G6" s="176" t="s">
+      <c r="G6" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="176"/>
-      <c r="I6" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J6" s="176" t="s">
+      <c r="H6" s="148"/>
+      <c r="I6" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="148" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="176"/>
-      <c r="L6" s="189">
+      <c r="K6" s="148"/>
+      <c r="L6" s="161">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="M6" s="179"/>
-      <c r="N6" s="179"/>
-      <c r="O6" s="180"/>
-      <c r="P6" s="176"/>
-      <c r="Q6" s="176"/>
-      <c r="R6" s="176"/>
-      <c r="S6" s="176"/>
-      <c r="T6" s="176"/>
-      <c r="U6" s="176"/>
-      <c r="V6" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W6" s="176"/>
-      <c r="X6" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y6" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z6" s="176"/>
-      <c r="AA6" s="176"/>
-      <c r="AB6" s="176"/>
-      <c r="AC6" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD6" s="176"/>
-    </row>
-    <row r="7" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A7" s="170" t="s">
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="152"/>
+      <c r="P6" s="148"/>
+      <c r="Q6" s="148"/>
+      <c r="R6" s="148"/>
+      <c r="S6" s="148"/>
+      <c r="T6" s="148"/>
+      <c r="U6" s="148"/>
+      <c r="V6" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W6" s="148"/>
+      <c r="X6" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y6" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z6" s="148"/>
+      <c r="AA6" s="148"/>
+      <c r="AB6" s="148"/>
+      <c r="AC6" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD6" s="148"/>
+    </row>
+    <row r="7" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A7" s="142" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="170" t="s">
+      <c r="B7" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="142" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="170" t="s">
+      <c r="E7" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="172">
+      <c r="F7" s="144">
         <v>3.414351851851852E-3</v>
       </c>
-      <c r="G7" s="170" t="s">
+      <c r="G7" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="170"/>
-      <c r="I7" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J7" s="170" t="s">
+      <c r="H7" s="142"/>
+      <c r="I7" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="K7" s="170"/>
-      <c r="L7" s="189">
+      <c r="K7" s="142"/>
+      <c r="L7" s="161">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M7" s="173"/>
-      <c r="N7" s="173"/>
-      <c r="O7" s="170"/>
-      <c r="P7" s="170"/>
-      <c r="Q7" s="170"/>
-      <c r="R7" s="170"/>
-      <c r="S7" s="170"/>
-      <c r="T7" s="170"/>
-      <c r="U7" s="170"/>
-      <c r="V7" s="170"/>
-      <c r="W7" s="170"/>
-      <c r="X7" s="170"/>
-      <c r="Y7" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z7" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA7" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB7" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC7" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD7" s="170" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A8" s="176" t="s">
+      <c r="M7" s="145"/>
+      <c r="N7" s="145"/>
+      <c r="O7" s="142"/>
+      <c r="P7" s="142"/>
+      <c r="Q7" s="142"/>
+      <c r="R7" s="142"/>
+      <c r="S7" s="142"/>
+      <c r="T7" s="142"/>
+      <c r="U7" s="142"/>
+      <c r="V7" s="142"/>
+      <c r="W7" s="142"/>
+      <c r="X7" s="142"/>
+      <c r="Y7" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z7" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA7" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB7" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC7" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD7" s="142" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A8" s="148" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="176" t="s">
+      <c r="B8" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="148" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="176" t="s">
+      <c r="E8" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="178">
+      <c r="F8" s="150">
         <v>1.7476851851851852E-3</v>
       </c>
-      <c r="G8" s="176" t="s">
+      <c r="G8" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="H8" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J8" s="176" t="s">
+      <c r="H8" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" s="148" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="176"/>
-      <c r="L8" s="189">
+      <c r="K8" s="148"/>
+      <c r="L8" s="161">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="M8" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="N8" s="179"/>
-      <c r="O8" s="180" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" s="176"/>
-      <c r="Q8" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S8" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="T8" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="U8" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="V8" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W8" s="176"/>
-      <c r="X8" s="176"/>
-      <c r="Y8" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z8" s="176"/>
-      <c r="AA8" s="176"/>
-      <c r="AB8" s="176"/>
-      <c r="AC8" s="176"/>
-      <c r="AD8" s="176"/>
-    </row>
-    <row r="9" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A9" s="170" t="s">
+      <c r="M8" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="N8" s="151"/>
+      <c r="O8" s="152" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="148"/>
+      <c r="Q8" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="U8" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="V8" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W8" s="148"/>
+      <c r="X8" s="148"/>
+      <c r="Y8" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z8" s="148"/>
+      <c r="AA8" s="148"/>
+      <c r="AB8" s="148"/>
+      <c r="AC8" s="148"/>
+      <c r="AD8" s="148"/>
+    </row>
+    <row r="9" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A9" s="142" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="170" t="s">
+      <c r="B9" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="170" t="s">
+      <c r="E9" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="172">
+      <c r="F9" s="144">
         <v>2.1875000000000002E-3</v>
       </c>
-      <c r="G9" s="170" t="s">
+      <c r="G9" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="170"/>
-      <c r="I9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9" s="170" t="s">
+      <c r="H9" s="142"/>
+      <c r="I9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="170"/>
-      <c r="L9" s="189">
+      <c r="K9" s="142"/>
+      <c r="L9" s="161">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="M9" s="173" t="s">
-        <v>32</v>
-      </c>
-      <c r="N9" s="173" t="s">
-        <v>32</v>
-      </c>
-      <c r="O9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="R9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="T9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="U9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="X9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC9" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD9" s="170" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A10" s="176" t="s">
+      <c r="M9" s="145" t="s">
+        <v>32</v>
+      </c>
+      <c r="N9" s="145" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="U9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="X9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC9" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD9" s="142" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A10" s="148" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="176" t="s">
+      <c r="B10" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="148" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="176" t="s">
+      <c r="E10" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="178">
+      <c r="F10" s="150">
         <v>3.3449074074074076E-3</v>
       </c>
-      <c r="G10" s="176" t="s">
+      <c r="G10" s="148" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="176"/>
-      <c r="J10" s="176" t="s">
+      <c r="H10" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="148"/>
+      <c r="J10" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="K10" s="176"/>
-      <c r="L10" s="189">
+      <c r="K10" s="148"/>
+      <c r="L10" s="161">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M10" s="179"/>
-      <c r="N10" s="179"/>
-      <c r="O10" s="180"/>
-      <c r="P10" s="176"/>
-      <c r="Q10" s="176"/>
-      <c r="R10" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S10" s="176"/>
-      <c r="T10" s="176"/>
-      <c r="U10" s="176"/>
-      <c r="V10" s="176"/>
-      <c r="W10" s="176"/>
-      <c r="X10" s="176"/>
-      <c r="Y10" s="176"/>
-      <c r="Z10" s="176"/>
-      <c r="AA10" s="176"/>
-      <c r="AB10" s="176"/>
-      <c r="AC10" s="176"/>
-      <c r="AD10" s="176"/>
-    </row>
-    <row r="11" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A11" s="170" t="s">
+      <c r="M10" s="151"/>
+      <c r="N10" s="151"/>
+      <c r="O10" s="152"/>
+      <c r="P10" s="148"/>
+      <c r="Q10" s="148"/>
+      <c r="R10" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S10" s="148"/>
+      <c r="T10" s="148"/>
+      <c r="U10" s="148"/>
+      <c r="V10" s="148"/>
+      <c r="W10" s="148"/>
+      <c r="X10" s="148"/>
+      <c r="Y10" s="148"/>
+      <c r="Z10" s="148"/>
+      <c r="AA10" s="148"/>
+      <c r="AB10" s="148"/>
+      <c r="AC10" s="148"/>
+      <c r="AD10" s="148"/>
+    </row>
+    <row r="11" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A11" s="142" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="170" t="s">
+      <c r="B11" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="170" t="s">
+      <c r="E11" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="172">
+      <c r="F11" s="144">
         <v>5.5555555555555558E-3</v>
       </c>
-      <c r="G11" s="170" t="s">
+      <c r="G11" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="H11" s="170"/>
-      <c r="I11" s="170"/>
-      <c r="J11" s="170" t="s">
+      <c r="H11" s="142"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="170"/>
-      <c r="L11" s="189">
+      <c r="K11" s="142"/>
+      <c r="L11" s="161">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="M11" s="173" t="s">
-        <v>32</v>
-      </c>
-      <c r="N11" s="173" t="s">
-        <v>32</v>
-      </c>
-      <c r="O11" s="174" t="s">
-        <v>32</v>
-      </c>
-      <c r="P11" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q11" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="R11" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S11" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="T11" s="170"/>
-      <c r="U11" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V11" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W11" s="170"/>
-      <c r="X11" s="170"/>
-      <c r="Y11" s="170"/>
-      <c r="Z11" s="170"/>
-      <c r="AA11" s="170"/>
-      <c r="AB11" s="170"/>
-      <c r="AC11" s="170"/>
-      <c r="AD11" s="170"/>
-    </row>
-    <row r="12" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A12" s="176" t="s">
+      <c r="M11" s="145" t="s">
+        <v>32</v>
+      </c>
+      <c r="N11" s="145" t="s">
+        <v>32</v>
+      </c>
+      <c r="O11" s="146" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q11" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="R11" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S11" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="142"/>
+      <c r="U11" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V11" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W11" s="142"/>
+      <c r="X11" s="142"/>
+      <c r="Y11" s="142"/>
+      <c r="Z11" s="142"/>
+      <c r="AA11" s="142"/>
+      <c r="AB11" s="142"/>
+      <c r="AC11" s="142"/>
+      <c r="AD11" s="142"/>
+    </row>
+    <row r="12" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A12" s="148" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="176" t="s">
+      <c r="B12" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="148" t="s">
         <v>55</v>
       </c>
-      <c r="E12" s="176" t="s">
+      <c r="E12" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="178">
+      <c r="F12" s="150">
         <v>2.7430555555555554E-3</v>
       </c>
-      <c r="G12" s="176" t="s">
+      <c r="G12" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="H12" s="176"/>
-      <c r="I12" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J12" s="176" t="s">
+      <c r="H12" s="148"/>
+      <c r="I12" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="K12" s="176"/>
-      <c r="L12" s="189">
+      <c r="K12" s="148"/>
+      <c r="L12" s="161">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="M12" s="179"/>
-      <c r="N12" s="179"/>
-      <c r="O12" s="176"/>
-      <c r="P12" s="176"/>
-      <c r="Q12" s="176"/>
-      <c r="R12" s="176"/>
-      <c r="S12" s="176"/>
-      <c r="T12" s="176"/>
-      <c r="U12" s="176"/>
-      <c r="V12" s="176"/>
-      <c r="W12" s="176"/>
-      <c r="X12" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y12" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z12" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA12" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB12" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC12" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD12" s="176" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A13" s="170" t="s">
+      <c r="M12" s="151"/>
+      <c r="N12" s="151"/>
+      <c r="O12" s="148"/>
+      <c r="P12" s="148"/>
+      <c r="Q12" s="148"/>
+      <c r="R12" s="148"/>
+      <c r="S12" s="148"/>
+      <c r="T12" s="148"/>
+      <c r="U12" s="148"/>
+      <c r="V12" s="148"/>
+      <c r="W12" s="148"/>
+      <c r="X12" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y12" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z12" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA12" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB12" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC12" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD12" s="148" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A13" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="170" t="s">
+      <c r="B13" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="170" t="s">
+      <c r="E13" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="172">
+      <c r="F13" s="144">
         <v>2.3032407407407407E-3</v>
       </c>
-      <c r="G13" s="170" t="s">
+      <c r="G13" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="H13" s="170"/>
-      <c r="I13" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J13" s="170" t="s">
+      <c r="H13" s="142"/>
+      <c r="I13" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="142" t="s">
         <v>60</v>
       </c>
-      <c r="K13" s="170"/>
-      <c r="L13" s="189">
+      <c r="K13" s="142"/>
+      <c r="L13" s="161">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="M13" s="173"/>
-      <c r="N13" s="173"/>
-      <c r="O13" s="174"/>
-      <c r="P13" s="170"/>
-      <c r="Q13" s="170"/>
-      <c r="R13" s="170"/>
-      <c r="S13" s="170"/>
-      <c r="T13" s="170"/>
-      <c r="U13" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V13" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W13" s="170"/>
-      <c r="X13" s="170"/>
-      <c r="Y13" s="170"/>
-      <c r="Z13" s="170"/>
-      <c r="AA13" s="170"/>
-      <c r="AB13" s="170"/>
-      <c r="AC13" s="170"/>
-      <c r="AD13" s="170"/>
-    </row>
-    <row r="14" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A14" s="176" t="s">
+      <c r="M13" s="145"/>
+      <c r="N13" s="145"/>
+      <c r="O13" s="146"/>
+      <c r="P13" s="142"/>
+      <c r="Q13" s="142"/>
+      <c r="R13" s="142"/>
+      <c r="S13" s="142"/>
+      <c r="T13" s="142"/>
+      <c r="U13" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V13" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W13" s="142"/>
+      <c r="X13" s="142"/>
+      <c r="Y13" s="142"/>
+      <c r="Z13" s="142"/>
+      <c r="AA13" s="142"/>
+      <c r="AB13" s="142"/>
+      <c r="AC13" s="142"/>
+      <c r="AD13" s="142"/>
+    </row>
+    <row r="14" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A14" s="148" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="183" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="176" t="s">
+      <c r="B14" s="155" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="148" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="176" t="s">
+      <c r="E14" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F14" s="178">
+      <c r="F14" s="150">
         <v>1.7708333333333332E-3</v>
       </c>
-      <c r="G14" s="176" t="s">
+      <c r="G14" s="148" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="176"/>
-      <c r="I14" s="176"/>
-      <c r="J14" s="176" t="s">
+      <c r="H14" s="148"/>
+      <c r="I14" s="148"/>
+      <c r="J14" s="148" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="176"/>
-      <c r="L14" s="189">
+      <c r="K14" s="148"/>
+      <c r="L14" s="161">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M14" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="N14" s="179"/>
-      <c r="O14" s="180"/>
-      <c r="P14" s="176"/>
-      <c r="Q14" s="176"/>
-      <c r="R14" s="176"/>
-      <c r="S14" s="176"/>
-      <c r="T14" s="176"/>
-      <c r="U14" s="176"/>
-      <c r="V14" s="176"/>
-      <c r="W14" s="176"/>
-      <c r="X14" s="176"/>
-      <c r="Y14" s="176"/>
-      <c r="Z14" s="176"/>
-      <c r="AA14" s="176"/>
-      <c r="AB14" s="176"/>
-      <c r="AC14" s="176"/>
-      <c r="AD14" s="176"/>
-    </row>
-    <row r="15" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A15" s="170" t="s">
+      <c r="M14" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="N14" s="151"/>
+      <c r="O14" s="152"/>
+      <c r="P14" s="148"/>
+      <c r="Q14" s="148"/>
+      <c r="R14" s="148"/>
+      <c r="S14" s="148"/>
+      <c r="T14" s="148"/>
+      <c r="U14" s="148"/>
+      <c r="V14" s="148"/>
+      <c r="W14" s="148"/>
+      <c r="X14" s="148"/>
+      <c r="Y14" s="148"/>
+      <c r="Z14" s="148"/>
+      <c r="AA14" s="148"/>
+      <c r="AB14" s="148"/>
+      <c r="AC14" s="148"/>
+      <c r="AD14" s="148"/>
+    </row>
+    <row r="15" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A15" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="170" t="s">
+      <c r="B15" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="142" t="s">
         <v>64</v>
       </c>
-      <c r="E15" s="170" t="s">
+      <c r="E15" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="172">
+      <c r="F15" s="144">
         <v>2.7893518518518519E-3</v>
       </c>
-      <c r="G15" s="170" t="s">
+      <c r="G15" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="170"/>
-      <c r="I15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J15" s="170" t="s">
+      <c r="H15" s="142"/>
+      <c r="I15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="K15" s="170"/>
-      <c r="L15" s="189">
+      <c r="K15" s="142"/>
+      <c r="L15" s="161">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="M15" s="173"/>
-      <c r="N15" s="173" t="s">
-        <v>32</v>
-      </c>
-      <c r="O15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="R15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S15" s="170"/>
-      <c r="T15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="U15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="X15" s="170"/>
-      <c r="Y15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z15" s="170"/>
-      <c r="AA15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC15" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD15" s="170" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A16" s="176" t="s">
+      <c r="M15" s="145"/>
+      <c r="N15" s="145" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S15" s="142"/>
+      <c r="T15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="U15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="X15" s="142"/>
+      <c r="Y15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z15" s="142"/>
+      <c r="AA15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC15" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD15" s="142" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A16" s="148" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="176" t="s">
+      <c r="B16" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="176" t="s">
+      <c r="E16" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="178">
+      <c r="F16" s="150">
         <v>2.488425925925926E-3</v>
       </c>
-      <c r="G16" s="176" t="s">
+      <c r="G16" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="176"/>
-      <c r="I16" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J16" s="176" t="s">
+      <c r="H16" s="148"/>
+      <c r="I16" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="K16" s="176"/>
-      <c r="L16" s="189">
+      <c r="K16" s="148"/>
+      <c r="L16" s="161">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="M16" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="N16" s="179"/>
-      <c r="O16" s="180" t="s">
-        <v>32</v>
-      </c>
-      <c r="P16" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q16" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R16" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S16" s="176"/>
-      <c r="T16" s="176"/>
-      <c r="U16" s="176"/>
-      <c r="V16" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W16" s="176"/>
-      <c r="X16" s="176"/>
-      <c r="Y16" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z16" s="176"/>
-      <c r="AA16" s="176"/>
-      <c r="AB16" s="176"/>
-      <c r="AC16" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD16" s="176"/>
-    </row>
-    <row r="17" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A17" s="170" t="s">
+      <c r="M16" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16" s="151"/>
+      <c r="O16" s="152" t="s">
+        <v>32</v>
+      </c>
+      <c r="P16" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q16" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R16" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S16" s="148"/>
+      <c r="T16" s="148"/>
+      <c r="U16" s="148"/>
+      <c r="V16" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W16" s="148"/>
+      <c r="X16" s="148"/>
+      <c r="Y16" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z16" s="148"/>
+      <c r="AA16" s="148"/>
+      <c r="AB16" s="148"/>
+      <c r="AC16" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD16" s="148"/>
+    </row>
+    <row r="17" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A17" s="142" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="170" t="s">
+      <c r="B17" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="142" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="170" t="s">
+      <c r="E17" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="172">
+      <c r="F17" s="144">
         <v>1.9328703703703704E-3</v>
       </c>
-      <c r="G17" s="170" t="s">
+      <c r="G17" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="170"/>
-      <c r="I17" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J17" s="170" t="s">
+      <c r="H17" s="142"/>
+      <c r="I17" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="170"/>
-      <c r="L17" s="189">
+      <c r="K17" s="142"/>
+      <c r="L17" s="161">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M17" s="173"/>
-      <c r="N17" s="173"/>
-      <c r="O17" s="174"/>
-      <c r="P17" s="170"/>
-      <c r="Q17" s="170"/>
-      <c r="R17" s="170"/>
-      <c r="S17" s="170"/>
-      <c r="T17" s="170"/>
-      <c r="U17" s="170"/>
-      <c r="V17" s="170"/>
-      <c r="W17" s="170"/>
-      <c r="X17" s="170"/>
-      <c r="Y17" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z17" s="170"/>
-      <c r="AA17" s="170"/>
-      <c r="AB17" s="170"/>
-      <c r="AC17" s="170"/>
-      <c r="AD17" s="170"/>
-    </row>
-    <row r="18" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A18" s="176" t="s">
+      <c r="M17" s="145"/>
+      <c r="N17" s="145"/>
+      <c r="O17" s="146"/>
+      <c r="P17" s="142"/>
+      <c r="Q17" s="142"/>
+      <c r="R17" s="142"/>
+      <c r="S17" s="142"/>
+      <c r="T17" s="142"/>
+      <c r="U17" s="142"/>
+      <c r="V17" s="142"/>
+      <c r="W17" s="142"/>
+      <c r="X17" s="142"/>
+      <c r="Y17" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z17" s="142"/>
+      <c r="AA17" s="142"/>
+      <c r="AB17" s="142"/>
+      <c r="AC17" s="142"/>
+      <c r="AD17" s="142"/>
+    </row>
+    <row r="18" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A18" s="148" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="176" t="s">
+      <c r="B18" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C18" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="176" t="s">
+      <c r="E18" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="178">
+      <c r="F18" s="150">
         <v>2.4305555555555556E-3</v>
       </c>
-      <c r="G18" s="176" t="s">
+      <c r="G18" s="148" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="176"/>
-      <c r="I18" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="176" t="s">
+      <c r="H18" s="148"/>
+      <c r="I18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" s="148" t="s">
         <v>69</v>
       </c>
-      <c r="K18" s="176"/>
-      <c r="L18" s="189">
+      <c r="K18" s="148"/>
+      <c r="L18" s="161">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="M18" s="179"/>
-      <c r="N18" s="179"/>
-      <c r="O18" s="176"/>
-      <c r="P18" s="176"/>
-      <c r="Q18" s="176"/>
-      <c r="R18" s="176"/>
-      <c r="S18" s="176"/>
-      <c r="T18" s="176"/>
-      <c r="U18" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="V18" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W18" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="X18" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y18" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z18" s="176"/>
-      <c r="AA18" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB18" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC18" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD18" s="176" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A19" s="170" t="s">
+      <c r="M18" s="151"/>
+      <c r="N18" s="151"/>
+      <c r="O18" s="148"/>
+      <c r="P18" s="148"/>
+      <c r="Q18" s="148"/>
+      <c r="R18" s="148"/>
+      <c r="S18" s="148"/>
+      <c r="T18" s="148"/>
+      <c r="U18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="V18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="X18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z18" s="148"/>
+      <c r="AA18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD18" s="148" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A19" s="142" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D19" s="170" t="s">
+      <c r="B19" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="170" t="s">
+      <c r="E19" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="172">
+      <c r="F19" s="144">
         <v>2.6041666666666665E-3</v>
       </c>
-      <c r="G19" s="170" t="s">
+      <c r="G19" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="170"/>
-      <c r="I19" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J19" s="170" t="s">
+      <c r="H19" s="142"/>
+      <c r="I19" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" s="142" t="s">
         <v>56</v>
       </c>
-      <c r="K19" s="170"/>
-      <c r="L19" s="189">
+      <c r="K19" s="142"/>
+      <c r="L19" s="161">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M19" s="173"/>
-      <c r="N19" s="173"/>
-      <c r="O19" s="170"/>
-      <c r="P19" s="170"/>
-      <c r="Q19" s="170"/>
-      <c r="R19" s="170"/>
-      <c r="S19" s="170"/>
-      <c r="T19" s="170"/>
-      <c r="U19" s="170"/>
-      <c r="V19" s="170"/>
-      <c r="W19" s="170"/>
-      <c r="X19" s="170"/>
-      <c r="Y19" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z19" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA19" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB19" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC19" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD19" s="170" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A20" s="176" t="s">
+      <c r="M19" s="145"/>
+      <c r="N19" s="145"/>
+      <c r="O19" s="142"/>
+      <c r="P19" s="142"/>
+      <c r="Q19" s="142"/>
+      <c r="R19" s="142"/>
+      <c r="S19" s="142"/>
+      <c r="T19" s="142"/>
+      <c r="U19" s="142"/>
+      <c r="V19" s="142"/>
+      <c r="W19" s="142"/>
+      <c r="X19" s="142"/>
+      <c r="Y19" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z19" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA19" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB19" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC19" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD19" s="142" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A20" s="148" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D20" s="176" t="s">
+      <c r="B20" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="148" t="s">
         <v>75</v>
       </c>
-      <c r="E20" s="176" t="s">
+      <c r="E20" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="178">
+      <c r="F20" s="150">
         <v>4.6874999999999998E-3</v>
       </c>
-      <c r="G20" s="176" t="s">
+      <c r="G20" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="H20" s="176"/>
-      <c r="I20" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J20" s="176" t="s">
+      <c r="H20" s="148"/>
+      <c r="I20" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="K20" s="176"/>
-      <c r="L20" s="189">
+      <c r="K20" s="148"/>
+      <c r="L20" s="161">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="M20" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="N20" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="O20" s="180"/>
-      <c r="P20" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q20" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R20" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S20" s="176"/>
-      <c r="T20" s="176"/>
-      <c r="U20" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="V20" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W20" s="176"/>
-      <c r="X20" s="176"/>
-      <c r="Y20" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z20" s="176"/>
-      <c r="AA20" s="176"/>
-      <c r="AB20" s="176"/>
-      <c r="AC20" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD20" s="176"/>
-    </row>
-    <row r="21" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A21" s="170" t="s">
+      <c r="M20" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="O20" s="152"/>
+      <c r="P20" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q20" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R20" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S20" s="148"/>
+      <c r="T20" s="148"/>
+      <c r="U20" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="V20" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W20" s="148"/>
+      <c r="X20" s="148"/>
+      <c r="Y20" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z20" s="148"/>
+      <c r="AA20" s="148"/>
+      <c r="AB20" s="148"/>
+      <c r="AC20" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD20" s="148"/>
+    </row>
+    <row r="21" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A21" s="142" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="170" t="s">
+      <c r="B21" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="142" t="s">
         <v>77</v>
       </c>
-      <c r="E21" s="170" t="s">
+      <c r="E21" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F21" s="172">
+      <c r="F21" s="144">
         <v>2.5115740740740741E-3</v>
       </c>
-      <c r="G21" s="170" t="s">
+      <c r="G21" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="H21" s="170"/>
-      <c r="I21" s="170"/>
-      <c r="J21" s="170" t="s">
+      <c r="H21" s="142"/>
+      <c r="I21" s="142"/>
+      <c r="J21" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="K21" s="170"/>
-      <c r="L21" s="189">
+      <c r="K21" s="142"/>
+      <c r="L21" s="161">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M21" s="173"/>
-      <c r="N21" s="173"/>
-      <c r="O21" s="174"/>
-      <c r="P21" s="170"/>
-      <c r="Q21" s="170"/>
-      <c r="R21" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S21" s="170"/>
-      <c r="T21" s="170"/>
-      <c r="U21" s="170"/>
-      <c r="V21" s="170"/>
-      <c r="W21" s="170"/>
-      <c r="X21" s="170"/>
-      <c r="Y21" s="170"/>
-      <c r="Z21" s="170"/>
-      <c r="AA21" s="170"/>
-      <c r="AB21" s="170"/>
-      <c r="AC21" s="170"/>
-      <c r="AD21" s="170"/>
-    </row>
-    <row r="22" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A22" s="176" t="s">
+      <c r="M21" s="145"/>
+      <c r="N21" s="145"/>
+      <c r="O21" s="146"/>
+      <c r="P21" s="142"/>
+      <c r="Q21" s="142"/>
+      <c r="R21" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S21" s="142"/>
+      <c r="T21" s="142"/>
+      <c r="U21" s="142"/>
+      <c r="V21" s="142"/>
+      <c r="W21" s="142"/>
+      <c r="X21" s="142"/>
+      <c r="Y21" s="142"/>
+      <c r="Z21" s="142"/>
+      <c r="AA21" s="142"/>
+      <c r="AB21" s="142"/>
+      <c r="AC21" s="142"/>
+      <c r="AD21" s="142"/>
+    </row>
+    <row r="22" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A22" s="148" t="s">
         <v>78</v>
       </c>
-      <c r="B22" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="176" t="s">
+      <c r="B22" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="148" t="s">
         <v>79</v>
       </c>
-      <c r="E22" s="176" t="s">
+      <c r="E22" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="178">
+      <c r="F22" s="150">
         <v>2.5810185185185185E-3</v>
       </c>
-      <c r="G22" s="176" t="s">
+      <c r="G22" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="H22" s="176"/>
-      <c r="I22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="176" t="s">
+      <c r="H22" s="148"/>
+      <c r="I22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="K22" s="176"/>
-      <c r="L22" s="189">
+      <c r="K22" s="148"/>
+      <c r="L22" s="161">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="M22" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="N22" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="O22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="P22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="T22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="U22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="V22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="X22" s="176"/>
-      <c r="Y22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC22" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD22" s="176" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A23" s="170" t="s">
+      <c r="M22" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="O22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="P22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="T22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="U22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="V22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="X22" s="148"/>
+      <c r="Y22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC22" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD22" s="148" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A23" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="171" t="s">
-        <v>2</v>
-      </c>
-      <c r="C23" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="170" t="s">
+      <c r="B23" s="143" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="142" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="170" t="s">
+      <c r="E23" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="172">
+      <c r="F23" s="144">
         <v>2.6041666666666665E-3</v>
       </c>
-      <c r="G23" s="170" t="s">
+      <c r="G23" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="H23" s="170"/>
-      <c r="I23" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J23" s="170" t="s">
+      <c r="H23" s="142"/>
+      <c r="I23" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="K23" s="170"/>
-      <c r="L23" s="189">
+      <c r="K23" s="142"/>
+      <c r="L23" s="161">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="M23" s="173"/>
-      <c r="N23" s="173"/>
-      <c r="O23" s="174"/>
-      <c r="P23" s="170"/>
-      <c r="Q23" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="R23" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S23" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="T23" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="U23" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V23" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W23" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="X23" s="170"/>
-      <c r="Y23" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z23" s="170"/>
-      <c r="AA23" s="170"/>
-      <c r="AB23" s="170"/>
-      <c r="AC23" s="170"/>
-      <c r="AD23" s="170"/>
-    </row>
-    <row r="24" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A24" s="176" t="s">
+      <c r="M23" s="145"/>
+      <c r="N23" s="145"/>
+      <c r="O23" s="146"/>
+      <c r="P23" s="142"/>
+      <c r="Q23" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="R23" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S23" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="T23" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="U23" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V23" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W23" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="X23" s="142"/>
+      <c r="Y23" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z23" s="142"/>
+      <c r="AA23" s="142"/>
+      <c r="AB23" s="142"/>
+      <c r="AC23" s="142"/>
+      <c r="AD23" s="142"/>
+    </row>
+    <row r="24" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A24" s="148" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="184"/>
-      <c r="D24" s="176" t="s">
+      <c r="B24" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="156"/>
+      <c r="D24" s="148" t="s">
         <v>83</v>
       </c>
-      <c r="E24" s="176" t="s">
+      <c r="E24" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F24" s="178">
+      <c r="F24" s="150">
         <v>3.8541666666666668E-3</v>
       </c>
-      <c r="G24" s="176" t="s">
+      <c r="G24" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="176"/>
-      <c r="I24" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J24" s="176" t="s">
+      <c r="H24" s="148"/>
+      <c r="I24" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="148" t="s">
         <v>84</v>
       </c>
-      <c r="K24" s="176"/>
-      <c r="L24" s="189">
+      <c r="K24" s="148"/>
+      <c r="L24" s="161">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="M24" s="179"/>
-      <c r="N24" s="179"/>
-      <c r="O24" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="P24" s="176"/>
-      <c r="Q24" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R24" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S24" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="T24" s="176"/>
-      <c r="U24" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="V24" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W24" s="176"/>
-      <c r="X24" s="176"/>
-      <c r="Y24" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z24" s="176"/>
-      <c r="AA24" s="176"/>
-      <c r="AB24" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC24" s="176"/>
-      <c r="AD24" s="176"/>
-    </row>
-    <row r="25" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A25" s="170" t="s">
+      <c r="M24" s="151"/>
+      <c r="N24" s="151"/>
+      <c r="O24" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="P24" s="148"/>
+      <c r="Q24" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R24" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S24" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="T24" s="148"/>
+      <c r="U24" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="V24" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W24" s="148"/>
+      <c r="X24" s="148"/>
+      <c r="Y24" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z24" s="148"/>
+      <c r="AA24" s="148"/>
+      <c r="AB24" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC24" s="148"/>
+      <c r="AD24" s="148"/>
+    </row>
+    <row r="25" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A25" s="142" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C25" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="170" t="s">
+      <c r="B25" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="142" t="s">
         <v>86</v>
       </c>
-      <c r="E25" s="170" t="s">
+      <c r="E25" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F25" s="172">
+      <c r="F25" s="144">
         <v>1.9791666666666668E-3</v>
       </c>
-      <c r="G25" s="170" t="s">
+      <c r="G25" s="142" t="s">
         <v>48</v>
       </c>
-      <c r="H25" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J25" s="170" t="s">
+      <c r="H25" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" s="142" t="s">
         <v>37</v>
       </c>
-      <c r="K25" s="170"/>
-      <c r="L25" s="189">
+      <c r="K25" s="142"/>
+      <c r="L25" s="161">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="M25" s="173"/>
-      <c r="N25" s="173"/>
-      <c r="O25" s="174" t="s">
-        <v>32</v>
-      </c>
-      <c r="P25" s="174" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q25" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="R25" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S25" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="T25" s="170"/>
-      <c r="U25" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V25" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W25" s="170"/>
-      <c r="X25" s="170"/>
-      <c r="Y25" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z25" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA25" s="170"/>
-      <c r="AB25" s="170"/>
-      <c r="AC25" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD25" s="170" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A26" s="176" t="s">
+      <c r="M25" s="145"/>
+      <c r="N25" s="145"/>
+      <c r="O25" s="146" t="s">
+        <v>32</v>
+      </c>
+      <c r="P25" s="146" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q25" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="R25" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S25" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="T25" s="142"/>
+      <c r="U25" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V25" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W25" s="142"/>
+      <c r="X25" s="142"/>
+      <c r="Y25" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z25" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA25" s="142"/>
+      <c r="AB25" s="142"/>
+      <c r="AC25" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD25" s="142" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A26" s="148" t="s">
         <v>87</v>
       </c>
-      <c r="B26" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="176" t="s">
+      <c r="B26" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="148" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="176" t="s">
+      <c r="E26" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F26" s="178">
+      <c r="F26" s="150">
         <v>2.650462962962963E-3</v>
       </c>
-      <c r="G26" s="176" t="s">
+      <c r="G26" s="148" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="176"/>
-      <c r="I26" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J26" s="176" t="s">
+      <c r="H26" s="148"/>
+      <c r="I26" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="K26" s="176"/>
-      <c r="L26" s="189">
+      <c r="K26" s="148"/>
+      <c r="L26" s="161">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M26" s="179"/>
-      <c r="N26" s="179"/>
-      <c r="O26" s="180"/>
-      <c r="P26" s="180"/>
-      <c r="Q26" s="180"/>
-      <c r="R26" s="180"/>
-      <c r="S26" s="180"/>
-      <c r="T26" s="180"/>
-      <c r="U26" s="180"/>
-      <c r="V26" s="180"/>
-      <c r="W26" s="180"/>
-      <c r="X26" s="180"/>
-      <c r="Y26" s="180"/>
-      <c r="Z26" s="180"/>
-      <c r="AA26" s="180"/>
-      <c r="AB26" s="180"/>
-      <c r="AC26" s="180" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD26" s="180"/>
-    </row>
-    <row r="27" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A27" s="170" t="s">
+      <c r="M26" s="151"/>
+      <c r="N26" s="151"/>
+      <c r="O26" s="152"/>
+      <c r="P26" s="152"/>
+      <c r="Q26" s="152"/>
+      <c r="R26" s="152"/>
+      <c r="S26" s="152"/>
+      <c r="T26" s="152"/>
+      <c r="U26" s="152"/>
+      <c r="V26" s="152"/>
+      <c r="W26" s="152"/>
+      <c r="X26" s="152"/>
+      <c r="Y26" s="152"/>
+      <c r="Z26" s="152"/>
+      <c r="AA26" s="152"/>
+      <c r="AB26" s="152"/>
+      <c r="AC26" s="152" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD26" s="152"/>
+    </row>
+    <row r="27" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A27" s="142" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C27" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="170" t="s">
+      <c r="B27" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="142" t="s">
         <v>51</v>
       </c>
-      <c r="E27" s="170" t="s">
+      <c r="E27" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="172">
+      <c r="F27" s="144">
         <v>3.0439814814814813E-3</v>
       </c>
-      <c r="G27" s="170" t="s">
+      <c r="G27" s="142" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J27" s="170" t="s">
+      <c r="H27" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J27" s="142" t="s">
         <v>40</v>
       </c>
-      <c r="K27" s="170"/>
-      <c r="L27" s="189">
+      <c r="K27" s="142"/>
+      <c r="L27" s="161">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="M27" s="173"/>
-      <c r="N27" s="173"/>
-      <c r="O27" s="170"/>
-      <c r="P27" s="170"/>
-      <c r="Q27" s="170"/>
-      <c r="R27" s="170"/>
-      <c r="S27" s="170"/>
-      <c r="T27" s="170"/>
-      <c r="U27" s="170"/>
-      <c r="V27" s="170"/>
-      <c r="W27" s="170"/>
-      <c r="X27" s="170"/>
-      <c r="Y27" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z27" s="170"/>
-      <c r="AA27" s="170"/>
-      <c r="AB27" s="170"/>
-      <c r="AC27" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD27" s="170"/>
-    </row>
-    <row r="28" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A28" s="176" t="s">
+      <c r="M27" s="145"/>
+      <c r="N27" s="145"/>
+      <c r="O27" s="142"/>
+      <c r="P27" s="142"/>
+      <c r="Q27" s="142"/>
+      <c r="R27" s="142"/>
+      <c r="S27" s="142"/>
+      <c r="T27" s="142"/>
+      <c r="U27" s="142"/>
+      <c r="V27" s="142"/>
+      <c r="W27" s="142"/>
+      <c r="X27" s="142"/>
+      <c r="Y27" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z27" s="142"/>
+      <c r="AA27" s="142"/>
+      <c r="AB27" s="142"/>
+      <c r="AC27" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD27" s="142"/>
+    </row>
+    <row r="28" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A28" s="148" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="176" t="s">
+      <c r="B28" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="148" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="176" t="s">
+      <c r="E28" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="178">
+      <c r="F28" s="150">
         <v>2.8587962962962963E-3</v>
       </c>
-      <c r="G28" s="176" t="s">
+      <c r="G28" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="176"/>
-      <c r="I28" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" s="176" t="s">
+      <c r="H28" s="148"/>
+      <c r="I28" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J28" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="K28" s="176"/>
-      <c r="L28" s="189">
+      <c r="K28" s="148"/>
+      <c r="L28" s="161">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M28" s="179"/>
-      <c r="N28" s="179"/>
-      <c r="O28" s="176"/>
-      <c r="P28" s="176"/>
-      <c r="Q28" s="176"/>
-      <c r="R28" s="176"/>
-      <c r="S28" s="176"/>
-      <c r="T28" s="176"/>
-      <c r="U28" s="176"/>
-      <c r="V28" s="176"/>
-      <c r="W28" s="176"/>
-      <c r="X28" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y28" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z28" s="176"/>
-      <c r="AA28" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB28" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC28" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD28" s="176" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A29" s="170" t="s">
+      <c r="M28" s="151"/>
+      <c r="N28" s="151"/>
+      <c r="O28" s="148"/>
+      <c r="P28" s="148"/>
+      <c r="Q28" s="148"/>
+      <c r="R28" s="148"/>
+      <c r="S28" s="148"/>
+      <c r="T28" s="148"/>
+      <c r="U28" s="148"/>
+      <c r="V28" s="148"/>
+      <c r="W28" s="148"/>
+      <c r="X28" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y28" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z28" s="148"/>
+      <c r="AA28" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB28" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC28" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD28" s="148" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A29" s="142" t="s">
         <v>92</v>
       </c>
-      <c r="B29" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C29" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="170" t="s">
+      <c r="B29" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="142" t="s">
         <v>93</v>
       </c>
-      <c r="E29" s="170" t="s">
+      <c r="E29" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F29" s="172">
+      <c r="F29" s="144">
         <v>2.0486111111111113E-3</v>
       </c>
-      <c r="G29" s="170" t="s">
+      <c r="G29" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="170"/>
-      <c r="I29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J29" s="170" t="s">
+      <c r="H29" s="142"/>
+      <c r="I29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="K29" s="170"/>
-      <c r="L29" s="189">
+      <c r="K29" s="142"/>
+      <c r="L29" s="161">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="M29" s="173"/>
-      <c r="N29" s="173" t="s">
-        <v>32</v>
-      </c>
-      <c r="O29" s="174" t="s">
-        <v>32</v>
-      </c>
-      <c r="P29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="R29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="T29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="U29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W29" s="170"/>
-      <c r="X29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z29" s="170"/>
-      <c r="AA29" s="170"/>
-      <c r="AB29" s="170"/>
-      <c r="AC29" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD29" s="170"/>
-    </row>
-    <row r="30" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A30" s="176" t="s">
+      <c r="M29" s="145"/>
+      <c r="N29" s="145" t="s">
+        <v>32</v>
+      </c>
+      <c r="O29" s="146" t="s">
+        <v>32</v>
+      </c>
+      <c r="P29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="R29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="T29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="U29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W29" s="142"/>
+      <c r="X29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z29" s="142"/>
+      <c r="AA29" s="142"/>
+      <c r="AB29" s="142"/>
+      <c r="AC29" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD29" s="142"/>
+    </row>
+    <row r="30" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A30" s="148" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="176" t="s">
+      <c r="B30" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="148" t="s">
         <v>95</v>
       </c>
-      <c r="E30" s="176" t="s">
+      <c r="E30" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F30" s="178">
+      <c r="F30" s="150">
         <v>3.5995370370370369E-3</v>
       </c>
-      <c r="G30" s="176" t="s">
+      <c r="G30" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="H30" s="176"/>
-      <c r="I30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J30" s="176" t="s">
+      <c r="H30" s="148"/>
+      <c r="I30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="K30" s="176"/>
-      <c r="L30" s="189">
+      <c r="K30" s="148"/>
+      <c r="L30" s="161">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="M30" s="179"/>
-      <c r="N30" s="179"/>
-      <c r="O30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="P30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="T30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="U30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="V30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="X30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC30" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD30" s="176"/>
-    </row>
-    <row r="31" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A31" s="170" t="s">
+      <c r="M30" s="151"/>
+      <c r="N30" s="151"/>
+      <c r="O30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="P30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="T30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="U30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="V30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="X30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC30" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD30" s="148"/>
+    </row>
+    <row r="31" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A31" s="142" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="170" t="s">
+      <c r="B31" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="142" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="170" t="s">
+      <c r="E31" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F31" s="172">
+      <c r="F31" s="144">
         <v>1.9675925925925924E-3</v>
       </c>
-      <c r="G31" s="170" t="s">
+      <c r="G31" s="142" t="s">
         <v>48</v>
       </c>
-      <c r="H31" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="170"/>
-      <c r="J31" s="170" t="s">
+      <c r="H31" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="I31" s="142"/>
+      <c r="J31" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="K31" s="170"/>
-      <c r="L31" s="189">
+      <c r="K31" s="142"/>
+      <c r="L31" s="161">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="M31" s="173" t="s">
-        <v>32</v>
-      </c>
-      <c r="N31" s="173"/>
-      <c r="O31" s="174"/>
-      <c r="P31" s="170"/>
-      <c r="Q31" s="170"/>
-      <c r="R31" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S31" s="170"/>
-      <c r="T31" s="170"/>
-      <c r="U31" s="170"/>
-      <c r="V31" s="170"/>
-      <c r="W31" s="170"/>
-      <c r="X31" s="170"/>
-      <c r="Y31" s="170"/>
-      <c r="Z31" s="170"/>
-      <c r="AA31" s="170"/>
-      <c r="AB31" s="170"/>
-      <c r="AC31" s="170"/>
-      <c r="AD31" s="170"/>
-    </row>
-    <row r="32" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A32" s="176" t="s">
+      <c r="M31" s="145" t="s">
+        <v>32</v>
+      </c>
+      <c r="N31" s="145"/>
+      <c r="O31" s="146"/>
+      <c r="P31" s="142"/>
+      <c r="Q31" s="142"/>
+      <c r="R31" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S31" s="142"/>
+      <c r="T31" s="142"/>
+      <c r="U31" s="142"/>
+      <c r="V31" s="142"/>
+      <c r="W31" s="142"/>
+      <c r="X31" s="142"/>
+      <c r="Y31" s="142"/>
+      <c r="Z31" s="142"/>
+      <c r="AA31" s="142"/>
+      <c r="AB31" s="142"/>
+      <c r="AC31" s="142"/>
+      <c r="AD31" s="142"/>
+    </row>
+    <row r="32" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A32" s="148" t="s">
         <v>97</v>
       </c>
-      <c r="B32" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="176" t="s">
+      <c r="B32" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D32" s="148" t="s">
         <v>98</v>
       </c>
-      <c r="E32" s="176" t="s">
+      <c r="E32" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F32" s="178">
+      <c r="F32" s="150">
         <v>3.2291666666666666E-3</v>
       </c>
-      <c r="G32" s="176" t="s">
+      <c r="G32" s="148" t="s">
         <v>31</v>
       </c>
-      <c r="H32" s="176"/>
-      <c r="I32" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J32" s="176" t="s">
+      <c r="H32" s="148"/>
+      <c r="I32" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J32" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="K32" s="176"/>
-      <c r="L32" s="189">
+      <c r="K32" s="148"/>
+      <c r="L32" s="161">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="M32" s="179"/>
-      <c r="N32" s="179"/>
-      <c r="O32" s="180" t="s">
-        <v>32</v>
-      </c>
-      <c r="P32" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q32" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R32" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S32" s="176"/>
-      <c r="T32" s="176"/>
-      <c r="U32" s="176"/>
-      <c r="V32" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W32" s="176"/>
-      <c r="X32" s="176"/>
-      <c r="Y32" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z32" s="176"/>
-      <c r="AA32" s="176"/>
-      <c r="AB32" s="176"/>
-      <c r="AC32" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD32" s="176"/>
-    </row>
-    <row r="33" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A33" s="170" t="s">
+      <c r="M32" s="151"/>
+      <c r="N32" s="151"/>
+      <c r="O32" s="152" t="s">
+        <v>32</v>
+      </c>
+      <c r="P32" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q32" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R32" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S32" s="148"/>
+      <c r="T32" s="148"/>
+      <c r="U32" s="148"/>
+      <c r="V32" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W32" s="148"/>
+      <c r="X32" s="148"/>
+      <c r="Y32" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z32" s="148"/>
+      <c r="AA32" s="148"/>
+      <c r="AB32" s="148"/>
+      <c r="AC32" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD32" s="148"/>
+    </row>
+    <row r="33" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A33" s="142" t="s">
         <v>99</v>
       </c>
-      <c r="B33" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="170" t="s">
+      <c r="B33" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D33" s="142" t="s">
         <v>100</v>
       </c>
-      <c r="E33" s="170" t="s">
+      <c r="E33" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="F33" s="172">
+      <c r="F33" s="144">
         <v>2.9513888888888888E-3</v>
       </c>
-      <c r="G33" s="170" t="s">
+      <c r="G33" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="H33" s="170"/>
-      <c r="I33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J33" s="170" t="s">
+      <c r="H33" s="142"/>
+      <c r="I33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="K33" s="170"/>
-      <c r="L33" s="189">
+      <c r="K33" s="142"/>
+      <c r="L33" s="161">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="M33" s="173"/>
-      <c r="N33" s="173"/>
-      <c r="O33" s="170"/>
-      <c r="P33" s="170"/>
-      <c r="Q33" s="170"/>
-      <c r="R33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="T33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="U33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="X33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC33" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD33" s="170" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A34" s="176" t="s">
+      <c r="M33" s="145"/>
+      <c r="N33" s="145"/>
+      <c r="O33" s="142"/>
+      <c r="P33" s="142"/>
+      <c r="Q33" s="142"/>
+      <c r="R33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="T33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="U33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="X33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC33" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD33" s="142" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A34" s="148" t="s">
         <v>101</v>
       </c>
-      <c r="B34" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="176" t="s">
+      <c r="B34" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="148" t="s">
         <v>102</v>
       </c>
-      <c r="E34" s="176" t="s">
+      <c r="E34" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="178">
+      <c r="F34" s="150">
         <v>4.1319444444444442E-3</v>
       </c>
-      <c r="G34" s="176" t="s">
+      <c r="G34" s="148" t="s">
         <v>31</v>
       </c>
-      <c r="H34" s="176"/>
-      <c r="I34" s="176"/>
-      <c r="J34" s="176" t="s">
+      <c r="H34" s="148"/>
+      <c r="I34" s="148"/>
+      <c r="J34" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="176"/>
-      <c r="L34" s="189">
+      <c r="K34" s="148"/>
+      <c r="L34" s="161">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="M34" s="179"/>
-      <c r="N34" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="O34" s="180" t="s">
-        <v>32</v>
-      </c>
-      <c r="P34" s="176"/>
-      <c r="Q34" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R34" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S34" s="176"/>
-      <c r="T34" s="176"/>
-      <c r="U34" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="V34" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W34" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="X34" s="176"/>
-      <c r="Y34" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z34" s="176"/>
-      <c r="AA34" s="176"/>
-      <c r="AB34" s="176"/>
-      <c r="AC34" s="176"/>
-      <c r="AD34" s="176"/>
-    </row>
-    <row r="35" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A35" s="170" t="s">
+      <c r="M34" s="151"/>
+      <c r="N34" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="O34" s="152" t="s">
+        <v>32</v>
+      </c>
+      <c r="P34" s="148"/>
+      <c r="Q34" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R34" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S34" s="148"/>
+      <c r="T34" s="148"/>
+      <c r="U34" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="V34" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W34" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="X34" s="148"/>
+      <c r="Y34" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z34" s="148"/>
+      <c r="AA34" s="148"/>
+      <c r="AB34" s="148"/>
+      <c r="AC34" s="148"/>
+      <c r="AD34" s="148"/>
+    </row>
+    <row r="35" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A35" s="142" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="170" t="s">
+      <c r="B35" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="170" t="s">
+      <c r="E35" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="172">
+      <c r="F35" s="144">
         <v>5.9606481481481481E-3</v>
       </c>
-      <c r="G35" s="170" t="s">
+      <c r="G35" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="H35" s="170"/>
-      <c r="I35" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J35" s="170" t="s">
+      <c r="H35" s="142"/>
+      <c r="I35" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" s="142" t="s">
         <v>56</v>
       </c>
-      <c r="K35" s="170"/>
-      <c r="L35" s="189">
+      <c r="K35" s="142"/>
+      <c r="L35" s="161">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="M35" s="173"/>
-      <c r="N35" s="173" t="s">
-        <v>32</v>
-      </c>
-      <c r="O35" s="174" t="s">
-        <v>32</v>
-      </c>
-      <c r="P35" s="170"/>
-      <c r="Q35" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="R35" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S35" s="170"/>
-      <c r="T35" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="U35" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V35" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W35" s="170"/>
-      <c r="X35" s="170"/>
-      <c r="Y35" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z35" s="170"/>
-      <c r="AA35" s="170"/>
-      <c r="AB35" s="170"/>
-      <c r="AC35" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD35" s="170"/>
-    </row>
-    <row r="36" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A36" s="176" t="s">
+      <c r="M35" s="145"/>
+      <c r="N35" s="145" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" s="146" t="s">
+        <v>32</v>
+      </c>
+      <c r="P35" s="142"/>
+      <c r="Q35" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="R35" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S35" s="142"/>
+      <c r="T35" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="U35" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V35" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W35" s="142"/>
+      <c r="X35" s="142"/>
+      <c r="Y35" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z35" s="142"/>
+      <c r="AA35" s="142"/>
+      <c r="AB35" s="142"/>
+      <c r="AC35" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD35" s="142"/>
+    </row>
+    <row r="36" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A36" s="148" t="s">
         <v>104</v>
       </c>
-      <c r="B36" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="176" t="s">
+      <c r="B36" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="148" t="s">
         <v>105</v>
       </c>
-      <c r="E36" s="176" t="s">
+      <c r="E36" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F36" s="178">
+      <c r="F36" s="150">
         <v>2.4305555555555556E-3</v>
       </c>
-      <c r="G36" s="176" t="s">
+      <c r="G36" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="H36" s="176"/>
-      <c r="I36" s="176"/>
-      <c r="J36" s="176" t="s">
+      <c r="H36" s="148"/>
+      <c r="I36" s="148"/>
+      <c r="J36" s="148" t="s">
         <v>40</v>
       </c>
-      <c r="K36" s="176"/>
-      <c r="L36" s="189">
+      <c r="K36" s="148"/>
+      <c r="L36" s="161">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="M36" s="179"/>
-      <c r="N36" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="O36" s="180"/>
-      <c r="P36" s="176"/>
-      <c r="Q36" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R36" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S36" s="176"/>
-      <c r="T36" s="176"/>
-      <c r="U36" s="176"/>
-      <c r="V36" s="176"/>
-      <c r="W36" s="176"/>
-      <c r="X36" s="176"/>
-      <c r="Y36" s="176"/>
-      <c r="Z36" s="176"/>
-      <c r="AA36" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB36" s="176"/>
-      <c r="AC36" s="176"/>
-      <c r="AD36" s="176"/>
-    </row>
-    <row r="37" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A37" s="170" t="s">
+      <c r="M36" s="151"/>
+      <c r="N36" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="O36" s="152"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R36" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S36" s="148"/>
+      <c r="T36" s="148"/>
+      <c r="U36" s="148"/>
+      <c r="V36" s="148"/>
+      <c r="W36" s="148"/>
+      <c r="X36" s="148"/>
+      <c r="Y36" s="148"/>
+      <c r="Z36" s="148"/>
+      <c r="AA36" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB36" s="148"/>
+      <c r="AC36" s="148"/>
+      <c r="AD36" s="148"/>
+    </row>
+    <row r="37" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A37" s="142" t="s">
         <v>106</v>
       </c>
-      <c r="B37" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="170" t="s">
+      <c r="B37" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="142" t="s">
         <v>107</v>
       </c>
-      <c r="E37" s="170" t="s">
+      <c r="E37" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="F37" s="172">
+      <c r="F37" s="144">
         <v>3.3680555555555556E-3</v>
       </c>
-      <c r="G37" s="170" t="s">
+      <c r="G37" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="H37" s="170"/>
-      <c r="I37" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J37" s="170" t="s">
+      <c r="H37" s="142"/>
+      <c r="I37" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J37" s="142" t="s">
         <v>56</v>
       </c>
-      <c r="K37" s="170"/>
-      <c r="L37" s="189">
+      <c r="K37" s="142"/>
+      <c r="L37" s="161">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="M37" s="173"/>
-      <c r="N37" s="173"/>
-      <c r="O37" s="170"/>
-      <c r="P37" s="170"/>
-      <c r="Q37" s="170"/>
-      <c r="R37" s="170"/>
-      <c r="S37" s="170"/>
-      <c r="T37" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="U37" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V37" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W37" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="X37" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y37" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z37" s="170"/>
-      <c r="AA37" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB37" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC37" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD37" s="170" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A38" s="176" t="s">
+      <c r="M37" s="145"/>
+      <c r="N37" s="145"/>
+      <c r="O37" s="142"/>
+      <c r="P37" s="142"/>
+      <c r="Q37" s="142"/>
+      <c r="R37" s="142"/>
+      <c r="S37" s="142"/>
+      <c r="T37" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="U37" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V37" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W37" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="X37" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y37" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z37" s="142"/>
+      <c r="AA37" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB37" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC37" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD37" s="142" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A38" s="148" t="s">
         <v>108</v>
       </c>
-      <c r="B38" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="176" t="s">
+      <c r="B38" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="E38" s="176" t="s">
+      <c r="E38" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F38" s="178">
+      <c r="F38" s="150">
         <v>2.6041666666666665E-3</v>
       </c>
-      <c r="G38" s="176" t="s">
+      <c r="G38" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="H38" s="176"/>
-      <c r="I38" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J38" s="176" t="s">
+      <c r="H38" s="148"/>
+      <c r="I38" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J38" s="148" t="s">
         <v>40</v>
       </c>
-      <c r="K38" s="176"/>
-      <c r="L38" s="189">
+      <c r="K38" s="148"/>
+      <c r="L38" s="161">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M38" s="179"/>
-      <c r="N38" s="179"/>
-      <c r="O38" s="176"/>
-      <c r="P38" s="176"/>
-      <c r="Q38" s="176"/>
-      <c r="R38" s="176"/>
-      <c r="S38" s="176"/>
-      <c r="T38" s="176"/>
-      <c r="U38" s="176"/>
-      <c r="V38" s="176"/>
-      <c r="W38" s="176"/>
-      <c r="X38" s="176"/>
-      <c r="Y38" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z38" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA38" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB38" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC38" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD38" s="176" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A39" s="170" t="s">
+      <c r="M38" s="151"/>
+      <c r="N38" s="151"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="148"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148"/>
+      <c r="T38" s="148"/>
+      <c r="U38" s="148"/>
+      <c r="V38" s="148"/>
+      <c r="W38" s="148"/>
+      <c r="X38" s="148"/>
+      <c r="Y38" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z38" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA38" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB38" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC38" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD38" s="148" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A39" s="142" t="s">
         <v>110</v>
       </c>
-      <c r="B39" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="170" t="s">
+      <c r="B39" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="142" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="170" t="s">
+      <c r="E39" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F39" s="172">
+      <c r="F39" s="144">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="G39" s="170" t="s">
+      <c r="G39" s="142" t="s">
         <v>112</v>
       </c>
-      <c r="H39" s="170"/>
-      <c r="I39" s="170"/>
-      <c r="J39" s="170" t="s">
+      <c r="H39" s="142"/>
+      <c r="I39" s="142"/>
+      <c r="J39" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="K39" s="170"/>
-      <c r="L39" s="189">
+      <c r="K39" s="142"/>
+      <c r="L39" s="161">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="M39" s="173"/>
-      <c r="N39" s="173"/>
-      <c r="O39" s="174"/>
-      <c r="P39" s="170"/>
-      <c r="Q39" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="R39" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S39" s="170"/>
-      <c r="T39" s="170"/>
-      <c r="U39" s="170"/>
-      <c r="V39" s="170"/>
-      <c r="W39" s="170"/>
-      <c r="X39" s="170"/>
-      <c r="Y39" s="170"/>
-      <c r="Z39" s="170"/>
-      <c r="AA39" s="170"/>
-      <c r="AB39" s="170"/>
-      <c r="AC39" s="170"/>
-      <c r="AD39" s="170"/>
-    </row>
-    <row r="40" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A40" s="176" t="s">
+      <c r="M39" s="145"/>
+      <c r="N39" s="145"/>
+      <c r="O39" s="146"/>
+      <c r="P39" s="142"/>
+      <c r="Q39" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="R39" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S39" s="142"/>
+      <c r="T39" s="142"/>
+      <c r="U39" s="142"/>
+      <c r="V39" s="142"/>
+      <c r="W39" s="142"/>
+      <c r="X39" s="142"/>
+      <c r="Y39" s="142"/>
+      <c r="Z39" s="142"/>
+      <c r="AA39" s="142"/>
+      <c r="AB39" s="142"/>
+      <c r="AC39" s="142"/>
+      <c r="AD39" s="142"/>
+    </row>
+    <row r="40" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A40" s="148" t="s">
         <v>113</v>
       </c>
-      <c r="B40" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C40" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="176" t="s">
+      <c r="B40" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C40" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="148" t="s">
         <v>98</v>
       </c>
-      <c r="E40" s="176" t="s">
+      <c r="E40" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F40" s="178">
+      <c r="F40" s="150">
         <v>2.0023148148148148E-3</v>
       </c>
-      <c r="G40" s="176" t="s">
+      <c r="G40" s="148" t="s">
         <v>31</v>
       </c>
-      <c r="H40" s="176"/>
-      <c r="I40" s="176"/>
-      <c r="J40" s="176" t="s">
+      <c r="H40" s="148"/>
+      <c r="I40" s="148"/>
+      <c r="J40" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="K40" s="176"/>
-      <c r="L40" s="189">
+      <c r="K40" s="148"/>
+      <c r="L40" s="161">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M40" s="179"/>
-      <c r="N40" s="179"/>
-      <c r="O40" s="180"/>
-      <c r="P40" s="176"/>
-      <c r="Q40" s="176"/>
-      <c r="R40" s="176"/>
-      <c r="S40" s="176"/>
-      <c r="T40" s="176"/>
-      <c r="U40" s="176"/>
-      <c r="V40" s="176"/>
-      <c r="W40" s="176"/>
-      <c r="X40" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y40" s="176"/>
-      <c r="Z40" s="176"/>
-      <c r="AA40" s="176"/>
-      <c r="AB40" s="176"/>
-      <c r="AC40" s="176"/>
-      <c r="AD40" s="176"/>
-    </row>
-    <row r="41" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A41" s="170" t="s">
+      <c r="M40" s="151"/>
+      <c r="N40" s="151"/>
+      <c r="O40" s="152"/>
+      <c r="P40" s="148"/>
+      <c r="Q40" s="148"/>
+      <c r="R40" s="148"/>
+      <c r="S40" s="148"/>
+      <c r="T40" s="148"/>
+      <c r="U40" s="148"/>
+      <c r="V40" s="148"/>
+      <c r="W40" s="148"/>
+      <c r="X40" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y40" s="148"/>
+      <c r="Z40" s="148"/>
+      <c r="AA40" s="148"/>
+      <c r="AB40" s="148"/>
+      <c r="AC40" s="148"/>
+      <c r="AD40" s="148"/>
+    </row>
+    <row r="41" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A41" s="142" t="s">
         <v>114</v>
       </c>
-      <c r="B41" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D41" s="170" t="s">
+      <c r="B41" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D41" s="142" t="s">
         <v>115</v>
       </c>
-      <c r="E41" s="170" t="s">
+      <c r="E41" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F41" s="172">
+      <c r="F41" s="144">
         <v>3.460648148148148E-3</v>
       </c>
-      <c r="G41" s="170" t="s">
+      <c r="G41" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="H41" s="170"/>
-      <c r="I41" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="J41" s="170" t="s">
+      <c r="H41" s="142"/>
+      <c r="I41" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="J41" s="142" t="s">
         <v>69</v>
       </c>
-      <c r="K41" s="170"/>
-      <c r="L41" s="189">
+      <c r="K41" s="142"/>
+      <c r="L41" s="161">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="M41" s="173"/>
-      <c r="N41" s="173"/>
-      <c r="O41" s="174"/>
-      <c r="P41" s="170"/>
-      <c r="Q41" s="170"/>
-      <c r="R41" s="170"/>
-      <c r="S41" s="170"/>
-      <c r="T41" s="170"/>
-      <c r="U41" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="V41" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="W41" s="170"/>
-      <c r="X41" s="170"/>
-      <c r="Y41" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z41" s="170"/>
-      <c r="AA41" s="170"/>
-      <c r="AB41" s="170"/>
-      <c r="AC41" s="170"/>
-      <c r="AD41" s="170"/>
-    </row>
-    <row r="42" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A42" s="176" t="s">
+      <c r="M41" s="145"/>
+      <c r="N41" s="145"/>
+      <c r="O41" s="146"/>
+      <c r="P41" s="142"/>
+      <c r="Q41" s="142"/>
+      <c r="R41" s="142"/>
+      <c r="S41" s="142"/>
+      <c r="T41" s="142"/>
+      <c r="U41" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="V41" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="W41" s="142"/>
+      <c r="X41" s="142"/>
+      <c r="Y41" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z41" s="142"/>
+      <c r="AA41" s="142"/>
+      <c r="AB41" s="142"/>
+      <c r="AC41" s="142"/>
+      <c r="AD41" s="142"/>
+    </row>
+    <row r="42" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A42" s="148" t="s">
         <v>116</v>
       </c>
-      <c r="B42" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D42" s="176" t="s">
+      <c r="B42" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="148" t="s">
         <v>117</v>
       </c>
-      <c r="E42" s="176" t="s">
+      <c r="E42" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F42" s="178">
+      <c r="F42" s="150">
         <v>2.2569444444444442E-3</v>
       </c>
-      <c r="G42" s="176" t="s">
+      <c r="G42" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="H42" s="176"/>
-      <c r="I42" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J42" s="176" t="s">
+      <c r="H42" s="148"/>
+      <c r="I42" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="K42" s="176"/>
-      <c r="L42" s="189">
+      <c r="K42" s="148"/>
+      <c r="L42" s="161">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="M42" s="179"/>
-      <c r="N42" s="179"/>
-      <c r="O42" s="180"/>
-      <c r="P42" s="176"/>
-      <c r="Q42" s="176"/>
-      <c r="R42" s="176"/>
-      <c r="S42" s="176"/>
-      <c r="T42" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="U42" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="V42" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W42" s="176"/>
-      <c r="X42" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y42" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z42" s="176"/>
-      <c r="AA42" s="176"/>
-      <c r="AB42" s="176"/>
-      <c r="AC42" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD42" s="176"/>
-    </row>
-    <row r="43" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A43" s="170" t="s">
+      <c r="M42" s="151"/>
+      <c r="N42" s="151"/>
+      <c r="O42" s="152"/>
+      <c r="P42" s="148"/>
+      <c r="Q42" s="148"/>
+      <c r="R42" s="148"/>
+      <c r="S42" s="148"/>
+      <c r="T42" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="U42" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="V42" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W42" s="148"/>
+      <c r="X42" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y42" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z42" s="148"/>
+      <c r="AA42" s="148"/>
+      <c r="AB42" s="148"/>
+      <c r="AC42" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD42" s="148"/>
+    </row>
+    <row r="43" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A43" s="142" t="s">
         <v>118</v>
       </c>
-      <c r="B43" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="170" t="s">
+      <c r="B43" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="142" t="s">
         <v>119</v>
       </c>
-      <c r="E43" s="170" t="s">
+      <c r="E43" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F43" s="172">
+      <c r="F43" s="144">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="G43" s="170" t="s">
+      <c r="G43" s="142" t="s">
         <v>36</v>
       </c>
-      <c r="H43" s="170"/>
-      <c r="I43" s="170"/>
-      <c r="J43" s="170" t="s">
+      <c r="H43" s="142"/>
+      <c r="I43" s="142"/>
+      <c r="J43" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="K43" s="170"/>
-      <c r="L43" s="189">
+      <c r="K43" s="142"/>
+      <c r="L43" s="161">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="M43" s="173"/>
-      <c r="N43" s="173"/>
-      <c r="O43" s="174"/>
-      <c r="P43" s="170"/>
-      <c r="Q43" s="170"/>
-      <c r="R43" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="S43" s="170"/>
-      <c r="T43" s="170"/>
-      <c r="U43" s="170"/>
-      <c r="V43" s="170"/>
-      <c r="W43" s="170"/>
-      <c r="X43" s="170"/>
-      <c r="Y43" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z43" s="170"/>
-      <c r="AA43" s="170"/>
-      <c r="AB43" s="170"/>
-      <c r="AC43" s="170"/>
-      <c r="AD43" s="170"/>
-    </row>
-    <row r="44" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A44" s="176" t="s">
+      <c r="M43" s="145"/>
+      <c r="N43" s="145"/>
+      <c r="O43" s="146"/>
+      <c r="P43" s="142"/>
+      <c r="Q43" s="142"/>
+      <c r="R43" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S43" s="142"/>
+      <c r="T43" s="142"/>
+      <c r="U43" s="142"/>
+      <c r="V43" s="142"/>
+      <c r="W43" s="142"/>
+      <c r="X43" s="142"/>
+      <c r="Y43" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z43" s="142"/>
+      <c r="AA43" s="142"/>
+      <c r="AB43" s="142"/>
+      <c r="AC43" s="142"/>
+      <c r="AD43" s="142"/>
+    </row>
+    <row r="44" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A44" s="148" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D44" s="176" t="s">
+      <c r="B44" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="148" t="s">
         <v>53</v>
       </c>
-      <c r="E44" s="176" t="s">
+      <c r="E44" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F44" s="178">
+      <c r="F44" s="150">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="G44" s="176" t="s">
+      <c r="G44" s="148" t="s">
         <v>31</v>
       </c>
-      <c r="H44" s="176"/>
-      <c r="I44" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J44" s="176" t="s">
+      <c r="H44" s="148"/>
+      <c r="I44" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J44" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="K44" s="176"/>
-      <c r="L44" s="189">
+      <c r="K44" s="148"/>
+      <c r="L44" s="161">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="M44" s="179"/>
-      <c r="N44" s="179"/>
-      <c r="O44" s="180"/>
-      <c r="P44" s="176"/>
-      <c r="Q44" s="176"/>
-      <c r="R44" s="176"/>
-      <c r="S44" s="176"/>
-      <c r="T44" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="U44" s="176"/>
-      <c r="V44" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W44" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="X44" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y44" s="176"/>
-      <c r="Z44" s="176"/>
-      <c r="AA44" s="176"/>
-      <c r="AB44" s="176"/>
-      <c r="AC44" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD44" s="176"/>
-    </row>
-    <row r="45" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A45" s="170" t="s">
+      <c r="M44" s="151"/>
+      <c r="N44" s="151"/>
+      <c r="O44" s="152"/>
+      <c r="P44" s="148"/>
+      <c r="Q44" s="148"/>
+      <c r="R44" s="148"/>
+      <c r="S44" s="148"/>
+      <c r="T44" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="U44" s="148"/>
+      <c r="V44" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W44" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="X44" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y44" s="148"/>
+      <c r="Z44" s="148"/>
+      <c r="AA44" s="148"/>
+      <c r="AB44" s="148"/>
+      <c r="AC44" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD44" s="148"/>
+    </row>
+    <row r="45" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A45" s="142" t="s">
         <v>121</v>
       </c>
-      <c r="B45" s="182" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="182" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="170" t="s">
+      <c r="B45" s="154" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="142" t="s">
         <v>122</v>
       </c>
-      <c r="E45" s="170" t="s">
+      <c r="E45" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F45" s="172">
+      <c r="F45" s="144">
         <v>3.1250000000000002E-3</v>
       </c>
-      <c r="G45" s="170" t="s">
+      <c r="G45" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="H45" s="170"/>
-      <c r="I45" s="170"/>
-      <c r="J45" s="170" t="s">
+      <c r="H45" s="142"/>
+      <c r="I45" s="142"/>
+      <c r="J45" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="K45" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="L45" s="189">
+      <c r="K45" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="L45" s="161">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M45" s="173"/>
-      <c r="N45" s="173"/>
-      <c r="O45" s="174"/>
-      <c r="P45" s="170"/>
-      <c r="Q45" s="170"/>
-      <c r="R45" s="170"/>
-      <c r="S45" s="170"/>
-      <c r="T45" s="170"/>
-      <c r="U45" s="170"/>
-      <c r="V45" s="170"/>
-      <c r="W45" s="170"/>
-      <c r="X45" s="170"/>
-      <c r="Y45" s="170"/>
-      <c r="Z45" s="170"/>
-      <c r="AA45" s="170"/>
-      <c r="AB45" s="170"/>
-      <c r="AC45" s="170"/>
-      <c r="AD45" s="170"/>
-    </row>
-    <row r="46" spans="1:30" s="175" customFormat="1" ht="22" customHeight="1">
-      <c r="A46" s="176" t="s">
+      <c r="M45" s="145"/>
+      <c r="N45" s="145"/>
+      <c r="O45" s="146"/>
+      <c r="P45" s="142"/>
+      <c r="Q45" s="142"/>
+      <c r="R45" s="142"/>
+      <c r="S45" s="142"/>
+      <c r="T45" s="142"/>
+      <c r="U45" s="142"/>
+      <c r="V45" s="142"/>
+      <c r="W45" s="142"/>
+      <c r="X45" s="142"/>
+      <c r="Y45" s="142"/>
+      <c r="Z45" s="142"/>
+      <c r="AA45" s="142"/>
+      <c r="AB45" s="142"/>
+      <c r="AC45" s="142"/>
+      <c r="AD45" s="142"/>
+    </row>
+    <row r="46" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+      <c r="A46" s="148" t="s">
         <v>123</v>
       </c>
-      <c r="B46" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D46" s="176" t="s">
+      <c r="B46" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="148" t="s">
         <v>93</v>
       </c>
-      <c r="E46" s="176" t="s">
+      <c r="E46" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F46" s="178">
+      <c r="F46" s="150">
         <v>3.3217592592592591E-3</v>
       </c>
-      <c r="G46" s="176" t="s">
+      <c r="G46" s="148" t="s">
         <v>36</v>
       </c>
-      <c r="H46" s="176"/>
-      <c r="I46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J46" s="176" t="s">
+      <c r="H46" s="148"/>
+      <c r="I46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J46" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="K46" s="176"/>
-      <c r="L46" s="189">
+      <c r="K46" s="148"/>
+      <c r="L46" s="161">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="M46" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="N46" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="O46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="P46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="T46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="U46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="V46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="X46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC46" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD46" s="176" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:30" s="175" customFormat="1" ht="20" customHeight="1">
-      <c r="A47" s="170" t="s">
+      <c r="M46" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="N46" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="O46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="P46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="T46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="U46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="V46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="X46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC46" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD46" s="148" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" s="147" customFormat="1" ht="20" customHeight="1">
+      <c r="A47" s="142" t="s">
         <v>124</v>
       </c>
-      <c r="B47" s="185"/>
-      <c r="C47" s="185"/>
-      <c r="D47" s="170" t="s">
+      <c r="B47" s="157"/>
+      <c r="C47" s="157"/>
+      <c r="D47" s="142" t="s">
         <v>125</v>
       </c>
-      <c r="E47" s="170" t="s">
+      <c r="E47" s="142" t="s">
         <v>30</v>
       </c>
-      <c r="F47" s="172"/>
-      <c r="G47" s="170" t="s">
+      <c r="F47" s="144"/>
+      <c r="G47" s="142" t="s">
         <v>126</v>
       </c>
-      <c r="H47" s="170"/>
-      <c r="I47" s="170"/>
-      <c r="J47" s="170" t="s">
+      <c r="H47" s="142"/>
+      <c r="I47" s="142"/>
+      <c r="J47" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="K47" s="170"/>
-      <c r="L47" s="189">
+      <c r="K47" s="142"/>
+      <c r="L47" s="161">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M47" s="173"/>
-      <c r="N47" s="173"/>
-      <c r="O47" s="174"/>
-      <c r="P47" s="170"/>
-      <c r="Q47" s="170"/>
-      <c r="R47" s="170"/>
-      <c r="S47" s="170"/>
-      <c r="T47" s="170"/>
-      <c r="U47" s="170"/>
-      <c r="V47" s="170"/>
-      <c r="W47" s="170" t="s">
-        <v>32</v>
-      </c>
-      <c r="X47" s="170"/>
-      <c r="Y47" s="170"/>
-      <c r="Z47" s="170"/>
-      <c r="AA47" s="170"/>
-      <c r="AB47" s="170"/>
-      <c r="AC47" s="170"/>
-      <c r="AD47" s="170"/>
-    </row>
-    <row r="48" spans="1:30" s="175" customFormat="1" ht="17" customHeight="1">
-      <c r="A48" s="176" t="s">
+      <c r="M47" s="145"/>
+      <c r="N47" s="145"/>
+      <c r="O47" s="146"/>
+      <c r="P47" s="142"/>
+      <c r="Q47" s="142"/>
+      <c r="R47" s="142"/>
+      <c r="S47" s="142"/>
+      <c r="T47" s="142"/>
+      <c r="U47" s="142"/>
+      <c r="V47" s="142"/>
+      <c r="W47" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="X47" s="142"/>
+      <c r="Y47" s="142"/>
+      <c r="Z47" s="142"/>
+      <c r="AA47" s="142"/>
+      <c r="AB47" s="142"/>
+      <c r="AC47" s="142"/>
+      <c r="AD47" s="142"/>
+    </row>
+    <row r="48" spans="1:30" s="147" customFormat="1" ht="17" customHeight="1">
+      <c r="A48" s="148" t="s">
         <v>127</v>
       </c>
-      <c r="B48" s="177" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="177" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="176" t="s">
+      <c r="B48" s="149" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="148" t="s">
         <v>128</v>
       </c>
-      <c r="E48" s="176" t="s">
+      <c r="E48" s="148" t="s">
         <v>30</v>
       </c>
-      <c r="F48" s="178">
+      <c r="F48" s="150">
         <v>2.0949074074074073E-3</v>
       </c>
-      <c r="G48" s="176" t="s">
+      <c r="G48" s="148" t="s">
         <v>31</v>
       </c>
-      <c r="H48" s="176"/>
-      <c r="I48" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="J48" s="176" t="s">
+      <c r="H48" s="148"/>
+      <c r="I48" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" s="148" t="s">
         <v>56</v>
       </c>
-      <c r="K48" s="176"/>
-      <c r="L48" s="189">
+      <c r="K48" s="148"/>
+      <c r="L48" s="161">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="M48" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="N48" s="179" t="s">
-        <v>32</v>
-      </c>
-      <c r="O48" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="P48" s="176"/>
-      <c r="Q48" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="R48" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="S48" s="176"/>
-      <c r="T48" s="176"/>
-      <c r="U48" s="176"/>
-      <c r="V48" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="W48" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="X48" s="176"/>
-      <c r="Y48" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z48" s="176"/>
-      <c r="AA48" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB48" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC48" s="176" t="s">
-        <v>32</v>
-      </c>
-      <c r="AD48" s="176" t="s">
+      <c r="M48" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="O48" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="P48" s="148"/>
+      <c r="Q48" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="R48" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="S48" s="148"/>
+      <c r="T48" s="148"/>
+      <c r="U48" s="148"/>
+      <c r="V48" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="W48" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="X48" s="148"/>
+      <c r="Y48" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z48" s="148"/>
+      <c r="AA48" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB48" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC48" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD48" s="148" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6331,24 +6331,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>260</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -6777,24 +6777,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>261</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -7082,24 +7082,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>262</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -7845,24 +7845,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>263</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -8218,24 +8218,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>264</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -8597,24 +8597,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>265</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -9292,24 +9292,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>266</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -9814,24 +9814,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>267</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -10206,24 +10206,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>268</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -10529,24 +10529,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>269</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -11848,24 +11848,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>270</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -12394,24 +12394,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -12722,24 +12722,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>272</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -13157,24 +13157,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>273</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -13486,24 +13486,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>274</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -14392,24 +14392,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="174" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
-      <c r="F1" s="144"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="176"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="177" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="179"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A3" s="115" t="s">
@@ -14712,14 +14712,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="17">
-      <c r="A18" s="148" t="s">
+      <c r="A18" s="180" t="s">
         <v>246</v>
       </c>
-      <c r="B18" s="149"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="149"/>
-      <c r="E18" s="149"/>
-      <c r="F18" s="150"/>
+      <c r="B18" s="181"/>
+      <c r="C18" s="181"/>
+      <c r="D18" s="181"/>
+      <c r="E18" s="181"/>
+      <c r="F18" s="182"/>
     </row>
     <row r="19" spans="1:6" ht="17">
       <c r="A19" s="126">
@@ -15060,24 +15060,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="155" t="s">
+      <c r="A1" s="187" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="156"/>
-      <c r="C1" s="156"/>
-      <c r="D1" s="156"/>
-      <c r="E1" s="156"/>
-      <c r="F1" s="157"/>
+      <c r="B1" s="188"/>
+      <c r="C1" s="188"/>
+      <c r="D1" s="188"/>
+      <c r="E1" s="188"/>
+      <c r="F1" s="189"/>
     </row>
     <row r="2" spans="1:6" ht="18" thickBot="1">
-      <c r="A2" s="151" t="s">
+      <c r="A2" s="183" t="s">
         <v>275</v>
       </c>
-      <c r="B2" s="152"/>
-      <c r="C2" s="152"/>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="153"/>
+      <c r="B2" s="184"/>
+      <c r="C2" s="184"/>
+      <c r="D2" s="184"/>
+      <c r="E2" s="184"/>
+      <c r="F2" s="185"/>
     </row>
     <row r="3" spans="1:6" ht="18" thickBot="1">
       <c r="A3" s="105" t="s">
@@ -15416,12 +15416,12 @@
     </row>
     <row r="19" spans="1:6" ht="18" thickBot="1">
       <c r="A19" s="94"/>
-      <c r="B19" s="154" t="s">
+      <c r="B19" s="186" t="s">
         <v>243</v>
       </c>
-      <c r="C19" s="154"/>
-      <c r="D19" s="154"/>
-      <c r="E19" s="154"/>
+      <c r="C19" s="186"/>
+      <c r="D19" s="186"/>
+      <c r="E19" s="186"/>
       <c r="F19" s="108">
         <f>SUM(F4:F18)</f>
         <v>4.0509259259259259E-2</v>
@@ -15581,14 +15581,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="158" t="s">
+      <c r="A1" s="190" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="159"/>
-      <c r="C1" s="159"/>
-      <c r="D1" s="159"/>
-      <c r="E1" s="159"/>
-      <c r="F1" s="160"/>
+      <c r="B1" s="191"/>
+      <c r="C1" s="191"/>
+      <c r="D1" s="191"/>
+      <c r="E1" s="191"/>
+      <c r="F1" s="192"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A2" s="54" t="s">
@@ -15891,14 +15891,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1">
-      <c r="A17" s="161" t="s">
+      <c r="A17" s="193" t="s">
         <v>246</v>
       </c>
-      <c r="B17" s="162"/>
-      <c r="C17" s="162"/>
-      <c r="D17" s="162"/>
-      <c r="E17" s="162"/>
-      <c r="F17" s="163"/>
+      <c r="B17" s="194"/>
+      <c r="C17" s="194"/>
+      <c r="D17" s="194"/>
+      <c r="E17" s="194"/>
+      <c r="F17" s="195"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="62">
@@ -16238,24 +16238,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="167" t="s">
+      <c r="A1" s="199" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="168"/>
-      <c r="C1" s="168"/>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="169"/>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
+      <c r="F1" s="201"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="196" t="s">
         <v>259</v>
       </c>
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
-      <c r="E2" s="165"/>
-      <c r="F2" s="166"/>
+      <c r="B2" s="197"/>
+      <c r="C2" s="197"/>
+      <c r="D2" s="197"/>
+      <c r="E2" s="197"/>
+      <c r="F2" s="198"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="119" t="s">

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1C04ED-D604-4C46-8936-B81008FB0AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F91A74-B5CF-C446-880E-6E1E596CED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3820" yWindow="3660" windowWidth="29580" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3020" windowWidth="29580" windowHeight="17160" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -42,6 +42,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="8">'2026-05-14 Fat Shallot'!$A$2:$F$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'2026-05-16 Fat Shallot'!$A$1:$F$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'2026-06-21 Chicago Union'!$A$1:$F$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'2026-06-24 Ridgeville Parks'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92F91A74-B5CF-C446-880E-6E1E596CED1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6296D778-BD0D-C24F-B0BB-8BC3785AAFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3020" windowWidth="29580" windowHeight="17160" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3880" yWindow="3020" windowWidth="29580" windowHeight="17160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Potential Gigs" sheetId="4" r:id="rId4"/>
     <sheet name="Finances" sheetId="5" r:id="rId5"/>
     <sheet name="2026-06-24 Ridgeville Parks" sheetId="6" r:id="rId6"/>
-    <sheet name="2026-06-21 Chicago Union" sheetId="7" r:id="rId7"/>
+    <sheet name="2026-06-21 Chicago Union Rain C" sheetId="7" r:id="rId7"/>
     <sheet name="2026-05-16 Fat Shallot" sheetId="8" r:id="rId8"/>
     <sheet name="2026-05-14 Fat Shallot" sheetId="9" r:id="rId9"/>
     <sheet name="2026-05-02 Lincolnwood" sheetId="10" r:id="rId10"/>
@@ -41,7 +41,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'2026-05-14 Fat Shallot'!$A$2:$F$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'2026-05-16 Fat Shallot'!$A$1:$F$29</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'2026-06-21 Chicago Union'!$A$1:$F$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'2026-06-21 Chicago Union Rain C'!$A$1:$F$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'2026-06-24 Ridgeville Parks'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2370" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="275">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -855,10 +855,6 @@
     <t>gig fee</t>
   </si>
   <si>
-    <t>2026-06-21
-Chicago Union</t>
-  </si>
-  <si>
     <t>2026-06-24 | Ridgeville Parks District | 6:00 PM</t>
   </si>
   <si>
@@ -910,7 +906,7 @@
     <t>2023-09-09 | Ewing Block Party</t>
   </si>
   <si>
-    <t>2026-06-21 | Chicago Union | 5:00 PM</t>
+    <t>2026-06-21 | Chicago Union (cancelled) | 5:00 PM</t>
   </si>
 </sst>
 </file>
@@ -2984,7 +2980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD49"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.83203125" bestFit="1" customWidth="1"/>
@@ -3010,10 +3006,9 @@
     <col min="25" max="25" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="27" max="29" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="167" customFormat="1" ht="28" customHeight="1" thickBot="1">
+    <row r="1" spans="1:29" s="167" customFormat="1" ht="28" customHeight="1" thickBot="1">
       <c r="A1" s="164" t="s">
         <v>0</v>
       </c>
@@ -3045,9 +3040,8 @@
       <c r="AA1" s="165"/>
       <c r="AB1" s="165"/>
       <c r="AC1" s="165"/>
-      <c r="AD1" s="165"/>
-    </row>
-    <row r="2" spans="1:30" s="173" customFormat="1" ht="56" customHeight="1" thickBot="1">
+    </row>
+    <row r="2" spans="1:29" s="173" customFormat="1" ht="56" customHeight="1" thickBot="1">
       <c r="A2" s="168" t="s">
         <v>1</v>
       </c>
@@ -3135,11 +3129,8 @@
       <c r="AC2" s="172" t="s">
         <v>250</v>
       </c>
-      <c r="AD2" s="172" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" s="163" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="3" spans="1:29" s="163" customFormat="1" ht="22" customHeight="1">
       <c r="A3" s="158" t="s">
         <v>28</v>
       </c>
@@ -3170,7 +3161,7 @@
       </c>
       <c r="K3" s="158"/>
       <c r="L3" s="161">
-        <f>COUNTIF(M3:AW3,"✓")</f>
+        <f>COUNTIF(M3:AV3,"✓")</f>
         <v>2</v>
       </c>
       <c r="M3" s="161"/>
@@ -3194,9 +3185,8 @@
       <c r="AA3" s="158"/>
       <c r="AB3" s="158"/>
       <c r="AC3" s="158"/>
-      <c r="AD3" s="158"/>
-    </row>
-    <row r="4" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="4" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A4" s="148" t="s">
         <v>34</v>
       </c>
@@ -3225,7 +3215,7 @@
       </c>
       <c r="K4" s="148"/>
       <c r="L4" s="161">
-        <f t="shared" ref="L4:L48" si="0">COUNTIF(M4:AW4,"✓")</f>
+        <f t="shared" ref="L4:L48" si="0">COUNTIF(M4:AV4,"✓")</f>
         <v>3</v>
       </c>
       <c r="M4" s="151"/>
@@ -3251,9 +3241,8 @@
       <c r="AA4" s="148"/>
       <c r="AB4" s="148"/>
       <c r="AC4" s="148"/>
-      <c r="AD4" s="148"/>
-    </row>
-    <row r="5" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="5" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A5" s="142" t="s">
         <v>245</v>
       </c>
@@ -3285,7 +3274,7 @@
       <c r="K5" s="142"/>
       <c r="L5" s="161">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M5" s="145"/>
       <c r="N5" s="145"/>
@@ -3322,11 +3311,8 @@
       <c r="AC5" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD5" s="142" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="6" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A6" s="148" t="s">
         <v>41</v>
       </c>
@@ -3385,9 +3371,8 @@
       <c r="AC6" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD6" s="148"/>
-    </row>
-    <row r="7" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="7" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A7" s="142" t="s">
         <v>44</v>
       </c>
@@ -3419,7 +3404,7 @@
       <c r="K7" s="142"/>
       <c r="L7" s="161">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M7" s="145"/>
       <c r="N7" s="145"/>
@@ -3448,11 +3433,8 @@
       <c r="AC7" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD7" s="142" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="8" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A8" s="148" t="s">
         <v>46</v>
       </c>
@@ -3523,9 +3505,8 @@
       <c r="AA8" s="148"/>
       <c r="AB8" s="148"/>
       <c r="AC8" s="148"/>
-      <c r="AD8" s="148"/>
-    </row>
-    <row r="9" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="9" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A9" s="142" t="s">
         <v>49</v>
       </c>
@@ -3557,7 +3538,7 @@
       <c r="K9" s="142"/>
       <c r="L9" s="161">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M9" s="145" t="s">
         <v>32</v>
@@ -3610,11 +3591,8 @@
       <c r="AC9" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD9" s="142" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="10" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A10" s="148" t="s">
         <v>50</v>
       </c>
@@ -3667,9 +3645,8 @@
       <c r="AA10" s="148"/>
       <c r="AB10" s="148"/>
       <c r="AC10" s="148"/>
-      <c r="AD10" s="148"/>
-    </row>
-    <row r="11" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="11" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A11" s="142" t="s">
         <v>52</v>
       </c>
@@ -3736,9 +3713,8 @@
       <c r="AA11" s="142"/>
       <c r="AB11" s="142"/>
       <c r="AC11" s="142"/>
-      <c r="AD11" s="142"/>
-    </row>
-    <row r="12" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="12" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A12" s="148" t="s">
         <v>54</v>
       </c>
@@ -3770,7 +3746,7 @@
       <c r="K12" s="148"/>
       <c r="L12" s="161">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12" s="151"/>
       <c r="N12" s="151"/>
@@ -3801,11 +3777,8 @@
       <c r="AC12" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD12" s="148" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="13" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A13" s="142" t="s">
         <v>57</v>
       </c>
@@ -3860,9 +3833,8 @@
       <c r="AA13" s="142"/>
       <c r="AB13" s="142"/>
       <c r="AC13" s="142"/>
-      <c r="AD13" s="142"/>
-    </row>
-    <row r="14" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="14" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A14" s="148" t="s">
         <v>61</v>
       </c>
@@ -3913,9 +3885,8 @@
       <c r="AA14" s="148"/>
       <c r="AB14" s="148"/>
       <c r="AC14" s="148"/>
-      <c r="AD14" s="148"/>
-    </row>
-    <row r="15" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="15" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A15" s="142" t="s">
         <v>63</v>
       </c>
@@ -3947,7 +3918,7 @@
       <c r="K15" s="142"/>
       <c r="L15" s="161">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M15" s="145"/>
       <c r="N15" s="145" t="s">
@@ -3992,11 +3963,8 @@
       <c r="AC15" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD15" s="142" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="16" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A16" s="148" t="s">
         <v>65</v>
       </c>
@@ -4063,9 +4031,8 @@
       <c r="AC16" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD16" s="148"/>
-    </row>
-    <row r="17" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="17" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A17" s="142" t="s">
         <v>67</v>
       </c>
@@ -4118,9 +4085,8 @@
       <c r="AA17" s="142"/>
       <c r="AB17" s="142"/>
       <c r="AC17" s="142"/>
-      <c r="AD17" s="142"/>
-    </row>
-    <row r="18" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="18" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A18" s="148" t="s">
         <v>70</v>
       </c>
@@ -4152,7 +4118,7 @@
       <c r="K18" s="148"/>
       <c r="L18" s="161">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M18" s="151"/>
       <c r="N18" s="151"/>
@@ -4187,11 +4153,8 @@
       <c r="AC18" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD18" s="148" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="19" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A19" s="142" t="s">
         <v>72</v>
       </c>
@@ -4223,7 +4186,7 @@
       <c r="K19" s="142"/>
       <c r="L19" s="161">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M19" s="145"/>
       <c r="N19" s="145"/>
@@ -4252,11 +4215,8 @@
       <c r="AC19" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD19" s="142" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="20" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A20" s="148" t="s">
         <v>74</v>
       </c>
@@ -4325,9 +4285,8 @@
       <c r="AC20" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD20" s="148"/>
-    </row>
-    <row r="21" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="21" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A21" s="142" t="s">
         <v>76</v>
       </c>
@@ -4378,9 +4337,8 @@
       <c r="AA21" s="142"/>
       <c r="AB21" s="142"/>
       <c r="AC21" s="142"/>
-      <c r="AD21" s="142"/>
-    </row>
-    <row r="22" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="22" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A22" s="148" t="s">
         <v>78</v>
       </c>
@@ -4412,7 +4370,7 @@
       <c r="K22" s="148"/>
       <c r="L22" s="161">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M22" s="151" t="s">
         <v>32</v>
@@ -4463,11 +4421,8 @@
       <c r="AC22" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD22" s="148" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="23" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A23" s="142" t="s">
         <v>80</v>
       </c>
@@ -4534,9 +4489,8 @@
       <c r="AA23" s="142"/>
       <c r="AB23" s="142"/>
       <c r="AC23" s="142"/>
-      <c r="AD23" s="142"/>
-    </row>
-    <row r="24" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="24" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A24" s="148" t="s">
         <v>82</v>
       </c>
@@ -4601,9 +4555,8 @@
         <v>32</v>
       </c>
       <c r="AC24" s="148"/>
-      <c r="AD24" s="148"/>
-    </row>
-    <row r="25" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="25" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A25" s="142" t="s">
         <v>85</v>
       </c>
@@ -4637,7 +4590,7 @@
       <c r="K25" s="142"/>
       <c r="L25" s="161">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M25" s="145"/>
       <c r="N25" s="145"/>
@@ -4676,11 +4629,8 @@
       <c r="AC25" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD25" s="142" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="26" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A26" s="148" t="s">
         <v>87</v>
       </c>
@@ -4733,9 +4683,8 @@
       <c r="AC26" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="AD26" s="152"/>
-    </row>
-    <row r="27" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="27" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A27" s="142" t="s">
         <v>89</v>
       </c>
@@ -4792,9 +4741,8 @@
       <c r="AC27" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD27" s="142"/>
-    </row>
-    <row r="28" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="28" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A28" s="148" t="s">
         <v>90</v>
       </c>
@@ -4826,7 +4774,7 @@
       <c r="K28" s="148"/>
       <c r="L28" s="161">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M28" s="151"/>
       <c r="N28" s="151"/>
@@ -4855,11 +4803,8 @@
       <c r="AC28" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD28" s="148" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="29" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A29" s="142" t="s">
         <v>92</v>
       </c>
@@ -4934,9 +4879,8 @@
       <c r="AC29" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD29" s="142"/>
-    </row>
-    <row r="30" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="30" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A30" s="148" t="s">
         <v>94</v>
       </c>
@@ -5017,9 +4961,8 @@
       <c r="AC30" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD30" s="148"/>
-    </row>
-    <row r="31" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="31" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A31" s="142" t="s">
         <v>96</v>
       </c>
@@ -5074,9 +5017,8 @@
       <c r="AA31" s="142"/>
       <c r="AB31" s="142"/>
       <c r="AC31" s="142"/>
-      <c r="AD31" s="142"/>
-    </row>
-    <row r="32" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="32" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A32" s="148" t="s">
         <v>97</v>
       </c>
@@ -5141,9 +5083,8 @@
       <c r="AC32" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD32" s="148"/>
-    </row>
-    <row r="33" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="33" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A33" s="142" t="s">
         <v>99</v>
       </c>
@@ -5175,7 +5116,7 @@
       <c r="K33" s="142"/>
       <c r="L33" s="161">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M33" s="145"/>
       <c r="N33" s="145"/>
@@ -5218,11 +5159,8 @@
       <c r="AC33" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD33" s="142" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="34" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A34" s="148" t="s">
         <v>101</v>
       </c>
@@ -5287,9 +5225,8 @@
       <c r="AA34" s="148"/>
       <c r="AB34" s="148"/>
       <c r="AC34" s="148"/>
-      <c r="AD34" s="148"/>
-    </row>
-    <row r="35" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="35" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A35" s="142" t="s">
         <v>103</v>
       </c>
@@ -5358,9 +5295,8 @@
       <c r="AC35" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD35" s="142"/>
-    </row>
-    <row r="36" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="36" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A36" s="148" t="s">
         <v>104</v>
       </c>
@@ -5417,9 +5353,8 @@
       </c>
       <c r="AB36" s="148"/>
       <c r="AC36" s="148"/>
-      <c r="AD36" s="148"/>
-    </row>
-    <row r="37" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="37" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A37" s="142" t="s">
         <v>106</v>
       </c>
@@ -5451,7 +5386,7 @@
       <c r="K37" s="142"/>
       <c r="L37" s="161">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M37" s="145"/>
       <c r="N37" s="145"/>
@@ -5488,11 +5423,8 @@
       <c r="AC37" s="142" t="s">
         <v>32</v>
       </c>
-      <c r="AD37" s="142" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="38" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A38" s="148" t="s">
         <v>108</v>
       </c>
@@ -5524,7 +5456,7 @@
       <c r="K38" s="148"/>
       <c r="L38" s="161">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M38" s="151"/>
       <c r="N38" s="151"/>
@@ -5553,11 +5485,8 @@
       <c r="AC38" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD38" s="148" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="39" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A39" s="142" t="s">
         <v>110</v>
       </c>
@@ -5610,9 +5539,8 @@
       <c r="AA39" s="142"/>
       <c r="AB39" s="142"/>
       <c r="AC39" s="142"/>
-      <c r="AD39" s="142"/>
-    </row>
-    <row r="40" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="40" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A40" s="148" t="s">
         <v>113</v>
       </c>
@@ -5663,9 +5591,8 @@
       <c r="AA40" s="148"/>
       <c r="AB40" s="148"/>
       <c r="AC40" s="148"/>
-      <c r="AD40" s="148"/>
-    </row>
-    <row r="41" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="41" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A41" s="142" t="s">
         <v>114</v>
       </c>
@@ -5722,9 +5649,8 @@
       <c r="AA41" s="142"/>
       <c r="AB41" s="142"/>
       <c r="AC41" s="142"/>
-      <c r="AD41" s="142"/>
-    </row>
-    <row r="42" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="42" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A42" s="148" t="s">
         <v>116</v>
       </c>
@@ -5787,9 +5713,8 @@
       <c r="AC42" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD42" s="148"/>
-    </row>
-    <row r="43" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="43" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A43" s="142" t="s">
         <v>118</v>
       </c>
@@ -5842,9 +5767,8 @@
       <c r="AA43" s="142"/>
       <c r="AB43" s="142"/>
       <c r="AC43" s="142"/>
-      <c r="AD43" s="142"/>
-    </row>
-    <row r="44" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="44" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A44" s="148" t="s">
         <v>120</v>
       </c>
@@ -5905,9 +5829,8 @@
       <c r="AC44" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD44" s="148"/>
-    </row>
-    <row r="45" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="45" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A45" s="142" t="s">
         <v>121</v>
       </c>
@@ -5958,9 +5881,8 @@
       <c r="AA45" s="142"/>
       <c r="AB45" s="142"/>
       <c r="AC45" s="142"/>
-      <c r="AD45" s="142"/>
-    </row>
-    <row r="46" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
+    </row>
+    <row r="46" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A46" s="148" t="s">
         <v>123</v>
       </c>
@@ -5992,7 +5914,7 @@
       <c r="K46" s="148"/>
       <c r="L46" s="161">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M46" s="151" t="s">
         <v>32</v>
@@ -6045,11 +5967,8 @@
       <c r="AC46" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD46" s="148" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="47" spans="1:30" s="147" customFormat="1" ht="20" customHeight="1">
+    </row>
+    <row r="47" spans="1:29" s="147" customFormat="1" ht="20" customHeight="1">
       <c r="A47" s="142" t="s">
         <v>124</v>
       </c>
@@ -6094,9 +6013,8 @@
       <c r="AA47" s="142"/>
       <c r="AB47" s="142"/>
       <c r="AC47" s="142"/>
-      <c r="AD47" s="142"/>
-    </row>
-    <row r="48" spans="1:30" s="147" customFormat="1" ht="17" customHeight="1">
+    </row>
+    <row r="48" spans="1:29" s="147" customFormat="1" ht="17" customHeight="1">
       <c r="A48" s="148" t="s">
         <v>127</v>
       </c>
@@ -6128,7 +6046,7 @@
       <c r="K48" s="148"/>
       <c r="L48" s="161">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M48" s="151" t="s">
         <v>32</v>
@@ -6169,11 +6087,8 @@
       <c r="AC48" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="AD48" s="148" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="49" spans="1:30">
+    </row>
+    <row r="49" spans="1:29">
       <c r="A49" s="7"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -6203,7 +6118,6 @@
       <c r="AA49" s="7"/>
       <c r="AB49" s="7"/>
       <c r="AC49" s="7"/>
-      <c r="AD49" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6222,7 +6136,6 @@
     <hyperlink ref="AA2" location="'2024-07-13 Chicago Union'!A1" display="2024-07-13_x000a_Chicago Union" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="AB2" location="'2024-06-08 Fat Shallot'!A1" display="2024-06-08_x000a_Fat Shallot" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
     <hyperlink ref="AC2" location="'2024-04-27 Lincolnwood'!A1" display="2024-04-27_x000a_Lincolnwood" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="AD2" location="'2023-09-09 Block Party'!A1" display="2023-09-09_x000a_Block Party" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
     <hyperlink ref="C3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
     <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
@@ -6343,7 +6256,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -6789,7 +6702,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -7094,7 +7007,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -7857,7 +7770,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -8230,7 +8143,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -8609,7 +8522,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -9304,7 +9217,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -9826,7 +9739,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -10218,7 +10131,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -10541,7 +10454,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -11759,7 +11672,9 @@
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
       <c r="K21" s="40"/>
-      <c r="L21" s="9"/>
+      <c r="L21" s="9" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="22" spans="1:12" ht="22" customHeight="1">
       <c r="A22" s="82">
@@ -11860,7 +11775,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -12406,7 +12321,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -12734,7 +12649,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -13169,7 +13084,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -13498,7 +13413,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -14404,7 +14319,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="177" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B2" s="178"/>
       <c r="C2" s="178"/>
@@ -15072,7 +14987,7 @@
     </row>
     <row r="2" spans="1:6" ht="18" thickBot="1">
       <c r="A2" s="183" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B2" s="184"/>
       <c r="C2" s="184"/>
@@ -16250,7 +16165,7 @@
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
       <c r="A2" s="196" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B2" s="197"/>
       <c r="C2" s="197"/>

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/milesshultz/Documents/kings_website/rock/docs/resources/setlists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6296D778-BD0D-C24F-B0BB-8BC3785AAFCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0CF8FAE-5407-194D-B46C-75870AF46B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3880" yWindow="3020" windowWidth="29580" windowHeight="17160" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3880" yWindow="3020" windowWidth="29580" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Song Tracker" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2355" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2356" uniqueCount="276">
   <si>
     <t>KINGS OF EWING — SONG TRACKER</t>
   </si>
@@ -906,7 +906,11 @@
     <t>2023-09-09 | Ewing Block Party</t>
   </si>
   <si>
-    <t>2026-06-21 | Chicago Union (cancelled) | 5:00 PM</t>
+    <t>2026-06-21 | Chicago Union | 5:00 PM</t>
+  </si>
+  <si>
+    <t>2026-06-21
+Chicago Union Rain C</t>
   </si>
 </sst>
 </file>
@@ -919,7 +923,7 @@
     <numFmt numFmtId="165" formatCode="[m]:ss"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1088,6 +1092,29 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Courier New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <strike/>
+      <u/>
+      <sz val="13"/>
+      <color rgb="FF0563C1"/>
       <name val="Courier New"/>
       <family val="1"/>
     </font>
@@ -2074,7 +2101,7 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2545,6 +2572,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2568,27 +2607,6 @@
     <xf numFmtId="0" fontId="21" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2621,6 +2639,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="66" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="69" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2980,7 +3013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AD49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.83203125" bestFit="1" customWidth="1"/>
@@ -3006,9 +3039,10 @@
     <col min="25" max="25" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="27" max="29" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="28.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="167" customFormat="1" ht="28" customHeight="1" thickBot="1">
+    <row r="1" spans="1:30" s="167" customFormat="1" ht="28" customHeight="1" thickBot="1">
       <c r="A1" s="164" t="s">
         <v>0</v>
       </c>
@@ -3041,7 +3075,7 @@
       <c r="AB1" s="165"/>
       <c r="AC1" s="165"/>
     </row>
-    <row r="2" spans="1:29" s="173" customFormat="1" ht="56" customHeight="1" thickBot="1">
+    <row r="2" spans="1:30" s="173" customFormat="1" ht="56" customHeight="1" thickBot="1">
       <c r="A2" s="168" t="s">
         <v>1</v>
       </c>
@@ -3129,8 +3163,11 @@
       <c r="AC2" s="172" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" s="163" customFormat="1" ht="22" customHeight="1">
+      <c r="AD2" s="203" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" s="163" customFormat="1" ht="22" customHeight="1">
       <c r="A3" s="158" t="s">
         <v>28</v>
       </c>
@@ -3186,7 +3223,7 @@
       <c r="AB3" s="158"/>
       <c r="AC3" s="158"/>
     </row>
-    <row r="4" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="4" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A4" s="148" t="s">
         <v>34</v>
       </c>
@@ -3242,7 +3279,7 @@
       <c r="AB4" s="148"/>
       <c r="AC4" s="148"/>
     </row>
-    <row r="5" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="5" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A5" s="142" t="s">
         <v>245</v>
       </c>
@@ -3312,7 +3349,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="6" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A6" s="148" t="s">
         <v>41</v>
       </c>
@@ -3372,7 +3409,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="7" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A7" s="142" t="s">
         <v>44</v>
       </c>
@@ -3434,7 +3471,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="8" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A8" s="148" t="s">
         <v>46</v>
       </c>
@@ -3506,7 +3543,7 @@
       <c r="AB8" s="148"/>
       <c r="AC8" s="148"/>
     </row>
-    <row r="9" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="9" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A9" s="142" t="s">
         <v>49</v>
       </c>
@@ -3592,7 +3629,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="10" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A10" s="148" t="s">
         <v>50</v>
       </c>
@@ -3646,7 +3683,7 @@
       <c r="AB10" s="148"/>
       <c r="AC10" s="148"/>
     </row>
-    <row r="11" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="11" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A11" s="142" t="s">
         <v>52</v>
       </c>
@@ -3714,7 +3751,7 @@
       <c r="AB11" s="142"/>
       <c r="AC11" s="142"/>
     </row>
-    <row r="12" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="12" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A12" s="148" t="s">
         <v>54</v>
       </c>
@@ -3778,7 +3815,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="13" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A13" s="142" t="s">
         <v>57</v>
       </c>
@@ -3834,7 +3871,7 @@
       <c r="AB13" s="142"/>
       <c r="AC13" s="142"/>
     </row>
-    <row r="14" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="14" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A14" s="148" t="s">
         <v>61</v>
       </c>
@@ -3886,7 +3923,7 @@
       <c r="AB14" s="148"/>
       <c r="AC14" s="148"/>
     </row>
-    <row r="15" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="15" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A15" s="142" t="s">
         <v>63</v>
       </c>
@@ -3964,7 +4001,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="147" customFormat="1" ht="22" customHeight="1">
+    <row r="16" spans="1:30" s="147" customFormat="1" ht="22" customHeight="1">
       <c r="A16" s="148" t="s">
         <v>65</v>
       </c>
@@ -6226,6 +6263,7 @@
     <hyperlink ref="B5" r:id="rId88" xr:uid="{EA461231-8E8E-5746-9DF4-72454CC19E36}"/>
     <hyperlink ref="C5" r:id="rId89" xr:uid="{C5ECF11B-005F-3145-827A-22E761430CCB}"/>
     <hyperlink ref="N2" location="'2026-05-16 Fat Shallot'!A1" display="'2026-05-16 Fat Shallot'!A1" xr:uid="{597DD363-3141-A541-AF9D-176342F818C3}"/>
+    <hyperlink ref="AD2" location="'2026-06-21 Chicago Union Rain C'!A1" tooltip="2026-06-21 Chicago Union Rain C (canceled)" display="2026-06-21_x000a_Chicago Union Rain C" xr:uid="{6840618D-39FF-DF48-B788-46D9D6FEF688}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -6245,24 +6283,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>259</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -6691,24 +6729,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>260</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -6996,24 +7034,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>261</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -7759,24 +7797,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>262</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -8132,24 +8170,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>263</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -8511,24 +8549,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>264</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -9206,24 +9244,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>265</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -9728,24 +9766,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>266</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -10120,24 +10158,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>267</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -10443,24 +10481,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>268</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -11445,7 +11483,7 @@
         <v>167</v>
       </c>
       <c r="B14" s="12"/>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="199" t="s">
         <v>168</v>
       </c>
       <c r="D14" s="9"/>
@@ -11651,7 +11689,7 @@
       <c r="B21" s="52">
         <v>0.70833333333333337</v>
       </c>
-      <c r="C21" s="9" t="s">
+      <c r="C21" s="199" t="s">
         <v>154</v>
       </c>
       <c r="D21" s="9" t="s">
@@ -11764,24 +11802,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>269</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -12310,24 +12348,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>270</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -12638,24 +12676,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -13073,24 +13111,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>272</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -13402,24 +13440,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>273</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="115" t="s">
@@ -14308,24 +14346,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="179"/>
+      <c r="C1" s="179"/>
+      <c r="D1" s="179"/>
+      <c r="E1" s="179"/>
+      <c r="F1" s="180"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="177" t="s">
+      <c r="A2" s="181" t="s">
         <v>257</v>
       </c>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="182"/>
+      <c r="E2" s="182"/>
+      <c r="F2" s="183"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A3" s="115" t="s">
@@ -14628,14 +14666,14 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="17">
-      <c r="A18" s="180" t="s">
+      <c r="A18" s="184" t="s">
         <v>246</v>
       </c>
-      <c r="B18" s="181"/>
-      <c r="C18" s="181"/>
-      <c r="D18" s="181"/>
-      <c r="E18" s="181"/>
-      <c r="F18" s="182"/>
+      <c r="B18" s="185"/>
+      <c r="C18" s="185"/>
+      <c r="D18" s="185"/>
+      <c r="E18" s="185"/>
+      <c r="F18" s="186"/>
     </row>
     <row r="19" spans="1:6" ht="17">
       <c r="A19" s="126">
@@ -14976,24 +15014,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="187" t="s">
+      <c r="A1" s="175" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="189"/>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+      <c r="D1" s="176"/>
+      <c r="E1" s="176"/>
+      <c r="F1" s="177"/>
     </row>
     <row r="2" spans="1:6" ht="18" thickBot="1">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="200" t="s">
         <v>274</v>
       </c>
-      <c r="B2" s="184"/>
-      <c r="C2" s="184"/>
-      <c r="D2" s="184"/>
-      <c r="E2" s="184"/>
-      <c r="F2" s="185"/>
+      <c r="B2" s="201"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="201"/>
+      <c r="E2" s="201"/>
+      <c r="F2" s="202"/>
     </row>
     <row r="3" spans="1:6" ht="18" thickBot="1">
       <c r="A3" s="105" t="s">
@@ -15332,12 +15370,12 @@
     </row>
     <row r="19" spans="1:6" ht="18" thickBot="1">
       <c r="A19" s="94"/>
-      <c r="B19" s="186" t="s">
+      <c r="B19" s="174" t="s">
         <v>243</v>
       </c>
-      <c r="C19" s="186"/>
-      <c r="D19" s="186"/>
-      <c r="E19" s="186"/>
+      <c r="C19" s="174"/>
+      <c r="D19" s="174"/>
+      <c r="E19" s="174"/>
       <c r="F19" s="108">
         <f>SUM(F4:F18)</f>
         <v>4.0509259259259259E-2</v>
@@ -15497,14 +15535,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="187" t="s">
         <v>244</v>
       </c>
-      <c r="B1" s="191"/>
-      <c r="C1" s="191"/>
-      <c r="D1" s="191"/>
-      <c r="E1" s="191"/>
-      <c r="F1" s="192"/>
+      <c r="B1" s="188"/>
+      <c r="C1" s="188"/>
+      <c r="D1" s="188"/>
+      <c r="E1" s="188"/>
+      <c r="F1" s="189"/>
     </row>
     <row r="2" spans="1:6" ht="22" customHeight="1" thickBot="1">
       <c r="A2" s="54" t="s">
@@ -15807,14 +15845,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22" customHeight="1">
-      <c r="A17" s="193" t="s">
+      <c r="A17" s="190" t="s">
         <v>246</v>
       </c>
-      <c r="B17" s="194"/>
-      <c r="C17" s="194"/>
-      <c r="D17" s="194"/>
-      <c r="E17" s="194"/>
-      <c r="F17" s="195"/>
+      <c r="B17" s="191"/>
+      <c r="C17" s="191"/>
+      <c r="D17" s="191"/>
+      <c r="E17" s="191"/>
+      <c r="F17" s="192"/>
     </row>
     <row r="18" spans="1:6" ht="22" customHeight="1">
       <c r="A18" s="62">
@@ -16154,24 +16192,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="50" thickBot="1">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="196" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="201"/>
+      <c r="B1" s="197"/>
+      <c r="C1" s="197"/>
+      <c r="D1" s="197"/>
+      <c r="E1" s="197"/>
+      <c r="F1" s="198"/>
     </row>
     <row r="2" spans="1:6" ht="28" customHeight="1" thickBot="1">
-      <c r="A2" s="196" t="s">
+      <c r="A2" s="193" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="197"/>
-      <c r="C2" s="197"/>
-      <c r="D2" s="197"/>
-      <c r="E2" s="197"/>
-      <c r="F2" s="198"/>
+      <c r="B2" s="194"/>
+      <c r="C2" s="194"/>
+      <c r="D2" s="194"/>
+      <c r="E2" s="194"/>
+      <c r="F2" s="195"/>
     </row>
     <row r="3" spans="1:6" ht="22" customHeight="1">
       <c r="A3" s="119" t="s">

--- a/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
+++ b/docs/resources/setlists/Kings_of_Ewing_Setlists.xlsx
@@ -1388,7 +1388,7 @@
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="228">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -1989,6 +1989,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="84" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="70" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="21" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14195,10 +14198,8 @@
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>6:00 PM</t>
-        </is>
+      <c r="B18" s="228" t="n">
+        <v>0.5</v>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
@@ -14214,7 +14215,7 @@
         <v>16</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="G18" s="9" t="n"/>
       <c r="H18" s="9" t="n"/>
@@ -18710,7 +18711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="4.83203125" customWidth="1" style="13" min="1" max="1"/>
@@ -19226,39 +19227,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
